--- a/research/traditional_assets/database/data/greece/greece_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_beverage_alcoholic.xlsx
@@ -588,115 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.113</v>
+        <v>0.154</v>
+      </c>
+      <c r="E2">
+        <v>0.5539999999999999</v>
       </c>
       <c r="G2">
-        <v>0.0526875</v>
+        <v>0.03666666666666667</v>
       </c>
       <c r="H2">
-        <v>0.0526875</v>
+        <v>0.03666666666666667</v>
       </c>
       <c r="I2">
-        <v>-0.0341875</v>
+        <v>-0.005589743589743589</v>
       </c>
       <c r="J2">
-        <v>-0.02786575969827586</v>
+        <v>-0.004447176830078384</v>
       </c>
       <c r="K2">
-        <v>1.89</v>
+        <v>3.07</v>
       </c>
       <c r="L2">
-        <v>0.118125</v>
+        <v>0.1574358974358974</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01817589576547231</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.1817589576547232</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01817589576547231</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.1817589576547232</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>0.07651515151515151</v>
+        <v>0.09771986970684039</v>
       </c>
       <c r="W2">
-        <v>0.0627906976744186</v>
+        <v>0.09136904761904761</v>
       </c>
       <c r="X2">
-        <v>0.09473699665972882</v>
+        <v>0.1618163271119344</v>
       </c>
       <c r="Y2">
-        <v>-0.03194629898531022</v>
+        <v>-0.07044727949288677</v>
       </c>
       <c r="Z2">
-        <v>0.4233924318602805</v>
+        <v>0.461320085166785</v>
       </c>
       <c r="AA2">
-        <v>-0.01179815176428721</v>
+        <v>-0.002051571994003513</v>
       </c>
       <c r="AB2">
-        <v>0.08248578834041914</v>
+        <v>0.142048997589148</v>
       </c>
       <c r="AC2">
-        <v>-0.09428394010470635</v>
+        <v>-0.1441005695831515</v>
       </c>
       <c r="AD2">
-        <v>11.7</v>
+        <v>9.81</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.7</v>
+        <v>9.81</v>
       </c>
       <c r="AG2">
-        <v>8.67</v>
+        <v>6.81</v>
       </c>
       <c r="AH2">
-        <v>0.2280701754385965</v>
+        <v>0.2421624290298692</v>
       </c>
       <c r="AI2">
-        <v>0.2582781456953642</v>
+        <v>0.2280864915136015</v>
       </c>
       <c r="AJ2">
-        <v>0.1796146674953387</v>
+        <v>0.1815515862436684</v>
       </c>
       <c r="AK2">
-        <v>0.2051100070972321</v>
+        <v>0.1702074481379655</v>
       </c>
       <c r="AL2">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="AM2">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="AN2">
-        <v>13.17567567567568</v>
+        <v>7.213235294117647</v>
       </c>
       <c r="AO2">
-        <v>-1.919298245614036</v>
+        <v>-0.394927536231884</v>
       </c>
       <c r="AP2">
-        <v>9.763513513513514</v>
+        <v>5.007352941176471</v>
       </c>
       <c r="AQ2">
-        <v>-1.919298245614036</v>
+        <v>-0.394927536231884</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.113</v>
+        <v>0.154</v>
+      </c>
+      <c r="E3">
+        <v>0.5539999999999999</v>
       </c>
       <c r="G3">
-        <v>0.0526875</v>
+        <v>0.03666666666666667</v>
       </c>
       <c r="H3">
-        <v>0.0526875</v>
+        <v>0.03666666666666667</v>
       </c>
       <c r="I3">
-        <v>-0.0341875</v>
+        <v>-0.005589743589743589</v>
       </c>
       <c r="J3">
-        <v>-0.02786575969827586</v>
+        <v>-0.004447176830078384</v>
       </c>
       <c r="K3">
-        <v>1.89</v>
+        <v>3.07</v>
       </c>
       <c r="L3">
-        <v>0.118125</v>
+        <v>0.1574358974358974</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01817589576547231</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1817589576547232</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01817589576547231</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1817589576547232</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="V3">
-        <v>0.07651515151515151</v>
+        <v>0.09771986970684039</v>
       </c>
       <c r="W3">
-        <v>0.0627906976744186</v>
+        <v>0.09136904761904761</v>
       </c>
       <c r="X3">
-        <v>0.09473699665972882</v>
+        <v>0.1618163271119344</v>
       </c>
       <c r="Y3">
-        <v>-0.03194629898531022</v>
+        <v>-0.07044727949288677</v>
       </c>
       <c r="Z3">
-        <v>0.4233924318602805</v>
+        <v>0.461320085166785</v>
       </c>
       <c r="AA3">
-        <v>-0.01179815176428721</v>
+        <v>-0.002051571994003513</v>
       </c>
       <c r="AB3">
-        <v>0.08248578834041914</v>
+        <v>0.142048997589148</v>
       </c>
       <c r="AC3">
-        <v>-0.09428394010470635</v>
+        <v>-0.1441005695831515</v>
       </c>
       <c r="AD3">
-        <v>11.7</v>
+        <v>9.81</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.7</v>
+        <v>9.81</v>
       </c>
       <c r="AG3">
-        <v>8.67</v>
+        <v>6.81</v>
       </c>
       <c r="AH3">
-        <v>0.2280701754385965</v>
+        <v>0.2421624290298692</v>
       </c>
       <c r="AI3">
-        <v>0.2582781456953642</v>
+        <v>0.2280864915136015</v>
       </c>
       <c r="AJ3">
-        <v>0.1796146674953387</v>
+        <v>0.1815515862436684</v>
       </c>
       <c r="AK3">
-        <v>0.2051100070972321</v>
+        <v>0.1702074481379655</v>
       </c>
       <c r="AL3">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="AM3">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="AN3">
-        <v>13.17567567567568</v>
+        <v>7.213235294117647</v>
       </c>
       <c r="AO3">
-        <v>-1.919298245614036</v>
+        <v>-0.394927536231884</v>
       </c>
       <c r="AP3">
-        <v>9.763513513513514</v>
+        <v>5.007352941176471</v>
       </c>
       <c r="AQ3">
-        <v>-1.919298245614036</v>
+        <v>-0.394927536231884</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/greece/greece_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_beverage_alcoholic.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="atse_ktila" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.154</v>
+        <v>0.163</v>
       </c>
       <c r="E2">
-        <v>0.5539999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="G2">
-        <v>0.03666666666666667</v>
+        <v>0.05732217573221758</v>
       </c>
       <c r="H2">
-        <v>0.03666666666666667</v>
+        <v>0.05732217573221758</v>
       </c>
       <c r="I2">
-        <v>-0.005589743589743589</v>
+        <v>0.000794979079497908</v>
       </c>
       <c r="J2">
-        <v>-0.004447176830078384</v>
+        <v>0.0006093672239323171</v>
       </c>
       <c r="K2">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="L2">
-        <v>0.1574358974358974</v>
+        <v>0.1456066945606695</v>
       </c>
       <c r="M2">
-        <v>0.5580000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="N2">
-        <v>0.01817589576547231</v>
+        <v>0.01576</v>
       </c>
       <c r="O2">
-        <v>0.1817589576547232</v>
+        <v>0.1698275862068965</v>
       </c>
       <c r="P2">
-        <v>0.5580000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="Q2">
-        <v>0.01817589576547231</v>
+        <v>0.01576</v>
       </c>
       <c r="R2">
-        <v>0.1817589576547232</v>
+        <v>0.1698275862068965</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>0.437</v>
       </c>
       <c r="V2">
-        <v>0.09771986970684039</v>
+        <v>0.01165333333333333</v>
       </c>
       <c r="W2">
-        <v>0.09136904761904761</v>
+        <v>0.1048192771084337</v>
       </c>
       <c r="X2">
-        <v>0.1618163271119344</v>
+        <v>0.1095499624054719</v>
       </c>
       <c r="Y2">
-        <v>-0.07044727949288677</v>
+        <v>-0.004730685297038129</v>
       </c>
       <c r="Z2">
-        <v>0.461320085166785</v>
+        <v>0.5973506623344162</v>
       </c>
       <c r="AA2">
-        <v>-0.002051571994003513</v>
+        <v>0.0003640059148208542</v>
       </c>
       <c r="AB2">
-        <v>0.142048997589148</v>
+        <v>0.09863014904290901</v>
       </c>
       <c r="AC2">
-        <v>-0.1441005695831515</v>
+        <v>-0.09826614312808815</v>
       </c>
       <c r="AD2">
-        <v>9.81</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9.81</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>6.81</v>
+        <v>11.063</v>
       </c>
       <c r="AH2">
-        <v>0.2421624290298692</v>
+        <v>0.2346938775510204</v>
       </c>
       <c r="AI2">
-        <v>0.2280864915136015</v>
+        <v>0.2327935222672065</v>
       </c>
       <c r="AJ2">
-        <v>0.1815515862436684</v>
+        <v>0.2278071783044705</v>
       </c>
       <c r="AK2">
-        <v>0.1702074481379655</v>
+        <v>0.2259461225823581</v>
       </c>
       <c r="AL2">
-        <v>0.276</v>
+        <v>0.246</v>
       </c>
       <c r="AM2">
-        <v>0.276</v>
+        <v>0.246</v>
       </c>
       <c r="AN2">
-        <v>7.213235294117647</v>
+        <v>6.571428571428571</v>
       </c>
       <c r="AO2">
-        <v>-0.394927536231884</v>
+        <v>0.07723577235772358</v>
       </c>
       <c r="AP2">
-        <v>5.007352941176471</v>
+        <v>6.321714285714286</v>
       </c>
       <c r="AQ2">
-        <v>-0.394927536231884</v>
+        <v>0.07723577235772358</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.154</v>
+        <v>0.163</v>
       </c>
       <c r="E3">
-        <v>0.5539999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="G3">
-        <v>0.03666666666666667</v>
+        <v>0.05732217573221758</v>
       </c>
       <c r="H3">
-        <v>0.03666666666666667</v>
+        <v>0.05732217573221758</v>
       </c>
       <c r="I3">
-        <v>-0.005589743589743589</v>
+        <v>0.000794979079497908</v>
       </c>
       <c r="J3">
-        <v>-0.004447176830078384</v>
+        <v>0.0006093672239323171</v>
       </c>
       <c r="K3">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="L3">
-        <v>0.1574358974358974</v>
+        <v>0.1456066945606695</v>
       </c>
       <c r="M3">
-        <v>0.5580000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="N3">
-        <v>0.01817589576547231</v>
+        <v>0.01576</v>
       </c>
       <c r="O3">
-        <v>0.1817589576547232</v>
+        <v>0.1698275862068965</v>
       </c>
       <c r="P3">
-        <v>0.5580000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="Q3">
-        <v>0.01817589576547231</v>
+        <v>0.01576</v>
       </c>
       <c r="R3">
-        <v>0.1817589576547232</v>
+        <v>0.1698275862068965</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +772,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
+        <v>0.437</v>
+      </c>
+      <c r="V3">
+        <v>0.01165333333333333</v>
+      </c>
+      <c r="W3">
+        <v>0.1048192771084337</v>
+      </c>
+      <c r="X3">
+        <v>0.1095499624054719</v>
+      </c>
+      <c r="Y3">
+        <v>-0.004730685297038129</v>
+      </c>
+      <c r="Z3">
+        <v>0.5973506623344162</v>
+      </c>
+      <c r="AA3">
+        <v>0.0003640059148208542</v>
+      </c>
+      <c r="AB3">
+        <v>0.09863014904290901</v>
+      </c>
+      <c r="AC3">
+        <v>-0.09826614312808815</v>
+      </c>
+      <c r="AD3">
+        <v>11.5</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>11.063</v>
+      </c>
+      <c r="AH3">
+        <v>0.2346938775510204</v>
+      </c>
+      <c r="AI3">
+        <v>0.2327935222672065</v>
+      </c>
+      <c r="AJ3">
+        <v>0.2278071783044705</v>
+      </c>
+      <c r="AK3">
+        <v>0.2259461225823581</v>
+      </c>
+      <c r="AL3">
+        <v>0.246</v>
+      </c>
+      <c r="AM3">
+        <v>0.246</v>
+      </c>
+      <c r="AN3">
+        <v>6.571428571428571</v>
+      </c>
+      <c r="AO3">
+        <v>0.07723577235772358</v>
+      </c>
+      <c r="AP3">
+        <v>6.321714285714286</v>
+      </c>
+      <c r="AQ3">
+        <v>0.07723577235772358</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ktima Kostas Lazaridis S.A. (ATSE:KTILA)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ATSE:KTILA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Beverage (Alcoholic)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.07723577235772321</v>
+      </c>
+      <c r="F2">
+        <v>4.72849257581225</v>
+      </c>
+      <c r="G2">
+        <v>6.57142857142857</v>
+      </c>
+      <c r="H2">
+        <v>4.2</v>
+      </c>
+      <c r="I2">
+        <v>0.23469387755102</v>
+      </c>
+      <c r="J2">
+        <v>0.15</v>
+      </c>
+      <c r="K2">
+        <v>37.5</v>
+      </c>
+      <c r="L2">
+        <v>45.5860319105745</v>
+      </c>
+      <c r="M2">
+        <v>48.563</v>
+      </c>
+      <c r="N2">
+        <v>52.4990319105745</v>
+      </c>
+      <c r="O2">
+        <v>11.5</v>
+      </c>
+      <c r="P2">
+        <v>7.35</v>
+      </c>
+      <c r="Q2">
+        <v>0.098630149042909</v>
+      </c>
+      <c r="R2">
+        <v>0.094144478216665</v>
+      </c>
+      <c r="S2">
+        <v>0.0630220619910736</v>
+      </c>
+      <c r="T2">
+        <v>0.039702</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.109549962405472</v>
+      </c>
+      <c r="X2">
+        <v>0.103751974372547</v>
+      </c>
+      <c r="Y2">
+        <v>0.85640180603723</v>
+      </c>
+      <c r="Z2">
+        <v>0.786219331673187</v>
+      </c>
+      <c r="AA2">
+        <v>11.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.08079751537317134</v>
+      </c>
+      <c r="AC2">
+        <v>0.07723577235772319</v>
+      </c>
+      <c r="AD2">
+        <v>11.5</v>
+      </c>
+      <c r="AE2">
+        <v>0.246</v>
+      </c>
+      <c r="AF2">
+        <v>1.731</v>
+      </c>
+      <c r="AG2">
+        <v>1.75</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>37.5</v>
+      </c>
+      <c r="AK2">
+        <v>0.08261304671092226</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>8.631</v>
+      </c>
+      <c r="AR2">
+        <v>0.246</v>
+      </c>
+      <c r="AS2">
+        <v>11.5</v>
+      </c>
+      <c r="AT2">
+        <v>0.437</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09589325565322131</v>
+      </c>
+      <c r="C2">
+        <v>51.32797643369117</v>
+      </c>
+      <c r="D2">
+        <v>50.89097643369117</v>
+      </c>
+      <c r="E2">
+        <v>-11.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.437</v>
+      </c>
+      <c r="H2">
+        <v>37.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.5</v>
+      </c>
+      <c r="K2">
+        <v>1.731</v>
+      </c>
+      <c r="L2">
+        <v>1.769</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.769</v>
+      </c>
+      <c r="O2">
+        <v>0.38918</v>
+      </c>
+      <c r="P2">
+        <v>1.37982</v>
+      </c>
+      <c r="Q2">
+        <v>3.11082</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09589325565322131</v>
+      </c>
+      <c r="T2">
+        <v>0.6910924838905985</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.034866</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09572831049078422</v>
+      </c>
+      <c r="C3">
+        <v>50.98542891035997</v>
+      </c>
+      <c r="D3">
+        <v>51.03842891035998</v>
+      </c>
+      <c r="E3">
+        <v>-11.01</v>
+      </c>
+      <c r="F3">
+        <v>0.49</v>
+      </c>
+      <c r="G3">
+        <v>0.437</v>
+      </c>
+      <c r="H3">
+        <v>37.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.5</v>
+      </c>
+      <c r="K3">
+        <v>1.731</v>
+      </c>
+      <c r="L3">
+        <v>1.769</v>
+      </c>
+      <c r="M3">
+        <v>0.021903</v>
+      </c>
+      <c r="N3">
+        <v>1.747097</v>
+      </c>
+      <c r="O3">
+        <v>0.38436134</v>
+      </c>
+      <c r="P3">
+        <v>1.36273566</v>
+      </c>
+      <c r="Q3">
+        <v>3.09373566</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09634308130382244</v>
+      </c>
+      <c r="T3">
+        <v>0.6965374549757971</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.034866</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>80.76519198283339</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09556336532834712</v>
+      </c>
+      <c r="C4">
+        <v>50.64373833314448</v>
+      </c>
+      <c r="D4">
+        <v>51.18673833314448</v>
+      </c>
+      <c r="E4">
+        <v>-10.52</v>
+      </c>
+      <c r="F4">
+        <v>0.98</v>
+      </c>
+      <c r="G4">
+        <v>0.437</v>
+      </c>
+      <c r="H4">
+        <v>37.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.5</v>
+      </c>
+      <c r="K4">
+        <v>1.731</v>
+      </c>
+      <c r="L4">
+        <v>1.769</v>
+      </c>
+      <c r="M4">
+        <v>0.043806</v>
+      </c>
+      <c r="N4">
+        <v>1.725194</v>
+      </c>
+      <c r="O4">
+        <v>0.37954268</v>
+      </c>
+      <c r="P4">
+        <v>1.34565132</v>
+      </c>
+      <c r="Q4">
+        <v>3.07665132</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09680208706974197</v>
+      </c>
+      <c r="T4">
+        <v>0.7020935479198774</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.034866</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>40.38259599141669</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09539842016591003</v>
+      </c>
+      <c r="C5">
+        <v>50.30291219425644</v>
+      </c>
+      <c r="D5">
+        <v>51.33591219425644</v>
+      </c>
+      <c r="E5">
+        <v>-10.03</v>
+      </c>
+      <c r="F5">
+        <v>1.47</v>
+      </c>
+      <c r="G5">
+        <v>0.437</v>
+      </c>
+      <c r="H5">
+        <v>37.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.5</v>
+      </c>
+      <c r="K5">
+        <v>1.731</v>
+      </c>
+      <c r="L5">
+        <v>1.769</v>
+      </c>
+      <c r="M5">
+        <v>0.065709</v>
+      </c>
+      <c r="N5">
+        <v>1.703291</v>
+      </c>
+      <c r="O5">
+        <v>0.37472402</v>
+      </c>
+      <c r="P5">
+        <v>1.32856698</v>
+      </c>
+      <c r="Q5">
+        <v>3.05956698</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0972705568720722</v>
+      </c>
+      <c r="T5">
+        <v>0.7077641994813614</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.034866</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>26.92173066094447</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09523347500347296</v>
+      </c>
+      <c r="C6">
+        <v>49.96295807350126</v>
+      </c>
+      <c r="D6">
+        <v>51.48595807350127</v>
+      </c>
+      <c r="E6">
+        <v>-9.539999999999999</v>
+      </c>
+      <c r="F6">
+        <v>1.96</v>
+      </c>
+      <c r="G6">
+        <v>0.437</v>
+      </c>
+      <c r="H6">
+        <v>37.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.5</v>
+      </c>
+      <c r="K6">
+        <v>1.731</v>
+      </c>
+      <c r="L6">
+        <v>1.769</v>
+      </c>
+      <c r="M6">
+        <v>0.08761200000000001</v>
+      </c>
+      <c r="N6">
+        <v>1.681388</v>
+      </c>
+      <c r="O6">
+        <v>0.36990536</v>
+      </c>
+      <c r="P6">
+        <v>1.31148264</v>
+      </c>
+      <c r="Q6">
+        <v>3.04248264</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.097748786461951</v>
+      </c>
+      <c r="T6">
+        <v>0.7135529896170429</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.034866</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>20.19129799570835</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09506852984103588</v>
+      </c>
+      <c r="C7">
+        <v>49.62388363956197</v>
+      </c>
+      <c r="D7">
+        <v>51.63688363956197</v>
+      </c>
+      <c r="E7">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="F7">
+        <v>2.45</v>
+      </c>
+      <c r="G7">
+        <v>0.437</v>
+      </c>
+      <c r="H7">
+        <v>37.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.5</v>
+      </c>
+      <c r="K7">
+        <v>1.731</v>
+      </c>
+      <c r="L7">
+        <v>1.769</v>
+      </c>
+      <c r="M7">
+        <v>0.109515</v>
+      </c>
+      <c r="N7">
+        <v>1.659485</v>
+      </c>
+      <c r="O7">
+        <v>0.3650867</v>
+      </c>
+      <c r="P7">
+        <v>1.2943983</v>
+      </c>
+      <c r="Q7">
+        <v>3.0253983</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09823708404319566</v>
+      </c>
+      <c r="T7">
+        <v>0.7194636490187389</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.034866</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>16.15303839656668</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09490358467859879</v>
+      </c>
+      <c r="C8">
+        <v>49.28569665130562</v>
+      </c>
+      <c r="D8">
+        <v>51.78869665130562</v>
+      </c>
+      <c r="E8">
+        <v>-8.56</v>
+      </c>
+      <c r="F8">
+        <v>2.94</v>
+      </c>
+      <c r="G8">
+        <v>0.437</v>
+      </c>
+      <c r="H8">
+        <v>37.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.5</v>
+      </c>
+      <c r="K8">
+        <v>1.731</v>
+      </c>
+      <c r="L8">
+        <v>1.769</v>
+      </c>
+      <c r="M8">
+        <v>0.131418</v>
+      </c>
+      <c r="N8">
+        <v>1.637582</v>
+      </c>
+      <c r="O8">
+        <v>0.36026804</v>
+      </c>
+      <c r="P8">
+        <v>1.27731396</v>
+      </c>
+      <c r="Q8">
+        <v>3.00831396</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09873577093467956</v>
+      </c>
+      <c r="T8">
+        <v>0.7255000671311091</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.034866</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>13.46086533047223</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.0947986995161617</v>
+      </c>
+      <c r="C9">
+        <v>48.89269650858105</v>
+      </c>
+      <c r="D9">
+        <v>51.88569650858106</v>
+      </c>
+      <c r="E9">
+        <v>-8.07</v>
+      </c>
+      <c r="F9">
+        <v>3.43</v>
+      </c>
+      <c r="G9">
+        <v>0.437</v>
+      </c>
+      <c r="H9">
+        <v>37.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.5</v>
+      </c>
+      <c r="K9">
+        <v>1.731</v>
+      </c>
+      <c r="L9">
+        <v>1.769</v>
+      </c>
+      <c r="M9">
+        <v>0.157094</v>
+      </c>
+      <c r="N9">
+        <v>1.611906</v>
+      </c>
+      <c r="O9">
+        <v>0.35461932</v>
+      </c>
+      <c r="P9">
+        <v>1.25728668</v>
+      </c>
+      <c r="Q9">
+        <v>2.98828668</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09924518227544268</v>
+      </c>
+      <c r="T9">
+        <v>0.7316663006867563</v>
+      </c>
+      <c r="U9">
+        <v>0.0458</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.035724</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.26077380421913</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09477961435372462</v>
+      </c>
+      <c r="C10">
+        <v>48.42038592922925</v>
+      </c>
+      <c r="D10">
+        <v>51.90338592922925</v>
+      </c>
+      <c r="E10">
+        <v>-7.58</v>
+      </c>
+      <c r="F10">
+        <v>3.92</v>
+      </c>
+      <c r="G10">
+        <v>0.437</v>
+      </c>
+      <c r="H10">
+        <v>37.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.5</v>
+      </c>
+      <c r="K10">
+        <v>1.731</v>
+      </c>
+      <c r="L10">
+        <v>1.769</v>
+      </c>
+      <c r="M10">
+        <v>0.18816</v>
+      </c>
+      <c r="N10">
+        <v>1.58084</v>
+      </c>
+      <c r="O10">
+        <v>0.3477847999999999</v>
+      </c>
+      <c r="P10">
+        <v>1.2330552</v>
+      </c>
+      <c r="Q10">
+        <v>2.9640552</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09976566777578762</v>
+      </c>
+      <c r="T10">
+        <v>0.7379665827979608</v>
+      </c>
+      <c r="U10">
+        <v>0.048</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.03744</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>9.4015731292517</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09464040919128754</v>
+      </c>
+      <c r="C11">
+        <v>48.0597764436247</v>
+      </c>
+      <c r="D11">
+        <v>52.0327764436247</v>
+      </c>
+      <c r="E11">
+        <v>-7.09</v>
+      </c>
+      <c r="F11">
+        <v>4.41</v>
+      </c>
+      <c r="G11">
+        <v>0.437</v>
+      </c>
+      <c r="H11">
+        <v>37.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.5</v>
+      </c>
+      <c r="K11">
+        <v>1.731</v>
+      </c>
+      <c r="L11">
+        <v>1.769</v>
+      </c>
+      <c r="M11">
+        <v>0.21168</v>
+      </c>
+      <c r="N11">
+        <v>1.55732</v>
+      </c>
+      <c r="O11">
+        <v>0.3426104</v>
+      </c>
+      <c r="P11">
+        <v>1.2147096</v>
+      </c>
+      <c r="Q11">
+        <v>2.9457096</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1002975925178984</v>
+      </c>
+      <c r="T11">
+        <v>0.7444053326478733</v>
+      </c>
+      <c r="U11">
+        <v>0.048</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.03744</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.356953892668177</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09461820402885043</v>
+      </c>
+      <c r="C12">
+        <v>47.59047571679348</v>
+      </c>
+      <c r="D12">
+        <v>52.05347571679349</v>
+      </c>
+      <c r="E12">
+        <v>-6.6</v>
+      </c>
+      <c r="F12">
+        <v>4.9</v>
+      </c>
+      <c r="G12">
+        <v>0.437</v>
+      </c>
+      <c r="H12">
+        <v>37.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.5</v>
+      </c>
+      <c r="K12">
+        <v>1.731</v>
+      </c>
+      <c r="L12">
+        <v>1.769</v>
+      </c>
+      <c r="M12">
+        <v>0.24255</v>
+      </c>
+      <c r="N12">
+        <v>1.52645</v>
+      </c>
+      <c r="O12">
+        <v>0.335819</v>
+      </c>
+      <c r="P12">
+        <v>1.190631</v>
+      </c>
+      <c r="Q12">
+        <v>2.921631</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1008413378098338</v>
+      </c>
+      <c r="T12">
+        <v>0.7509871658277837</v>
+      </c>
+      <c r="U12">
+        <v>0.0495</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.293341579055864</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09449069886641337</v>
+      </c>
+      <c r="C13">
+        <v>47.21965337144286</v>
+      </c>
+      <c r="D13">
+        <v>52.17265337144286</v>
+      </c>
+      <c r="E13">
+        <v>-6.11</v>
+      </c>
+      <c r="F13">
+        <v>5.39</v>
+      </c>
+      <c r="G13">
+        <v>0.437</v>
+      </c>
+      <c r="H13">
+        <v>37.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.5</v>
+      </c>
+      <c r="K13">
+        <v>1.731</v>
+      </c>
+      <c r="L13">
+        <v>1.769</v>
+      </c>
+      <c r="M13">
+        <v>0.266805</v>
+      </c>
+      <c r="N13">
+        <v>1.502195</v>
+      </c>
+      <c r="O13">
+        <v>0.3304829</v>
+      </c>
+      <c r="P13">
+        <v>1.1717121</v>
+      </c>
+      <c r="Q13">
+        <v>2.9027121</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1013973020970937</v>
+      </c>
+      <c r="T13">
+        <v>0.7577169053712878</v>
+      </c>
+      <c r="U13">
+        <v>0.0495</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.630310526414422</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09449423370397628</v>
+      </c>
+      <c r="C14">
+        <v>46.72634204381288</v>
+      </c>
+      <c r="D14">
+        <v>52.16934204381289</v>
+      </c>
+      <c r="E14">
+        <v>-5.62</v>
+      </c>
+      <c r="F14">
+        <v>5.88</v>
+      </c>
+      <c r="G14">
+        <v>0.437</v>
+      </c>
+      <c r="H14">
+        <v>37.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.5</v>
+      </c>
+      <c r="K14">
+        <v>1.731</v>
+      </c>
+      <c r="L14">
+        <v>1.769</v>
+      </c>
+      <c r="M14">
+        <v>0.299292</v>
+      </c>
+      <c r="N14">
+        <v>1.469708</v>
+      </c>
+      <c r="O14">
+        <v>0.32333576</v>
+      </c>
+      <c r="P14">
+        <v>1.14637224</v>
+      </c>
+      <c r="Q14">
+        <v>2.87737224</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1019659019363367</v>
+      </c>
+      <c r="T14">
+        <v>0.7645995935407804</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.039702</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.910615719765312</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09437764854153917</v>
+      </c>
+      <c r="C15">
+        <v>46.34577760605818</v>
+      </c>
+      <c r="D15">
+        <v>52.27877760605818</v>
+      </c>
+      <c r="E15">
+        <v>-5.13</v>
+      </c>
+      <c r="F15">
+        <v>6.37</v>
+      </c>
+      <c r="G15">
+        <v>0.437</v>
+      </c>
+      <c r="H15">
+        <v>37.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.5</v>
+      </c>
+      <c r="K15">
+        <v>1.731</v>
+      </c>
+      <c r="L15">
+        <v>1.769</v>
+      </c>
+      <c r="M15">
+        <v>0.324233</v>
+      </c>
+      <c r="N15">
+        <v>1.444767</v>
+      </c>
+      <c r="O15">
+        <v>0.31784874</v>
+      </c>
+      <c r="P15">
+        <v>1.12691826</v>
+      </c>
+      <c r="Q15">
+        <v>2.85791826</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1025475730362519</v>
+      </c>
+      <c r="T15">
+        <v>0.7716405044268131</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.039702</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.455952972091058</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09426106337910209</v>
+      </c>
+      <c r="C16">
+        <v>45.96567325911396</v>
+      </c>
+      <c r="D16">
+        <v>52.38867325911396</v>
+      </c>
+      <c r="E16">
+        <v>-4.64</v>
+      </c>
+      <c r="F16">
+        <v>6.86</v>
+      </c>
+      <c r="G16">
+        <v>0.437</v>
+      </c>
+      <c r="H16">
+        <v>37.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.5</v>
+      </c>
+      <c r="K16">
+        <v>1.731</v>
+      </c>
+      <c r="L16">
+        <v>1.769</v>
+      </c>
+      <c r="M16">
+        <v>0.349174</v>
+      </c>
+      <c r="N16">
+        <v>1.419826</v>
+      </c>
+      <c r="O16">
+        <v>0.31236172</v>
+      </c>
+      <c r="P16">
+        <v>1.10746428</v>
+      </c>
+      <c r="Q16">
+        <v>2.83846428</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1031427713710489</v>
+      </c>
+      <c r="T16">
+        <v>0.7788451574264745</v>
+      </c>
+      <c r="U16">
+        <v>0.0509</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.039702</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.066242045513124</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.094144478216665</v>
+      </c>
+      <c r="C17">
+        <v>45.58603191057449</v>
+      </c>
+      <c r="D17">
+        <v>52.49903191057449</v>
+      </c>
+      <c r="E17">
+        <v>-4.15</v>
+      </c>
+      <c r="F17">
+        <v>7.35</v>
+      </c>
+      <c r="G17">
+        <v>0.437</v>
+      </c>
+      <c r="H17">
+        <v>37.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.5</v>
+      </c>
+      <c r="K17">
+        <v>1.731</v>
+      </c>
+      <c r="L17">
+        <v>1.769</v>
+      </c>
+      <c r="M17">
+        <v>0.374115</v>
+      </c>
+      <c r="N17">
+        <v>1.394885</v>
+      </c>
+      <c r="O17">
+        <v>0.3068747</v>
+      </c>
+      <c r="P17">
+        <v>1.0880103</v>
+      </c>
+      <c r="Q17">
+        <v>2.8190103</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1037519743725471</v>
+      </c>
+      <c r="T17">
+        <v>0.7862193316731868</v>
+      </c>
+      <c r="U17">
+        <v>0.0509</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.039702</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.72849257581225</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.0943523730542279</v>
+      </c>
+      <c r="C18">
+        <v>44.89956365708323</v>
+      </c>
+      <c r="D18">
+        <v>52.30256365708323</v>
+      </c>
+      <c r="E18">
+        <v>-3.66</v>
+      </c>
+      <c r="F18">
+        <v>7.84</v>
+      </c>
+      <c r="G18">
+        <v>0.437</v>
+      </c>
+      <c r="H18">
+        <v>37.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.5</v>
+      </c>
+      <c r="K18">
+        <v>1.731</v>
+      </c>
+      <c r="L18">
+        <v>1.769</v>
+      </c>
+      <c r="M18">
+        <v>0.41944</v>
+      </c>
+      <c r="N18">
+        <v>1.34956</v>
+      </c>
+      <c r="O18">
+        <v>0.2969032</v>
+      </c>
+      <c r="P18">
+        <v>1.0526568</v>
+      </c>
+      <c r="Q18">
+        <v>2.7836568</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1043756822074142</v>
+      </c>
+      <c r="T18">
+        <v>0.7937690814972017</v>
+      </c>
+      <c r="U18">
+        <v>0.0535</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.04173</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.217528132748426</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09461408789179084</v>
+      </c>
+      <c r="C19">
+        <v>44.16431451894133</v>
+      </c>
+      <c r="D19">
+        <v>52.05731451894133</v>
+      </c>
+      <c r="E19">
+        <v>-3.17</v>
+      </c>
+      <c r="F19">
+        <v>8.33</v>
+      </c>
+      <c r="G19">
+        <v>0.437</v>
+      </c>
+      <c r="H19">
+        <v>37.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.5</v>
+      </c>
+      <c r="K19">
+        <v>1.731</v>
+      </c>
+      <c r="L19">
+        <v>1.769</v>
+      </c>
+      <c r="M19">
+        <v>0.468146</v>
+      </c>
+      <c r="N19">
+        <v>1.300854</v>
+      </c>
+      <c r="O19">
+        <v>0.28618788</v>
+      </c>
+      <c r="P19">
+        <v>1.01466612</v>
+      </c>
+      <c r="Q19">
+        <v>2.74566612</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1050144191467359</v>
+      </c>
+      <c r="T19">
+        <v>0.8015007530037231</v>
+      </c>
+      <c r="U19">
+        <v>0.0562</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.043836</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.778735693565682</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09453884272935374</v>
+      </c>
+      <c r="C20">
+        <v>43.74458976857355</v>
+      </c>
+      <c r="D20">
+        <v>52.12758976857355</v>
+      </c>
+      <c r="E20">
+        <v>-2.68</v>
+      </c>
+      <c r="F20">
+        <v>8.82</v>
+      </c>
+      <c r="G20">
+        <v>0.437</v>
+      </c>
+      <c r="H20">
+        <v>37.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.5</v>
+      </c>
+      <c r="K20">
+        <v>1.731</v>
+      </c>
+      <c r="L20">
+        <v>1.769</v>
+      </c>
+      <c r="M20">
+        <v>0.495684</v>
+      </c>
+      <c r="N20">
+        <v>1.273316</v>
+      </c>
+      <c r="O20">
+        <v>0.28012952</v>
+      </c>
+      <c r="P20">
+        <v>0.9931864799999999</v>
+      </c>
+      <c r="Q20">
+        <v>2.72418648</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1056687350357972</v>
+      </c>
+      <c r="T20">
+        <v>0.809421001864062</v>
+      </c>
+      <c r="U20">
+        <v>0.0562</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.043836</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.568805932812033</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09516013756691666</v>
+      </c>
+      <c r="C21">
+        <v>42.67995308711834</v>
+      </c>
+      <c r="D21">
+        <v>51.55295308711835</v>
+      </c>
+      <c r="E21">
+        <v>-2.19</v>
+      </c>
+      <c r="F21">
+        <v>9.31</v>
+      </c>
+      <c r="G21">
+        <v>0.437</v>
+      </c>
+      <c r="H21">
+        <v>37.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.5</v>
+      </c>
+      <c r="K21">
+        <v>1.731</v>
+      </c>
+      <c r="L21">
+        <v>1.769</v>
+      </c>
+      <c r="M21">
+        <v>0.566979</v>
+      </c>
+      <c r="N21">
+        <v>1.202021</v>
+      </c>
+      <c r="O21">
+        <v>0.26444462</v>
+      </c>
+      <c r="P21">
+        <v>0.9375763799999999</v>
+      </c>
+      <c r="Q21">
+        <v>2.66857638</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1063392068727366</v>
+      </c>
+      <c r="T21">
+        <v>0.8175368124246561</v>
+      </c>
+      <c r="U21">
+        <v>0.0609</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.047502</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>3.120045010485397</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09657235240447959</v>
+      </c>
+      <c r="C22">
+        <v>40.92976820213917</v>
+      </c>
+      <c r="D22">
+        <v>50.29276820213918</v>
+      </c>
+      <c r="E22">
+        <v>-1.699999999999999</v>
+      </c>
+      <c r="F22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.437</v>
+      </c>
+      <c r="H22">
+        <v>37.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.5</v>
+      </c>
+      <c r="K22">
+        <v>1.731</v>
+      </c>
+      <c r="L22">
+        <v>1.769</v>
+      </c>
+      <c r="M22">
+        <v>0.68796</v>
+      </c>
+      <c r="N22">
+        <v>1.08104</v>
+      </c>
+      <c r="O22">
+        <v>0.2378288</v>
+      </c>
+      <c r="P22">
+        <v>0.8432111999999998</v>
+      </c>
+      <c r="Q22">
+        <v>2.5742112</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1070264405055995</v>
+      </c>
+      <c r="T22">
+        <v>0.8258555182492653</v>
+      </c>
+      <c r="U22">
+        <v>0.0702</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.054756</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.571370428513285</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09737616724204248</v>
+      </c>
+      <c r="C23">
+        <v>39.74962278624083</v>
+      </c>
+      <c r="D23">
+        <v>49.60262278624084</v>
+      </c>
+      <c r="E23">
+        <v>-1.210000000000001</v>
+      </c>
+      <c r="F23">
+        <v>10.29</v>
+      </c>
+      <c r="G23">
+        <v>0.437</v>
+      </c>
+      <c r="H23">
+        <v>37.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.5</v>
+      </c>
+      <c r="K23">
+        <v>1.731</v>
+      </c>
+      <c r="L23">
+        <v>1.769</v>
+      </c>
+      <c r="M23">
+        <v>0.7707209999999999</v>
+      </c>
+      <c r="N23">
+        <v>0.998279</v>
+      </c>
+      <c r="O23">
+        <v>0.21962138</v>
+      </c>
+      <c r="P23">
+        <v>0.7786576200000001</v>
+      </c>
+      <c r="Q23">
+        <v>2.50965762</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1077310724582816</v>
+      </c>
+      <c r="T23">
+        <v>0.8343848242213326</v>
+      </c>
+      <c r="U23">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.295253405577375</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.0974467820796054</v>
+      </c>
+      <c r="C24">
+        <v>39.19989775058601</v>
+      </c>
+      <c r="D24">
+        <v>49.54289775058601</v>
+      </c>
+      <c r="E24">
+        <v>-0.7200000000000006</v>
+      </c>
+      <c r="F24">
+        <v>10.78</v>
+      </c>
+      <c r="G24">
+        <v>0.437</v>
+      </c>
+      <c r="H24">
+        <v>37.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.5</v>
+      </c>
+      <c r="K24">
+        <v>1.731</v>
+      </c>
+      <c r="L24">
+        <v>1.769</v>
+      </c>
+      <c r="M24">
+        <v>0.8074219999999999</v>
+      </c>
+      <c r="N24">
+        <v>0.961578</v>
+      </c>
+      <c r="O24">
+        <v>0.21154716</v>
+      </c>
+      <c r="P24">
+        <v>0.75003084</v>
+      </c>
+      <c r="Q24">
+        <v>2.48103084</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.10845377189693</v>
+      </c>
+      <c r="T24">
+        <v>0.8431328303465302</v>
+      </c>
+      <c r="U24">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.190923705323858</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09751739691716832</v>
+      </c>
+      <c r="C25">
+        <v>38.65031636822348</v>
+      </c>
+      <c r="D25">
+        <v>49.48331636822348</v>
+      </c>
+      <c r="E25">
+        <v>-0.2299999999999986</v>
+      </c>
+      <c r="F25">
+        <v>11.27</v>
+      </c>
+      <c r="G25">
+        <v>0.437</v>
+      </c>
+      <c r="H25">
+        <v>37.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.5</v>
+      </c>
+      <c r="K25">
+        <v>1.731</v>
+      </c>
+      <c r="L25">
+        <v>1.769</v>
+      </c>
+      <c r="M25">
+        <v>0.8441230000000001</v>
+      </c>
+      <c r="N25">
+        <v>0.9248769999999998</v>
+      </c>
+      <c r="O25">
+        <v>0.20347294</v>
+      </c>
+      <c r="P25">
+        <v>0.7214040599999999</v>
+      </c>
+      <c r="Q25">
+        <v>2.45240406</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1091952427495692</v>
+      </c>
+      <c r="T25">
+        <v>0.8521080574100445</v>
+      </c>
+      <c r="U25">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.095666152918473</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09758801175473122</v>
+      </c>
+      <c r="C26">
+        <v>38.10087812149396</v>
+      </c>
+      <c r="D26">
+        <v>49.42387812149396</v>
+      </c>
+      <c r="E26">
+        <v>0.2599999999999998</v>
+      </c>
+      <c r="F26">
+        <v>11.76</v>
+      </c>
+      <c r="G26">
+        <v>0.437</v>
+      </c>
+      <c r="H26">
+        <v>37.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.5</v>
+      </c>
+      <c r="K26">
+        <v>1.731</v>
+      </c>
+      <c r="L26">
+        <v>1.769</v>
+      </c>
+      <c r="M26">
+        <v>0.8808239999999999</v>
+      </c>
+      <c r="N26">
+        <v>0.888176</v>
+      </c>
+      <c r="O26">
+        <v>0.19539872</v>
+      </c>
+      <c r="P26">
+        <v>0.6927772799999999</v>
+      </c>
+      <c r="Q26">
+        <v>2.42377728</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1099562259930674</v>
+      </c>
+      <c r="T26">
+        <v>0.8613194746594407</v>
+      </c>
+      <c r="U26">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.008346729880203</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1008371265922941</v>
+      </c>
+      <c r="C27">
+        <v>35.02236597473065</v>
+      </c>
+      <c r="D27">
+        <v>46.83536597473065</v>
+      </c>
+      <c r="E27">
+        <v>0.75</v>
+      </c>
+      <c r="F27">
+        <v>12.25</v>
+      </c>
+      <c r="G27">
+        <v>0.437</v>
+      </c>
+      <c r="H27">
+        <v>37.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.5</v>
+      </c>
+      <c r="K27">
+        <v>1.731</v>
+      </c>
+      <c r="L27">
+        <v>1.769</v>
+      </c>
+      <c r="M27">
+        <v>1.1172</v>
+      </c>
+      <c r="N27">
+        <v>0.6517999999999999</v>
+      </c>
+      <c r="O27">
+        <v>0.143396</v>
+      </c>
+      <c r="P27">
+        <v>0.508404</v>
+      </c>
+      <c r="Q27">
+        <v>2.239404</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1107375021230588</v>
+      </c>
+      <c r="T27">
+        <v>0.8707765297021541</v>
+      </c>
+      <c r="U27">
+        <v>0.0912</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.071136</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>1.583422842821339</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1010348814298571</v>
+      </c>
+      <c r="C28">
+        <v>34.38354396402315</v>
+      </c>
+      <c r="D28">
+        <v>46.68654396402316</v>
+      </c>
+      <c r="E28">
+        <v>1.24</v>
+      </c>
+      <c r="F28">
+        <v>12.74</v>
+      </c>
+      <c r="G28">
+        <v>0.437</v>
+      </c>
+      <c r="H28">
+        <v>37.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.5</v>
+      </c>
+      <c r="K28">
+        <v>1.731</v>
+      </c>
+      <c r="L28">
+        <v>1.769</v>
+      </c>
+      <c r="M28">
+        <v>1.161888</v>
+      </c>
+      <c r="N28">
+        <v>0.6071119999999999</v>
+      </c>
+      <c r="O28">
+        <v>0.13356464</v>
+      </c>
+      <c r="P28">
+        <v>0.4735473599999999</v>
+      </c>
+      <c r="Q28">
+        <v>2.20454736</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1115398938241312</v>
+      </c>
+      <c r="T28">
+        <v>0.8804891808271031</v>
+      </c>
+      <c r="U28">
+        <v>0.0912</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.071136</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>1.522521964251287</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.116861147222132</v>
+      </c>
+      <c r="C29">
+        <v>24.42822504429463</v>
+      </c>
+      <c r="D29">
+        <v>37.22122504429463</v>
+      </c>
+      <c r="E29">
+        <v>1.73</v>
+      </c>
+      <c r="F29">
+        <v>13.23</v>
+      </c>
+      <c r="G29">
+        <v>0.437</v>
+      </c>
+      <c r="H29">
+        <v>37.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.5</v>
+      </c>
+      <c r="K29">
+        <v>1.731</v>
+      </c>
+      <c r="L29">
+        <v>1.769</v>
+      </c>
+      <c r="M29">
+        <v>2.071818</v>
+      </c>
+      <c r="N29">
+        <v>-0.3028180000000005</v>
+      </c>
+      <c r="O29">
+        <v>-0.0666199600000001</v>
+      </c>
+      <c r="P29">
+        <v>-0.2361980400000004</v>
+      </c>
+      <c r="Q29">
+        <v>1.49480196</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1130432824681148</v>
+      </c>
+      <c r="T29">
+        <v>0.8986871374917971</v>
+      </c>
+      <c r="U29">
+        <v>0.1566</v>
+      </c>
+      <c r="V29">
+        <v>0.1878446851991825</v>
+      </c>
+      <c r="W29">
+        <v>0.127183522297808</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.8538394781781024</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.118039147222132</v>
+      </c>
+      <c r="C30">
+        <v>23.38487982745044</v>
+      </c>
+      <c r="D30">
+        <v>36.66787982745044</v>
+      </c>
+      <c r="E30">
+        <v>2.220000000000001</v>
+      </c>
+      <c r="F30">
+        <v>13.72</v>
+      </c>
+      <c r="G30">
+        <v>0.437</v>
+      </c>
+      <c r="H30">
+        <v>37.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.5</v>
+      </c>
+      <c r="K30">
+        <v>1.731</v>
+      </c>
+      <c r="L30">
+        <v>1.769</v>
+      </c>
+      <c r="M30">
+        <v>2.148552</v>
+      </c>
+      <c r="N30">
+        <v>-0.3795520000000006</v>
+      </c>
+      <c r="O30">
+        <v>-0.08350144000000012</v>
+      </c>
+      <c r="P30">
+        <v>-0.2960505600000004</v>
+      </c>
+      <c r="Q30">
+        <v>1.43494944</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1140744391690609</v>
+      </c>
+      <c r="T30">
+        <v>0.9111689032902943</v>
+      </c>
+      <c r="U30">
+        <v>0.1566</v>
+      </c>
+      <c r="V30">
+        <v>0.1811359464420688</v>
+      </c>
+      <c r="W30">
+        <v>0.128234110787172</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.8233452111003129</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1350790620850064</v>
+      </c>
+      <c r="C31">
+        <v>16.40522842317937</v>
+      </c>
+      <c r="D31">
+        <v>30.17822842317937</v>
+      </c>
+      <c r="E31">
+        <v>2.709999999999999</v>
+      </c>
+      <c r="F31">
+        <v>14.21</v>
+      </c>
+      <c r="G31">
+        <v>0.437</v>
+      </c>
+      <c r="H31">
+        <v>37.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.5</v>
+      </c>
+      <c r="K31">
+        <v>1.731</v>
+      </c>
+      <c r="L31">
+        <v>1.769</v>
+      </c>
+      <c r="M31">
+        <v>2.967048</v>
+      </c>
+      <c r="N31">
+        <v>-1.198048</v>
+      </c>
+      <c r="O31">
+        <v>-0.2635705600000001</v>
+      </c>
+      <c r="P31">
+        <v>-0.9344774400000002</v>
+      </c>
+      <c r="Q31">
+        <v>0.7965225599999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1161542409360538</v>
+      </c>
+      <c r="T31">
+        <v>0.936344124999167</v>
+      </c>
+      <c r="U31">
+        <v>0.2088</v>
+      </c>
+      <c r="V31">
+        <v>0.1311674094925326</v>
+      </c>
+      <c r="W31">
+        <v>0.1814122448979592</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5962154976933302</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1367790620850064</v>
+      </c>
+      <c r="C32">
+        <v>15.39161667156968</v>
+      </c>
+      <c r="D32">
+        <v>29.65461667156968</v>
+      </c>
+      <c r="E32">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="F32">
+        <v>14.7</v>
+      </c>
+      <c r="G32">
+        <v>0.437</v>
+      </c>
+      <c r="H32">
+        <v>37.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.5</v>
+      </c>
+      <c r="K32">
+        <v>1.731</v>
+      </c>
+      <c r="L32">
+        <v>1.769</v>
+      </c>
+      <c r="M32">
+        <v>3.06936</v>
+      </c>
+      <c r="N32">
+        <v>-1.30036</v>
+      </c>
+      <c r="O32">
+        <v>-0.2860792</v>
+      </c>
+      <c r="P32">
+        <v>-1.0142808</v>
+      </c>
+      <c r="Q32">
+        <v>0.7167192</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1172593015208546</v>
+      </c>
+      <c r="T32">
+        <v>0.9497204696420122</v>
+      </c>
+      <c r="U32">
+        <v>0.2088</v>
+      </c>
+      <c r="V32">
+        <v>0.1267951625094482</v>
+      </c>
+      <c r="W32">
+        <v>0.1823251700680272</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5763416477702192</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1384790620850064</v>
+      </c>
+      <c r="C33">
+        <v>14.39586503940969</v>
+      </c>
+      <c r="D33">
+        <v>29.14886503940969</v>
+      </c>
+      <c r="E33">
+        <v>3.69</v>
+      </c>
+      <c r="F33">
+        <v>15.19</v>
+      </c>
+      <c r="G33">
+        <v>0.437</v>
+      </c>
+      <c r="H33">
+        <v>37.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.5</v>
+      </c>
+      <c r="K33">
+        <v>1.731</v>
+      </c>
+      <c r="L33">
+        <v>1.769</v>
+      </c>
+      <c r="M33">
+        <v>3.171672</v>
+      </c>
+      <c r="N33">
+        <v>-1.402672</v>
+      </c>
+      <c r="O33">
+        <v>-0.3085878400000001</v>
+      </c>
+      <c r="P33">
+        <v>-1.09408416</v>
+      </c>
+      <c r="Q33">
+        <v>0.6369158400000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1183963928472438</v>
+      </c>
+      <c r="T33">
+        <v>0.9634845344194326</v>
+      </c>
+      <c r="U33">
+        <v>0.2088</v>
+      </c>
+      <c r="V33">
+        <v>0.1227049959768854</v>
+      </c>
+      <c r="W33">
+        <v>0.1831791968400263</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5577499817131153</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1401790620850064</v>
+      </c>
+      <c r="C34">
+        <v>13.41707505114321</v>
+      </c>
+      <c r="D34">
+        <v>28.66007505114321</v>
+      </c>
+      <c r="E34">
+        <v>4.18</v>
+      </c>
+      <c r="F34">
+        <v>15.68</v>
+      </c>
+      <c r="G34">
+        <v>0.437</v>
+      </c>
+      <c r="H34">
+        <v>37.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.5</v>
+      </c>
+      <c r="K34">
+        <v>1.731</v>
+      </c>
+      <c r="L34">
+        <v>1.769</v>
+      </c>
+      <c r="M34">
+        <v>3.273984</v>
+      </c>
+      <c r="N34">
+        <v>-1.504984</v>
+      </c>
+      <c r="O34">
+        <v>-0.33109648</v>
+      </c>
+      <c r="P34">
+        <v>-1.17388752</v>
+      </c>
+      <c r="Q34">
+        <v>0.55711248</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1195669280361738</v>
+      </c>
+      <c r="T34">
+        <v>0.9776534246314832</v>
+      </c>
+      <c r="U34">
+        <v>0.2088</v>
+      </c>
+      <c r="V34">
+        <v>0.1188704648526077</v>
+      </c>
+      <c r="W34">
+        <v>0.1839798469387755</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.5403202947845804</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1418790620850064</v>
+      </c>
+      <c r="C35">
+        <v>12.45440750255062</v>
+      </c>
+      <c r="D35">
+        <v>28.18740750255062</v>
+      </c>
+      <c r="E35">
+        <v>4.670000000000002</v>
+      </c>
+      <c r="F35">
+        <v>16.17</v>
+      </c>
+      <c r="G35">
+        <v>0.437</v>
+      </c>
+      <c r="H35">
+        <v>37.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.5</v>
+      </c>
+      <c r="K35">
+        <v>1.731</v>
+      </c>
+      <c r="L35">
+        <v>1.769</v>
+      </c>
+      <c r="M35">
+        <v>3.376296</v>
+      </c>
+      <c r="N35">
+        <v>-1.607296000000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.3536051200000001</v>
+      </c>
+      <c r="P35">
+        <v>-1.25369088</v>
+      </c>
+      <c r="Q35">
+        <v>0.4773091199999997</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1207724045740272</v>
+      </c>
+      <c r="T35">
+        <v>0.9922452667901621</v>
+      </c>
+      <c r="U35">
+        <v>0.2088</v>
+      </c>
+      <c r="V35">
+        <v>0.1152683295540438</v>
+      </c>
+      <c r="W35">
+        <v>0.1847319727891157</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5239469525183811</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1435790620850064</v>
+      </c>
+      <c r="C36">
+        <v>11.50707765247562</v>
+      </c>
+      <c r="D36">
+        <v>27.73007765247562</v>
+      </c>
+      <c r="E36">
+        <v>5.16</v>
+      </c>
+      <c r="F36">
+        <v>16.66</v>
+      </c>
+      <c r="G36">
+        <v>0.437</v>
+      </c>
+      <c r="H36">
+        <v>37.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.5</v>
+      </c>
+      <c r="K36">
+        <v>1.731</v>
+      </c>
+      <c r="L36">
+        <v>1.769</v>
+      </c>
+      <c r="M36">
+        <v>3.478608</v>
+      </c>
+      <c r="N36">
+        <v>-1.709608</v>
+      </c>
+      <c r="O36">
+        <v>-0.3761137600000001</v>
+      </c>
+      <c r="P36">
+        <v>-1.33349424</v>
+      </c>
+      <c r="Q36">
+        <v>0.3975057599999998</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1220144107039367</v>
+      </c>
+      <c r="T36">
+        <v>1.007279285983952</v>
+      </c>
+      <c r="U36">
+        <v>0.2088</v>
+      </c>
+      <c r="V36">
+        <v>0.1118780845671602</v>
+      </c>
+      <c r="W36">
+        <v>0.185439855942377</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5085367480325462</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.156051894319758</v>
+      </c>
+      <c r="C37">
+        <v>8.067252334747831</v>
+      </c>
+      <c r="D37">
+        <v>24.78025233474783</v>
+      </c>
+      <c r="E37">
+        <v>5.650000000000002</v>
+      </c>
+      <c r="F37">
+        <v>17.15</v>
+      </c>
+      <c r="G37">
+        <v>0.437</v>
+      </c>
+      <c r="H37">
+        <v>37.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.5</v>
+      </c>
+      <c r="K37">
+        <v>1.731</v>
+      </c>
+      <c r="L37">
+        <v>1.769</v>
+      </c>
+      <c r="M37">
+        <v>4.095420000000001</v>
+      </c>
+      <c r="N37">
+        <v>-2.326420000000001</v>
+      </c>
+      <c r="O37">
+        <v>-0.5118124000000002</v>
+      </c>
+      <c r="P37">
+        <v>-1.8146076</v>
+      </c>
+      <c r="Q37">
+        <v>-0.08360760000000034</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1237143743066921</v>
+      </c>
+      <c r="T37">
+        <v>1.027856708926649</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.09502810456558788</v>
+      </c>
+      <c r="W37">
+        <v>0.2161072886297376</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.4319459298435813</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.158051894319758</v>
+      </c>
+      <c r="C38">
+        <v>7.161657220286962</v>
+      </c>
+      <c r="D38">
+        <v>24.36465722028696</v>
+      </c>
+      <c r="E38">
+        <v>6.140000000000001</v>
+      </c>
+      <c r="F38">
+        <v>17.64</v>
+      </c>
+      <c r="G38">
+        <v>0.437</v>
+      </c>
+      <c r="H38">
+        <v>37.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.5</v>
+      </c>
+      <c r="K38">
+        <v>1.731</v>
+      </c>
+      <c r="L38">
+        <v>1.769</v>
+      </c>
+      <c r="M38">
+        <v>4.212432000000001</v>
+      </c>
+      <c r="N38">
+        <v>-2.443432</v>
+      </c>
+      <c r="O38">
+        <v>-0.5375550400000001</v>
+      </c>
+      <c r="P38">
+        <v>-1.905876960000001</v>
+      </c>
+      <c r="Q38">
+        <v>-0.1748769600000004</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1250411614052341</v>
+      </c>
+      <c r="T38">
+        <v>1.043916970003628</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.09238843499432156</v>
+      </c>
+      <c r="W38">
+        <v>0.216737641723356</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.4199474317923707</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.160051894319758</v>
+      </c>
+      <c r="C39">
+        <v>6.269772245920564</v>
+      </c>
+      <c r="D39">
+        <v>23.96277224592056</v>
+      </c>
+      <c r="E39">
+        <v>6.629999999999999</v>
+      </c>
+      <c r="F39">
+        <v>18.13</v>
+      </c>
+      <c r="G39">
+        <v>0.437</v>
+      </c>
+      <c r="H39">
+        <v>37.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.5</v>
+      </c>
+      <c r="K39">
+        <v>1.731</v>
+      </c>
+      <c r="L39">
+        <v>1.769</v>
+      </c>
+      <c r="M39">
+        <v>4.329444</v>
+      </c>
+      <c r="N39">
+        <v>-2.560443999999999</v>
+      </c>
+      <c r="O39">
+        <v>-0.5632976799999999</v>
+      </c>
+      <c r="P39">
+        <v>-1.99714632</v>
+      </c>
+      <c r="Q39">
+        <v>-0.2661463199999996</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1264100687291267</v>
+      </c>
+      <c r="T39">
+        <v>1.060487080638606</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.08989145026474531</v>
+      </c>
+      <c r="W39">
+        <v>0.2173339216767788</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.4085975012033879</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.162051894319758</v>
+      </c>
+      <c r="C40">
+        <v>5.390929991151591</v>
+      </c>
+      <c r="D40">
+        <v>23.57392999115159</v>
+      </c>
+      <c r="E40">
+        <v>7.120000000000001</v>
+      </c>
+      <c r="F40">
+        <v>18.62</v>
+      </c>
+      <c r="G40">
+        <v>0.437</v>
+      </c>
+      <c r="H40">
+        <v>37.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.5</v>
+      </c>
+      <c r="K40">
+        <v>1.731</v>
+      </c>
+      <c r="L40">
+        <v>1.769</v>
+      </c>
+      <c r="M40">
+        <v>4.446456</v>
+      </c>
+      <c r="N40">
+        <v>-2.677456</v>
+      </c>
+      <c r="O40">
+        <v>-0.5890403200000001</v>
+      </c>
+      <c r="P40">
+        <v>-2.08841568</v>
+      </c>
+      <c r="Q40">
+        <v>-0.3574156800000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1278231343537901</v>
+      </c>
+      <c r="T40">
+        <v>1.077591710971487</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.08752588578409411</v>
+      </c>
+      <c r="W40">
+        <v>0.2178988184747583</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.397844935382246</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.164051894319758</v>
+      </c>
+      <c r="C41">
+        <v>4.524505664490803</v>
+      </c>
+      <c r="D41">
+        <v>23.1975056644908</v>
+      </c>
+      <c r="E41">
+        <v>7.609999999999999</v>
+      </c>
+      <c r="F41">
+        <v>19.11</v>
+      </c>
+      <c r="G41">
+        <v>0.437</v>
+      </c>
+      <c r="H41">
+        <v>37.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.5</v>
+      </c>
+      <c r="K41">
+        <v>1.731</v>
+      </c>
+      <c r="L41">
+        <v>1.769</v>
+      </c>
+      <c r="M41">
+        <v>4.563468</v>
+      </c>
+      <c r="N41">
+        <v>-2.794468</v>
+      </c>
+      <c r="O41">
+        <v>-0.61478296</v>
+      </c>
+      <c r="P41">
+        <v>-2.17968504</v>
+      </c>
+      <c r="Q41">
+        <v>-0.4486850400000002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1292825299989342</v>
+      </c>
+      <c r="T41">
+        <v>1.095257148856265</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.08528163230245067</v>
+      </c>
+      <c r="W41">
+        <v>0.2184347462061748</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3876437831929577</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.166051894319758</v>
+      </c>
+      <c r="C42">
+        <v>3.669913753486316</v>
+      </c>
+      <c r="D42">
+        <v>22.83291375348632</v>
+      </c>
+      <c r="E42">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="F42">
+        <v>19.6</v>
+      </c>
+      <c r="G42">
+        <v>0.437</v>
+      </c>
+      <c r="H42">
+        <v>37.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.5</v>
+      </c>
+      <c r="K42">
+        <v>1.731</v>
+      </c>
+      <c r="L42">
+        <v>1.769</v>
+      </c>
+      <c r="M42">
+        <v>4.68048</v>
+      </c>
+      <c r="N42">
+        <v>-2.91148</v>
+      </c>
+      <c r="O42">
+        <v>-0.6405256</v>
+      </c>
+      <c r="P42">
+        <v>-2.2709544</v>
+      </c>
+      <c r="Q42">
+        <v>-0.5399543999999998</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1307905721655831</v>
+      </c>
+      <c r="T42">
+        <v>1.113511434670536</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.0831495914948894</v>
+      </c>
+      <c r="W42">
+        <v>0.2189438775510204</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3779526886131337</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.168051894319758</v>
+      </c>
+      <c r="C43">
+        <v>2.826604985771091</v>
+      </c>
+      <c r="D43">
+        <v>22.47960498577109</v>
+      </c>
+      <c r="E43">
+        <v>8.59</v>
+      </c>
+      <c r="F43">
+        <v>20.09</v>
+      </c>
+      <c r="G43">
+        <v>0.437</v>
+      </c>
+      <c r="H43">
+        <v>37.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.5</v>
+      </c>
+      <c r="K43">
+        <v>1.731</v>
+      </c>
+      <c r="L43">
+        <v>1.769</v>
+      </c>
+      <c r="M43">
+        <v>4.797492</v>
+      </c>
+      <c r="N43">
+        <v>-3.028492</v>
+      </c>
+      <c r="O43">
+        <v>-0.66626824</v>
+      </c>
+      <c r="P43">
+        <v>-2.36222376</v>
+      </c>
+      <c r="Q43">
+        <v>-0.6312237599999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1323497344056777</v>
+      </c>
+      <c r="T43">
+        <v>1.132384509834444</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.0811215526779409</v>
+      </c>
+      <c r="W43">
+        <v>0.2194281732205077</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3687343303542768</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.170051894319758</v>
+      </c>
+      <c r="C44">
+        <v>1.994063567953447</v>
+      </c>
+      <c r="D44">
+        <v>22.13706356795344</v>
+      </c>
+      <c r="E44">
+        <v>9.079999999999998</v>
+      </c>
+      <c r="F44">
+        <v>20.58</v>
+      </c>
+      <c r="G44">
+        <v>0.437</v>
+      </c>
+      <c r="H44">
+        <v>37.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.5</v>
+      </c>
+      <c r="K44">
+        <v>1.731</v>
+      </c>
+      <c r="L44">
+        <v>1.769</v>
+      </c>
+      <c r="M44">
+        <v>4.914504</v>
+      </c>
+      <c r="N44">
+        <v>-3.145504</v>
+      </c>
+      <c r="O44">
+        <v>-0.69201088</v>
+      </c>
+      <c r="P44">
+        <v>-2.45349312</v>
+      </c>
+      <c r="Q44">
+        <v>-0.72249312</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.133962660860948</v>
+      </c>
+      <c r="T44">
+        <v>1.151908380693658</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.07919008713798992</v>
+      </c>
+      <c r="W44">
+        <v>0.219889407191448</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3599549415363178</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.172051894319758</v>
+      </c>
+      <c r="C45">
+        <v>1.171804673159311</v>
+      </c>
+      <c r="D45">
+        <v>21.80480467315931</v>
+      </c>
+      <c r="E45">
+        <v>9.57</v>
+      </c>
+      <c r="F45">
+        <v>21.07</v>
+      </c>
+      <c r="G45">
+        <v>0.437</v>
+      </c>
+      <c r="H45">
+        <v>37.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.5</v>
+      </c>
+      <c r="K45">
+        <v>1.731</v>
+      </c>
+      <c r="L45">
+        <v>1.769</v>
+      </c>
+      <c r="M45">
+        <v>5.031516000000001</v>
+      </c>
+      <c r="N45">
+        <v>-3.262516000000001</v>
+      </c>
+      <c r="O45">
+        <v>-0.7177535200000001</v>
+      </c>
+      <c r="P45">
+        <v>-2.544762480000001</v>
+      </c>
+      <c r="Q45">
+        <v>-0.8137624800000005</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1356321812269295</v>
+      </c>
+      <c r="T45">
+        <v>1.172117299653196</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.07734845720454828</v>
+      </c>
+      <c r="W45">
+        <v>0.2203291884195539</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3515838963843104</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.174051894319758</v>
+      </c>
+      <c r="C46">
+        <v>0.3593721514881665</v>
+      </c>
+      <c r="D46">
+        <v>21.48237215148816</v>
+      </c>
+      <c r="E46">
+        <v>10.06</v>
+      </c>
+      <c r="F46">
+        <v>21.56</v>
+      </c>
+      <c r="G46">
+        <v>0.437</v>
+      </c>
+      <c r="H46">
+        <v>37.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.5</v>
+      </c>
+      <c r="K46">
+        <v>1.731</v>
+      </c>
+      <c r="L46">
+        <v>1.769</v>
+      </c>
+      <c r="M46">
+        <v>5.148528</v>
+      </c>
+      <c r="N46">
+        <v>-3.379528</v>
+      </c>
+      <c r="O46">
+        <v>-0.74349616</v>
+      </c>
+      <c r="P46">
+        <v>-2.63603184</v>
+      </c>
+      <c r="Q46">
+        <v>-0.9050318399999997</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1373613273202676</v>
+      </c>
+      <c r="T46">
+        <v>1.193047965718432</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.07559053772262674</v>
+      </c>
+      <c r="W46">
+        <v>0.2207489795918368</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.343593353284667</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.176051894319758</v>
+      </c>
+      <c r="C47">
+        <v>-0.4436635593551443</v>
+      </c>
+      <c r="D47">
+        <v>21.16933644064486</v>
+      </c>
+      <c r="E47">
+        <v>10.55</v>
+      </c>
+      <c r="F47">
+        <v>22.05</v>
+      </c>
+      <c r="G47">
+        <v>0.437</v>
+      </c>
+      <c r="H47">
+        <v>37.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.5</v>
+      </c>
+      <c r="K47">
+        <v>1.731</v>
+      </c>
+      <c r="L47">
+        <v>1.769</v>
+      </c>
+      <c r="M47">
+        <v>5.265540000000001</v>
+      </c>
+      <c r="N47">
+        <v>-3.49654</v>
+      </c>
+      <c r="O47">
+        <v>-0.7692388000000001</v>
+      </c>
+      <c r="P47">
+        <v>-2.7273012</v>
+      </c>
+      <c r="Q47">
+        <v>-0.9963012000000002</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1391533514533634</v>
+      </c>
+      <c r="T47">
+        <v>1.214739746913312</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.07391074799545724</v>
+      </c>
+      <c r="W47">
+        <v>0.2211501133786848</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3359579454338966</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.178051894319758</v>
+      </c>
+      <c r="C48">
+        <v>-1.237707343377714</v>
+      </c>
+      <c r="D48">
+        <v>20.86529265662229</v>
+      </c>
+      <c r="E48">
+        <v>11.04</v>
+      </c>
+      <c r="F48">
+        <v>22.54</v>
+      </c>
+      <c r="G48">
+        <v>0.437</v>
+      </c>
+      <c r="H48">
+        <v>37.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.5</v>
+      </c>
+      <c r="K48">
+        <v>1.731</v>
+      </c>
+      <c r="L48">
+        <v>1.769</v>
+      </c>
+      <c r="M48">
+        <v>5.382552000000001</v>
+      </c>
+      <c r="N48">
+        <v>-3.613552000000001</v>
+      </c>
+      <c r="O48">
+        <v>-0.7949814400000003</v>
+      </c>
+      <c r="P48">
+        <v>-2.818570560000001</v>
+      </c>
+      <c r="Q48">
+        <v>-1.087570560000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1410117468506479</v>
+      </c>
+      <c r="T48">
+        <v>1.237234927411707</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.07230399260425163</v>
+      </c>
+      <c r="W48">
+        <v>0.2215338065661047</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3286545118375075</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.180051894319758</v>
+      </c>
+      <c r="C49">
+        <v>-2.02314115341057</v>
+      </c>
+      <c r="D49">
+        <v>20.56985884658943</v>
+      </c>
+      <c r="E49">
+        <v>11.53</v>
+      </c>
+      <c r="F49">
+        <v>23.03</v>
+      </c>
+      <c r="G49">
+        <v>0.437</v>
+      </c>
+      <c r="H49">
+        <v>37.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.5</v>
+      </c>
+      <c r="K49">
+        <v>1.731</v>
+      </c>
+      <c r="L49">
+        <v>1.769</v>
+      </c>
+      <c r="M49">
+        <v>5.499564</v>
+      </c>
+      <c r="N49">
+        <v>-3.730564</v>
+      </c>
+      <c r="O49">
+        <v>-0.8207240800000001</v>
+      </c>
+      <c r="P49">
+        <v>-2.90983992</v>
+      </c>
+      <c r="Q49">
+        <v>-1.17883992</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1429402703761318</v>
+      </c>
+      <c r="T49">
+        <v>1.26057898264589</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.0707656097828846</v>
+      </c>
+      <c r="W49">
+        <v>0.2219011723838472</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3216618626494755</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.182051894319758</v>
+      </c>
+      <c r="C50">
+        <v>-2.800325611867699</v>
+      </c>
+      <c r="D50">
+        <v>20.2826743881323</v>
+      </c>
+      <c r="E50">
+        <v>12.02</v>
+      </c>
+      <c r="F50">
+        <v>23.52</v>
+      </c>
+      <c r="G50">
+        <v>0.437</v>
+      </c>
+      <c r="H50">
+        <v>37.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.5</v>
+      </c>
+      <c r="K50">
+        <v>1.731</v>
+      </c>
+      <c r="L50">
+        <v>1.769</v>
+      </c>
+      <c r="M50">
+        <v>5.616576</v>
+      </c>
+      <c r="N50">
+        <v>-3.847576</v>
+      </c>
+      <c r="O50">
+        <v>-0.84646672</v>
+      </c>
+      <c r="P50">
+        <v>-3.00110928</v>
+      </c>
+      <c r="Q50">
+        <v>-1.27010928</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1449429678833651</v>
+      </c>
+      <c r="T50">
+        <v>1.284820886158311</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.06929132624574118</v>
+      </c>
+      <c r="W50">
+        <v>0.222253231292517</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3149605738442781</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.184051894319758</v>
+      </c>
+      <c r="C51">
+        <v>-3.569601479258207</v>
+      </c>
+      <c r="D51">
+        <v>20.00339852074179</v>
+      </c>
+      <c r="E51">
+        <v>12.51</v>
+      </c>
+      <c r="F51">
+        <v>24.01</v>
+      </c>
+      <c r="G51">
+        <v>0.437</v>
+      </c>
+      <c r="H51">
+        <v>37.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.5</v>
+      </c>
+      <c r="K51">
+        <v>1.731</v>
+      </c>
+      <c r="L51">
+        <v>1.769</v>
+      </c>
+      <c r="M51">
+        <v>5.733588</v>
+      </c>
+      <c r="N51">
+        <v>-3.964588</v>
+      </c>
+      <c r="O51">
+        <v>-0.87220936</v>
+      </c>
+      <c r="P51">
+        <v>-3.09237864</v>
+      </c>
+      <c r="Q51">
+        <v>-1.36137864</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1470242025477448</v>
+      </c>
+      <c r="T51">
+        <v>1.310013452553572</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.06787721754684849</v>
+      </c>
+      <c r="W51">
+        <v>0.2225909204498126</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3085328070311295</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.186051894319758</v>
+      </c>
+      <c r="C52">
+        <v>-4.331291003024937</v>
+      </c>
+      <c r="D52">
+        <v>19.73170899697506</v>
+      </c>
+      <c r="E52">
+        <v>13</v>
+      </c>
+      <c r="F52">
+        <v>24.5</v>
+      </c>
+      <c r="G52">
+        <v>0.437</v>
+      </c>
+      <c r="H52">
+        <v>37.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.5</v>
+      </c>
+      <c r="K52">
+        <v>1.731</v>
+      </c>
+      <c r="L52">
+        <v>1.769</v>
+      </c>
+      <c r="M52">
+        <v>5.8506</v>
+      </c>
+      <c r="N52">
+        <v>-4.0816</v>
+      </c>
+      <c r="O52">
+        <v>-0.897952</v>
+      </c>
+      <c r="P52">
+        <v>-3.183648</v>
+      </c>
+      <c r="Q52">
+        <v>-1.452648</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1491886865986997</v>
+      </c>
+      <c r="T52">
+        <v>1.336213721604644</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.06651967319591152</v>
+      </c>
+      <c r="W52">
+        <v>0.2229151020408163</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.302362150890507</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.188051894319758</v>
+      </c>
+      <c r="C53">
+        <v>-5.085699157935206</v>
+      </c>
+      <c r="D53">
+        <v>19.46730084206479</v>
+      </c>
+      <c r="E53">
+        <v>13.49</v>
+      </c>
+      <c r="F53">
+        <v>24.99</v>
+      </c>
+      <c r="G53">
+        <v>0.437</v>
+      </c>
+      <c r="H53">
+        <v>37.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.5</v>
+      </c>
+      <c r="K53">
+        <v>1.731</v>
+      </c>
+      <c r="L53">
+        <v>1.769</v>
+      </c>
+      <c r="M53">
+        <v>5.967612000000001</v>
+      </c>
+      <c r="N53">
+        <v>-4.198612000000001</v>
+      </c>
+      <c r="O53">
+        <v>-0.9236946400000001</v>
+      </c>
+      <c r="P53">
+        <v>-3.274917360000001</v>
+      </c>
+      <c r="Q53">
+        <v>-1.543917360000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1514415169374487</v>
+      </c>
+      <c r="T53">
+        <v>1.363483389392494</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.06521536587834463</v>
+      </c>
+      <c r="W53">
+        <v>0.2232265706282513</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2964334812652029</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1900518943197581</v>
+      </c>
+      <c r="C54">
+        <v>-5.833114788061593</v>
+      </c>
+      <c r="D54">
+        <v>19.20988521193841</v>
+      </c>
+      <c r="E54">
+        <v>13.98</v>
+      </c>
+      <c r="F54">
+        <v>25.48</v>
+      </c>
+      <c r="G54">
+        <v>0.437</v>
+      </c>
+      <c r="H54">
+        <v>37.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.5</v>
+      </c>
+      <c r="K54">
+        <v>1.731</v>
+      </c>
+      <c r="L54">
+        <v>1.769</v>
+      </c>
+      <c r="M54">
+        <v>6.084624000000001</v>
+      </c>
+      <c r="N54">
+        <v>-4.315624000000001</v>
+      </c>
+      <c r="O54">
+        <v>-0.9494372800000002</v>
+      </c>
+      <c r="P54">
+        <v>-3.36618672</v>
+      </c>
+      <c r="Q54">
+        <v>-1.63518672</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1537882152069789</v>
+      </c>
+      <c r="T54">
+        <v>1.391889293338171</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.063961224226838</v>
+      </c>
+      <c r="W54">
+        <v>0.2235260596546311</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2907328373947182</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.192051894319758</v>
+      </c>
+      <c r="C55">
+        <v>-6.57381165934277</v>
+      </c>
+      <c r="D55">
+        <v>18.95918834065723</v>
+      </c>
+      <c r="E55">
+        <v>14.47</v>
+      </c>
+      <c r="F55">
+        <v>25.97</v>
+      </c>
+      <c r="G55">
+        <v>0.437</v>
+      </c>
+      <c r="H55">
+        <v>37.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.5</v>
+      </c>
+      <c r="K55">
+        <v>1.731</v>
+      </c>
+      <c r="L55">
+        <v>1.769</v>
+      </c>
+      <c r="M55">
+        <v>6.201636000000001</v>
+      </c>
+      <c r="N55">
+        <v>-4.432636</v>
+      </c>
+      <c r="O55">
+        <v>-0.9751799200000001</v>
+      </c>
+      <c r="P55">
+        <v>-3.45745608</v>
+      </c>
+      <c r="Q55">
+        <v>-1.72645608</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1562347729773401</v>
+      </c>
+      <c r="T55">
+        <v>1.421503959153876</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06275440867538823</v>
+      </c>
+      <c r="W55">
+        <v>0.2238142472083173</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2852473121608556</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.194051894319758</v>
+      </c>
+      <c r="C56">
+        <v>-7.308049430788039</v>
+      </c>
+      <c r="D56">
+        <v>18.71495056921196</v>
+      </c>
+      <c r="E56">
+        <v>14.96</v>
+      </c>
+      <c r="F56">
+        <v>26.46</v>
+      </c>
+      <c r="G56">
+        <v>0.437</v>
+      </c>
+      <c r="H56">
+        <v>37.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.5</v>
+      </c>
+      <c r="K56">
+        <v>1.731</v>
+      </c>
+      <c r="L56">
+        <v>1.769</v>
+      </c>
+      <c r="M56">
+        <v>6.318648</v>
+      </c>
+      <c r="N56">
+        <v>-4.549648</v>
+      </c>
+      <c r="O56">
+        <v>-1.00092256</v>
+      </c>
+      <c r="P56">
+        <v>-3.54872544</v>
+      </c>
+      <c r="Q56">
+        <v>-1.81772544</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1587877028246736</v>
+      </c>
+      <c r="T56">
+        <v>1.452406219135482</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.06159228999621438</v>
+      </c>
+      <c r="W56">
+        <v>0.224091761148904</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2799649545282472</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.196051894319758</v>
+      </c>
+      <c r="C57">
+        <v>-8.03607455156855</v>
+      </c>
+      <c r="D57">
+        <v>18.47692544843145</v>
+      </c>
+      <c r="E57">
+        <v>15.45</v>
+      </c>
+      <c r="F57">
+        <v>26.95</v>
+      </c>
+      <c r="G57">
+        <v>0.437</v>
+      </c>
+      <c r="H57">
+        <v>37.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.5</v>
+      </c>
+      <c r="K57">
+        <v>1.731</v>
+      </c>
+      <c r="L57">
+        <v>1.769</v>
+      </c>
+      <c r="M57">
+        <v>6.435660000000001</v>
+      </c>
+      <c r="N57">
+        <v>-4.666660000000001</v>
+      </c>
+      <c r="O57">
+        <v>-1.0266652</v>
+      </c>
+      <c r="P57">
+        <v>-3.639994800000001</v>
+      </c>
+      <c r="Q57">
+        <v>-1.908994800000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1614540962207774</v>
+      </c>
+      <c r="T57">
+        <v>1.484681912894048</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.06047243017810137</v>
+      </c>
+      <c r="W57">
+        <v>0.2243591836734694</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2748746826277335</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.198051894319758</v>
+      </c>
+      <c r="C58">
+        <v>-8.758121090510585</v>
+      </c>
+      <c r="D58">
+        <v>18.24487890948942</v>
+      </c>
+      <c r="E58">
+        <v>15.94</v>
+      </c>
+      <c r="F58">
+        <v>27.44</v>
+      </c>
+      <c r="G58">
+        <v>0.437</v>
+      </c>
+      <c r="H58">
+        <v>37.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.5</v>
+      </c>
+      <c r="K58">
+        <v>1.731</v>
+      </c>
+      <c r="L58">
+        <v>1.769</v>
+      </c>
+      <c r="M58">
+        <v>6.552672</v>
+      </c>
+      <c r="N58">
+        <v>-4.783672</v>
+      </c>
+      <c r="O58">
+        <v>-1.05240784</v>
+      </c>
+      <c r="P58">
+        <v>-3.73126416</v>
+      </c>
+      <c r="Q58">
+        <v>-2.00026416</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1642416893167042</v>
+      </c>
+      <c r="T58">
+        <v>1.518424683641641</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.05939256535349243</v>
+      </c>
+      <c r="W58">
+        <v>0.224617055393586</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2699662061522383</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.200051894319758</v>
+      </c>
+      <c r="C59">
+        <v>-9.474411503859905</v>
+      </c>
+      <c r="D59">
+        <v>18.0185884961401</v>
+      </c>
+      <c r="E59">
+        <v>16.43</v>
+      </c>
+      <c r="F59">
+        <v>27.93</v>
+      </c>
+      <c r="G59">
+        <v>0.437</v>
+      </c>
+      <c r="H59">
+        <v>37.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.5</v>
+      </c>
+      <c r="K59">
+        <v>1.731</v>
+      </c>
+      <c r="L59">
+        <v>1.769</v>
+      </c>
+      <c r="M59">
+        <v>6.669684000000001</v>
+      </c>
+      <c r="N59">
+        <v>-4.900684000000001</v>
+      </c>
+      <c r="O59">
+        <v>-1.07815048</v>
+      </c>
+      <c r="P59">
+        <v>-3.822533520000001</v>
+      </c>
+      <c r="Q59">
+        <v>-2.09153352</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1671589379054648</v>
+      </c>
+      <c r="T59">
+        <v>1.553736885586795</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.0583505905227294</v>
+      </c>
+      <c r="W59">
+        <v>0.2248658789831722</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2652299569214973</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.202051894319758</v>
+      </c>
+      <c r="C60">
+        <v>-10.1851573466107</v>
+      </c>
+      <c r="D60">
+        <v>17.7978426533893</v>
+      </c>
+      <c r="E60">
+        <v>16.92</v>
+      </c>
+      <c r="F60">
+        <v>28.42</v>
+      </c>
+      <c r="G60">
+        <v>0.437</v>
+      </c>
+      <c r="H60">
+        <v>37.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.5</v>
+      </c>
+      <c r="K60">
+        <v>1.731</v>
+      </c>
+      <c r="L60">
+        <v>1.769</v>
+      </c>
+      <c r="M60">
+        <v>6.786696</v>
+      </c>
+      <c r="N60">
+        <v>-5.017696</v>
+      </c>
+      <c r="O60">
+        <v>-1.10389312</v>
+      </c>
+      <c r="P60">
+        <v>-3.91380288</v>
+      </c>
+      <c r="Q60">
+        <v>-2.18280288</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1702151030936901</v>
+      </c>
+      <c r="T60">
+        <v>1.590730620957909</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.05734454585854443</v>
+      </c>
+      <c r="W60">
+        <v>0.2251061224489796</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2606570266297474</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.204051894319758</v>
+      </c>
+      <c r="C61">
+        <v>-10.89055993218048</v>
+      </c>
+      <c r="D61">
+        <v>17.58244006781952</v>
+      </c>
+      <c r="E61">
+        <v>17.41</v>
+      </c>
+      <c r="F61">
+        <v>28.91</v>
+      </c>
+      <c r="G61">
+        <v>0.437</v>
+      </c>
+      <c r="H61">
+        <v>37.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.5</v>
+      </c>
+      <c r="K61">
+        <v>1.731</v>
+      </c>
+      <c r="L61">
+        <v>1.769</v>
+      </c>
+      <c r="M61">
+        <v>6.903708</v>
+      </c>
+      <c r="N61">
+        <v>-5.134708</v>
+      </c>
+      <c r="O61">
+        <v>-1.12963576</v>
+      </c>
+      <c r="P61">
+        <v>-4.00507224</v>
+      </c>
+      <c r="Q61">
+        <v>-2.27407224</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1734203495106094</v>
+      </c>
+      <c r="T61">
+        <v>1.629528928786151</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.05637260440331485</v>
+      </c>
+      <c r="W61">
+        <v>0.2253382220684884</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2562391109241584</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.206051894319758</v>
+      </c>
+      <c r="C62">
+        <v>-11.59081094475442</v>
+      </c>
+      <c r="D62">
+        <v>17.37218905524558</v>
+      </c>
+      <c r="E62">
+        <v>17.9</v>
+      </c>
+      <c r="F62">
+        <v>29.4</v>
+      </c>
+      <c r="G62">
+        <v>0.437</v>
+      </c>
+      <c r="H62">
+        <v>37.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.5</v>
+      </c>
+      <c r="K62">
+        <v>1.731</v>
+      </c>
+      <c r="L62">
+        <v>1.769</v>
+      </c>
+      <c r="M62">
+        <v>7.02072</v>
+      </c>
+      <c r="N62">
+        <v>-5.25172</v>
+      </c>
+      <c r="O62">
+        <v>-1.1553784</v>
+      </c>
+      <c r="P62">
+        <v>-4.0963416</v>
+      </c>
+      <c r="Q62">
+        <v>-2.3653416</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1767858582483746</v>
+      </c>
+      <c r="T62">
+        <v>1.670267152005804</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05543306099659295</v>
+      </c>
+      <c r="W62">
+        <v>0.2255625850340136</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2519684590754225</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.208051894319758</v>
+      </c>
+      <c r="C63">
+        <v>-12.28609300821453</v>
+      </c>
+      <c r="D63">
+        <v>17.16690699178547</v>
+      </c>
+      <c r="E63">
+        <v>18.39</v>
+      </c>
+      <c r="F63">
+        <v>29.89</v>
+      </c>
+      <c r="G63">
+        <v>0.437</v>
+      </c>
+      <c r="H63">
+        <v>37.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.5</v>
+      </c>
+      <c r="K63">
+        <v>1.731</v>
+      </c>
+      <c r="L63">
+        <v>1.769</v>
+      </c>
+      <c r="M63">
+        <v>7.137732000000001</v>
+      </c>
+      <c r="N63">
+        <v>-5.368732000000001</v>
+      </c>
+      <c r="O63">
+        <v>-1.18112104</v>
+      </c>
+      <c r="P63">
+        <v>-4.187610960000001</v>
+      </c>
+      <c r="Q63">
+        <v>-2.456610960000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1803239571778201</v>
+      </c>
+      <c r="T63">
+        <v>1.713094514877748</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.05452432229173075</v>
+      </c>
+      <c r="W63">
+        <v>0.2257795918367347</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2478378285987762</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.210051894319758</v>
+      </c>
+      <c r="C64">
+        <v>-12.97658021520251</v>
+      </c>
+      <c r="D64">
+        <v>16.96641978479748</v>
+      </c>
+      <c r="E64">
+        <v>18.88</v>
+      </c>
+      <c r="F64">
+        <v>30.38</v>
+      </c>
+      <c r="G64">
+        <v>0.437</v>
+      </c>
+      <c r="H64">
+        <v>37.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.5</v>
+      </c>
+      <c r="K64">
+        <v>1.731</v>
+      </c>
+      <c r="L64">
+        <v>1.769</v>
+      </c>
+      <c r="M64">
+        <v>7.254744000000001</v>
+      </c>
+      <c r="N64">
+        <v>-5.485744</v>
+      </c>
+      <c r="O64">
+        <v>-1.20686368</v>
+      </c>
+      <c r="P64">
+        <v>-4.278880320000001</v>
+      </c>
+      <c r="Q64">
+        <v>-2.547880320000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1840482718403943</v>
+      </c>
+      <c r="T64">
+        <v>1.758175949479794</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05364489773863832</v>
+      </c>
+      <c r="W64">
+        <v>0.2259895984200132</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2438404442665378</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.212051894319758</v>
+      </c>
+      <c r="C65">
+        <v>-13.66243861953816</v>
+      </c>
+      <c r="D65">
+        <v>16.77056138046184</v>
+      </c>
+      <c r="E65">
+        <v>19.37</v>
+      </c>
+      <c r="F65">
+        <v>30.87</v>
+      </c>
+      <c r="G65">
+        <v>0.437</v>
+      </c>
+      <c r="H65">
+        <v>37.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.5</v>
+      </c>
+      <c r="K65">
+        <v>1.731</v>
+      </c>
+      <c r="L65">
+        <v>1.769</v>
+      </c>
+      <c r="M65">
+        <v>7.371756</v>
+      </c>
+      <c r="N65">
+        <v>-5.602756</v>
+      </c>
+      <c r="O65">
+        <v>-1.23260632</v>
+      </c>
+      <c r="P65">
+        <v>-4.37014968</v>
+      </c>
+      <c r="Q65">
+        <v>-2.63914968</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1879739008090537</v>
+      </c>
+      <c r="T65">
+        <v>1.805694218384654</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.0527933914253266</v>
+      </c>
+      <c r="W65">
+        <v>0.226192938127632</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2399699610242119</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.214051894319758</v>
+      </c>
+      <c r="C66">
+        <v>-14.34382669492025</v>
+      </c>
+      <c r="D66">
+        <v>16.57917330507975</v>
+      </c>
+      <c r="E66">
+        <v>19.86</v>
+      </c>
+      <c r="F66">
+        <v>31.36</v>
+      </c>
+      <c r="G66">
+        <v>0.437</v>
+      </c>
+      <c r="H66">
+        <v>37.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.5</v>
+      </c>
+      <c r="K66">
+        <v>1.731</v>
+      </c>
+      <c r="L66">
+        <v>1.769</v>
+      </c>
+      <c r="M66">
+        <v>7.488768</v>
+      </c>
+      <c r="N66">
+        <v>-5.719768</v>
+      </c>
+      <c r="O66">
+        <v>-1.25834896</v>
+      </c>
+      <c r="P66">
+        <v>-4.46141904</v>
+      </c>
+      <c r="Q66">
+        <v>-2.73041904</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1921176202759718</v>
+      </c>
+      <c r="T66">
+        <v>1.855852391117561</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05196849468430588</v>
+      </c>
+      <c r="W66">
+        <v>0.2263899234693878</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2362204303832086</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.216051894319758</v>
+      </c>
+      <c r="C67">
+        <v>-15.02089576257344</v>
+      </c>
+      <c r="D67">
+        <v>16.39210423742656</v>
+      </c>
+      <c r="E67">
+        <v>20.35</v>
+      </c>
+      <c r="F67">
+        <v>31.85</v>
+      </c>
+      <c r="G67">
+        <v>0.437</v>
+      </c>
+      <c r="H67">
+        <v>37.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.5</v>
+      </c>
+      <c r="K67">
+        <v>1.731</v>
+      </c>
+      <c r="L67">
+        <v>1.769</v>
+      </c>
+      <c r="M67">
+        <v>7.605780000000001</v>
+      </c>
+      <c r="N67">
+        <v>-5.836780000000001</v>
+      </c>
+      <c r="O67">
+        <v>-1.2840916</v>
+      </c>
+      <c r="P67">
+        <v>-4.552688400000001</v>
+      </c>
+      <c r="Q67">
+        <v>-2.821688400000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1964981237124281</v>
+      </c>
+      <c r="T67">
+        <v>1.908876745149491</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05116897938147039</v>
+      </c>
+      <c r="W67">
+        <v>0.2265808477237049</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2325862699157746</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.218051894319758</v>
+      </c>
+      <c r="C68">
+        <v>-15.6937903902663</v>
+      </c>
+      <c r="D68">
+        <v>16.2092096097337</v>
+      </c>
+      <c r="E68">
+        <v>20.84</v>
+      </c>
+      <c r="F68">
+        <v>32.34</v>
+      </c>
+      <c r="G68">
+        <v>0.437</v>
+      </c>
+      <c r="H68">
+        <v>37.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.5</v>
+      </c>
+      <c r="K68">
+        <v>1.731</v>
+      </c>
+      <c r="L68">
+        <v>1.769</v>
+      </c>
+      <c r="M68">
+        <v>7.722792000000001</v>
+      </c>
+      <c r="N68">
+        <v>-5.953792000000001</v>
+      </c>
+      <c r="O68">
+        <v>-1.30983424</v>
+      </c>
+      <c r="P68">
+        <v>-4.643957760000001</v>
+      </c>
+      <c r="Q68">
+        <v>-2.912957760000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2011363038216172</v>
+      </c>
+      <c r="T68">
+        <v>1.965020178830358</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.05039369181508448</v>
+      </c>
+      <c r="W68">
+        <v>0.2267659863945578</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2290622355231113</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.220051894319758</v>
+      </c>
+      <c r="C69">
+        <v>-16.36264876491191</v>
+      </c>
+      <c r="D69">
+        <v>16.0303512350881</v>
+      </c>
+      <c r="E69">
+        <v>21.33000000000001</v>
+      </c>
+      <c r="F69">
+        <v>32.83000000000001</v>
+      </c>
+      <c r="G69">
+        <v>0.437</v>
+      </c>
+      <c r="H69">
+        <v>37.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.5</v>
+      </c>
+      <c r="K69">
+        <v>1.731</v>
+      </c>
+      <c r="L69">
+        <v>1.769</v>
+      </c>
+      <c r="M69">
+        <v>7.839804000000002</v>
+      </c>
+      <c r="N69">
+        <v>-6.070804000000002</v>
+      </c>
+      <c r="O69">
+        <v>-1.33557688</v>
+      </c>
+      <c r="P69">
+        <v>-4.735227120000001</v>
+      </c>
+      <c r="Q69">
+        <v>-3.004227120000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2060555857556056</v>
+      </c>
+      <c r="T69">
+        <v>2.024566244855521</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04964154716112799</v>
+      </c>
+      <c r="W69">
+        <v>0.2269455985379226</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2256433961869455</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.222051894319758</v>
+      </c>
+      <c r="C70">
+        <v>-17.02760304076912</v>
+      </c>
+      <c r="D70">
+        <v>15.85539695923088</v>
+      </c>
+      <c r="E70">
+        <v>21.82</v>
+      </c>
+      <c r="F70">
+        <v>33.32</v>
+      </c>
+      <c r="G70">
+        <v>0.437</v>
+      </c>
+      <c r="H70">
+        <v>37.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.5</v>
+      </c>
+      <c r="K70">
+        <v>1.731</v>
+      </c>
+      <c r="L70">
+        <v>1.769</v>
+      </c>
+      <c r="M70">
+        <v>7.956816000000001</v>
+      </c>
+      <c r="N70">
+        <v>-6.187816000000001</v>
+      </c>
+      <c r="O70">
+        <v>-1.36131952</v>
+      </c>
+      <c r="P70">
+        <v>-4.82649648</v>
+      </c>
+      <c r="Q70">
+        <v>-3.09549648</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2112823228104683</v>
+      </c>
+      <c r="T70">
+        <v>2.087833940007256</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.04891152440875847</v>
+      </c>
+      <c r="W70">
+        <v>0.2271199279711885</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2223251109489022</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.224051894319758</v>
+      </c>
+      <c r="C71">
+        <v>-17.68877966508869</v>
+      </c>
+      <c r="D71">
+        <v>15.68422033491131</v>
+      </c>
+      <c r="E71">
+        <v>22.31</v>
+      </c>
+      <c r="F71">
+        <v>33.81</v>
+      </c>
+      <c r="G71">
+        <v>0.437</v>
+      </c>
+      <c r="H71">
+        <v>37.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.5</v>
+      </c>
+      <c r="K71">
+        <v>1.731</v>
+      </c>
+      <c r="L71">
+        <v>1.769</v>
+      </c>
+      <c r="M71">
+        <v>8.073828000000001</v>
+      </c>
+      <c r="N71">
+        <v>-6.304828000000001</v>
+      </c>
+      <c r="O71">
+        <v>-1.38706216</v>
+      </c>
+      <c r="P71">
+        <v>-4.91776584</v>
+      </c>
+      <c r="Q71">
+        <v>-3.186765840000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2168462687075802</v>
+      </c>
+      <c r="T71">
+        <v>2.155183421942974</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.04820266173616777</v>
+      </c>
+      <c r="W71">
+        <v>0.2272892043774032</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2191030078916717</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.226051894319758</v>
+      </c>
+      <c r="C72">
+        <v>-18.34629968289025</v>
+      </c>
+      <c r="D72">
+        <v>15.51670031710975</v>
+      </c>
+      <c r="E72">
+        <v>22.8</v>
+      </c>
+      <c r="F72">
+        <v>34.3</v>
+      </c>
+      <c r="G72">
+        <v>0.437</v>
+      </c>
+      <c r="H72">
+        <v>37.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.5</v>
+      </c>
+      <c r="K72">
+        <v>1.731</v>
+      </c>
+      <c r="L72">
+        <v>1.769</v>
+      </c>
+      <c r="M72">
+        <v>8.190840000000001</v>
+      </c>
+      <c r="N72">
+        <v>-6.421840000000001</v>
+      </c>
+      <c r="O72">
+        <v>-1.4128048</v>
+      </c>
+      <c r="P72">
+        <v>-5.009035200000001</v>
+      </c>
+      <c r="Q72">
+        <v>-3.278035200000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2227811443311662</v>
+      </c>
+      <c r="T72">
+        <v>2.227022869341073</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.04751405228279394</v>
+      </c>
+      <c r="W72">
+        <v>0.2274536443148688</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2159729649217906</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.228051894319758</v>
+      </c>
+      <c r="C73">
+        <v>-19.00027902241425</v>
+      </c>
+      <c r="D73">
+        <v>15.35272097758575</v>
+      </c>
+      <c r="E73">
+        <v>23.29</v>
+      </c>
+      <c r="F73">
+        <v>34.79</v>
+      </c>
+      <c r="G73">
+        <v>0.437</v>
+      </c>
+      <c r="H73">
+        <v>37.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.5</v>
+      </c>
+      <c r="K73">
+        <v>1.731</v>
+      </c>
+      <c r="L73">
+        <v>1.769</v>
+      </c>
+      <c r="M73">
+        <v>8.307852</v>
+      </c>
+      <c r="N73">
+        <v>-6.538852</v>
+      </c>
+      <c r="O73">
+        <v>-1.43854744</v>
+      </c>
+      <c r="P73">
+        <v>-5.100304560000001</v>
+      </c>
+      <c r="Q73">
+        <v>-3.369304560000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.229125321721896</v>
+      </c>
+      <c r="T73">
+        <v>2.303816761387317</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04684484027881093</v>
+      </c>
+      <c r="W73">
+        <v>0.22761345214142</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2129310921764134</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.230051894319758</v>
+      </c>
+      <c r="C74">
+        <v>-19.65082876266328</v>
+      </c>
+      <c r="D74">
+        <v>15.19217123733672</v>
+      </c>
+      <c r="E74">
+        <v>23.78</v>
+      </c>
+      <c r="F74">
+        <v>35.28</v>
+      </c>
+      <c r="G74">
+        <v>0.437</v>
+      </c>
+      <c r="H74">
+        <v>37.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.5</v>
+      </c>
+      <c r="K74">
+        <v>1.731</v>
+      </c>
+      <c r="L74">
+        <v>1.769</v>
+      </c>
+      <c r="M74">
+        <v>8.424864000000001</v>
+      </c>
+      <c r="N74">
+        <v>-6.655864000000001</v>
+      </c>
+      <c r="O74">
+        <v>-1.46429008</v>
+      </c>
+      <c r="P74">
+        <v>-5.191573920000001</v>
+      </c>
+      <c r="Q74">
+        <v>-3.460573920000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2359226546405352</v>
+      </c>
+      <c r="T74">
+        <v>2.386095931436864</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.04619421749716078</v>
+      </c>
+      <c r="W74">
+        <v>0.227768820861678</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2099737158961854</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.232051894319758</v>
+      </c>
+      <c r="C75">
+        <v>-20.29805538433043</v>
+      </c>
+      <c r="D75">
+        <v>15.03494461566957</v>
+      </c>
+      <c r="E75">
+        <v>24.27</v>
+      </c>
+      <c r="F75">
+        <v>35.77</v>
+      </c>
+      <c r="G75">
+        <v>0.437</v>
+      </c>
+      <c r="H75">
+        <v>37.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.5</v>
+      </c>
+      <c r="K75">
+        <v>1.731</v>
+      </c>
+      <c r="L75">
+        <v>1.769</v>
+      </c>
+      <c r="M75">
+        <v>8.541876</v>
+      </c>
+      <c r="N75">
+        <v>-6.772876</v>
+      </c>
+      <c r="O75">
+        <v>-1.49003272</v>
+      </c>
+      <c r="P75">
+        <v>-5.28284328</v>
+      </c>
+      <c r="Q75">
+        <v>-3.55184328</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2432234937012958</v>
+      </c>
+      <c r="T75">
+        <v>2.474469854823414</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04556141999719967</v>
+      </c>
+      <c r="W75">
+        <v>0.2279199329046687</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.207097363623635</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.234051894319758</v>
+      </c>
+      <c r="C76">
+        <v>-20.94206100530584</v>
+      </c>
+      <c r="D76">
+        <v>14.88093899469416</v>
+      </c>
+      <c r="E76">
+        <v>24.76</v>
+      </c>
+      <c r="F76">
+        <v>36.26</v>
+      </c>
+      <c r="G76">
+        <v>0.437</v>
+      </c>
+      <c r="H76">
+        <v>37.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.5</v>
+      </c>
+      <c r="K76">
+        <v>1.731</v>
+      </c>
+      <c r="L76">
+        <v>1.769</v>
+      </c>
+      <c r="M76">
+        <v>8.658887999999999</v>
+      </c>
+      <c r="N76">
+        <v>-6.889887999999999</v>
+      </c>
+      <c r="O76">
+        <v>-1.51577536</v>
+      </c>
+      <c r="P76">
+        <v>-5.374112639999999</v>
+      </c>
+      <c r="Q76">
+        <v>-3.643112639999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2510859357667302</v>
+      </c>
+      <c r="T76">
+        <v>2.569641772316622</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04494572513237265</v>
+      </c>
+      <c r="W76">
+        <v>0.2280669608383894</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2042987506016939</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.236051894319758</v>
+      </c>
+      <c r="C77">
+        <v>-21.58294360185592</v>
+      </c>
+      <c r="D77">
+        <v>14.73005639814408</v>
+      </c>
+      <c r="E77">
+        <v>25.25</v>
+      </c>
+      <c r="F77">
+        <v>36.75</v>
+      </c>
+      <c r="G77">
+        <v>0.437</v>
+      </c>
+      <c r="H77">
+        <v>37.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.5</v>
+      </c>
+      <c r="K77">
+        <v>1.731</v>
+      </c>
+      <c r="L77">
+        <v>1.769</v>
+      </c>
+      <c r="M77">
+        <v>8.7759</v>
+      </c>
+      <c r="N77">
+        <v>-7.0069</v>
+      </c>
+      <c r="O77">
+        <v>-1.541518</v>
+      </c>
+      <c r="P77">
+        <v>-5.465382</v>
+      </c>
+      <c r="Q77">
+        <v>-3.734382</v>
+      </c>
+      <c r="R77">
         <v>3</v>
       </c>
-      <c r="V3">
-        <v>0.09771986970684039</v>
-      </c>
-      <c r="W3">
-        <v>0.09136904761904761</v>
-      </c>
-      <c r="X3">
-        <v>0.1618163271119344</v>
-      </c>
-      <c r="Y3">
-        <v>-0.07044727949288677</v>
-      </c>
-      <c r="Z3">
-        <v>0.461320085166785</v>
-      </c>
-      <c r="AA3">
-        <v>-0.002051571994003513</v>
-      </c>
-      <c r="AB3">
-        <v>0.142048997589148</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1441005695831515</v>
-      </c>
-      <c r="AD3">
-        <v>9.81</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>9.81</v>
-      </c>
-      <c r="AG3">
-        <v>6.81</v>
-      </c>
-      <c r="AH3">
-        <v>0.2421624290298692</v>
-      </c>
-      <c r="AI3">
-        <v>0.2280864915136015</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1815515862436684</v>
-      </c>
-      <c r="AK3">
-        <v>0.1702074481379655</v>
-      </c>
-      <c r="AL3">
-        <v>0.276</v>
-      </c>
-      <c r="AM3">
-        <v>0.276</v>
-      </c>
-      <c r="AN3">
-        <v>7.213235294117647</v>
-      </c>
-      <c r="AO3">
-        <v>-0.394927536231884</v>
-      </c>
-      <c r="AP3">
-        <v>5.007352941176471</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.394927536231884</v>
+      <c r="S77">
+        <v>0.2595773731973994</v>
+      </c>
+      <c r="T77">
+        <v>2.672427443209287</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04434644879727435</v>
+      </c>
+      <c r="W77">
+        <v>0.2282100680272109</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.201574767260338</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.238051894319758</v>
+      </c>
+      <c r="C78">
+        <v>-22.2207972164821</v>
+      </c>
+      <c r="D78">
+        <v>14.5822027835179</v>
+      </c>
+      <c r="E78">
+        <v>25.74</v>
+      </c>
+      <c r="F78">
+        <v>37.24</v>
+      </c>
+      <c r="G78">
+        <v>0.437</v>
+      </c>
+      <c r="H78">
+        <v>37.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.5</v>
+      </c>
+      <c r="K78">
+        <v>1.731</v>
+      </c>
+      <c r="L78">
+        <v>1.769</v>
+      </c>
+      <c r="M78">
+        <v>8.892912000000001</v>
+      </c>
+      <c r="N78">
+        <v>-7.123912000000001</v>
+      </c>
+      <c r="O78">
+        <v>-1.56726064</v>
+      </c>
+      <c r="P78">
+        <v>-5.55665136</v>
+      </c>
+      <c r="Q78">
+        <v>-3.82565136</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2687764304139577</v>
+      </c>
+      <c r="T78">
+        <v>2.783778586676341</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04376294289204705</v>
+      </c>
+      <c r="W78">
+        <v>0.2283494092373792</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.198922467691123</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.240051894319758</v>
+      </c>
+      <c r="C79">
+        <v>-22.8557121533855</v>
+      </c>
+      <c r="D79">
+        <v>14.43728784661451</v>
+      </c>
+      <c r="E79">
+        <v>26.23</v>
+      </c>
+      <c r="F79">
+        <v>37.73</v>
+      </c>
+      <c r="G79">
+        <v>0.437</v>
+      </c>
+      <c r="H79">
+        <v>37.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.5</v>
+      </c>
+      <c r="K79">
+        <v>1.731</v>
+      </c>
+      <c r="L79">
+        <v>1.769</v>
+      </c>
+      <c r="M79">
+        <v>9.009924000000002</v>
+      </c>
+      <c r="N79">
+        <v>-7.240924000000001</v>
+      </c>
+      <c r="O79">
+        <v>-1.59300328</v>
+      </c>
+      <c r="P79">
+        <v>-5.647920720000001</v>
+      </c>
+      <c r="Q79">
+        <v>-3.916920720000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2787754056493472</v>
+      </c>
+      <c r="T79">
+        <v>2.904812438270965</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04319459298435813</v>
+      </c>
+      <c r="W79">
+        <v>0.2284851311953353</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1963390590198096</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.242051894319758</v>
+      </c>
+      <c r="C80">
+        <v>-23.48777516239146</v>
+      </c>
+      <c r="D80">
+        <v>14.29522483760853</v>
+      </c>
+      <c r="E80">
+        <v>26.72</v>
+      </c>
+      <c r="F80">
+        <v>38.22</v>
+      </c>
+      <c r="G80">
+        <v>0.437</v>
+      </c>
+      <c r="H80">
+        <v>37.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.5</v>
+      </c>
+      <c r="K80">
+        <v>1.731</v>
+      </c>
+      <c r="L80">
+        <v>1.769</v>
+      </c>
+      <c r="M80">
+        <v>9.126936000000001</v>
+      </c>
+      <c r="N80">
+        <v>-7.357936</v>
+      </c>
+      <c r="O80">
+        <v>-1.61874592</v>
+      </c>
+      <c r="P80">
+        <v>-5.73919008</v>
+      </c>
+      <c r="Q80">
+        <v>-4.00819008</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2896833786334084</v>
+      </c>
+      <c r="T80">
+        <v>3.036849367283281</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04264081615122534</v>
+      </c>
+      <c r="W80">
+        <v>0.2286173731030874</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1938218915964788</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.244051894319758</v>
+      </c>
+      <c r="C81">
+        <v>-24.11706961212101</v>
+      </c>
+      <c r="D81">
+        <v>14.15593038787899</v>
+      </c>
+      <c r="E81">
+        <v>27.21</v>
+      </c>
+      <c r="F81">
+        <v>38.71</v>
+      </c>
+      <c r="G81">
+        <v>0.437</v>
+      </c>
+      <c r="H81">
+        <v>37.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.5</v>
+      </c>
+      <c r="K81">
+        <v>1.731</v>
+      </c>
+      <c r="L81">
+        <v>1.769</v>
+      </c>
+      <c r="M81">
+        <v>9.243948000000001</v>
+      </c>
+      <c r="N81">
+        <v>-7.474948000000001</v>
+      </c>
+      <c r="O81">
+        <v>-1.64448856</v>
+      </c>
+      <c r="P81">
+        <v>-5.830459440000001</v>
+      </c>
+      <c r="Q81">
+        <v>-4.099459440000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3016302061873803</v>
+      </c>
+      <c r="T81">
+        <v>3.181461241915819</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04210105898475412</v>
+      </c>
+      <c r="W81">
+        <v>0.2287462671144407</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1913684499307006</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.246051894319758</v>
+      </c>
+      <c r="C82">
+        <v>-24.74367565313541</v>
+      </c>
+      <c r="D82">
+        <v>14.01932434686459</v>
+      </c>
+      <c r="E82">
+        <v>27.7</v>
+      </c>
+      <c r="F82">
+        <v>39.2</v>
+      </c>
+      <c r="G82">
+        <v>0.437</v>
+      </c>
+      <c r="H82">
+        <v>37.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.5</v>
+      </c>
+      <c r="K82">
+        <v>1.731</v>
+      </c>
+      <c r="L82">
+        <v>1.769</v>
+      </c>
+      <c r="M82">
+        <v>9.36096</v>
+      </c>
+      <c r="N82">
+        <v>-7.59196</v>
+      </c>
+      <c r="O82">
+        <v>-1.6702312</v>
+      </c>
+      <c r="P82">
+        <v>-5.9217288</v>
+      </c>
+      <c r="Q82">
+        <v>-4.1907288</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3147717164967493</v>
+      </c>
+      <c r="T82">
+        <v>3.34053430401161</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0415747957474447</v>
+      </c>
+      <c r="W82">
+        <v>0.2288719387755102</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1889763443065668</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.248051894319758</v>
+      </c>
+      <c r="C83">
+        <v>-25.36767037172508</v>
+      </c>
+      <c r="D83">
+        <v>13.88532962827493</v>
+      </c>
+      <c r="E83">
+        <v>28.19</v>
+      </c>
+      <c r="F83">
+        <v>39.69</v>
+      </c>
+      <c r="G83">
+        <v>0.437</v>
+      </c>
+      <c r="H83">
+        <v>37.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.5</v>
+      </c>
+      <c r="K83">
+        <v>1.731</v>
+      </c>
+      <c r="L83">
+        <v>1.769</v>
+      </c>
+      <c r="M83">
+        <v>9.477972000000001</v>
+      </c>
+      <c r="N83">
+        <v>-7.708972000000001</v>
+      </c>
+      <c r="O83">
+        <v>-1.69597384</v>
+      </c>
+      <c r="P83">
+        <v>-6.01299816</v>
+      </c>
+      <c r="Q83">
+        <v>-4.281998160000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3292965436807888</v>
+      </c>
+      <c r="T83">
+        <v>3.51635189895959</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04106152666414292</v>
+      </c>
+      <c r="W83">
+        <v>0.2289945074326027</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1866433030188315</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2500518943197581</v>
+      </c>
+      <c r="C84">
+        <v>-25.98912793496243</v>
+      </c>
+      <c r="D84">
+        <v>13.75387206503758</v>
+      </c>
+      <c r="E84">
+        <v>28.68</v>
+      </c>
+      <c r="F84">
+        <v>40.18</v>
+      </c>
+      <c r="G84">
+        <v>0.437</v>
+      </c>
+      <c r="H84">
+        <v>37.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.5</v>
+      </c>
+      <c r="K84">
+        <v>1.731</v>
+      </c>
+      <c r="L84">
+        <v>1.769</v>
+      </c>
+      <c r="M84">
+        <v>9.594984</v>
+      </c>
+      <c r="N84">
+        <v>-7.825984</v>
+      </c>
+      <c r="O84">
+        <v>-1.72171648</v>
+      </c>
+      <c r="P84">
+        <v>-6.104267520000001</v>
+      </c>
+      <c r="Q84">
+        <v>-4.373267520000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3454352405519437</v>
+      </c>
+      <c r="T84">
+        <v>3.711704782235123</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04056077633897045</v>
+      </c>
+      <c r="W84">
+        <v>0.2291140866102539</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1843671651771384</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.252051894319758</v>
+      </c>
+      <c r="C85">
+        <v>-26.60811972759254</v>
+      </c>
+      <c r="D85">
+        <v>13.62488027240746</v>
+      </c>
+      <c r="E85">
+        <v>29.17</v>
+      </c>
+      <c r="F85">
+        <v>40.67</v>
+      </c>
+      <c r="G85">
+        <v>0.437</v>
+      </c>
+      <c r="H85">
+        <v>37.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.5</v>
+      </c>
+      <c r="K85">
+        <v>1.731</v>
+      </c>
+      <c r="L85">
+        <v>1.769</v>
+      </c>
+      <c r="M85">
+        <v>9.711996000000001</v>
+      </c>
+      <c r="N85">
+        <v>-7.942996000000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.74745912</v>
+      </c>
+      <c r="P85">
+        <v>-6.195536880000001</v>
+      </c>
+      <c r="Q85">
+        <v>-4.464536880000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3634726076432345</v>
+      </c>
+      <c r="T85">
+        <v>3.930040357660718</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04007209228669369</v>
+      </c>
+      <c r="W85">
+        <v>0.2292307843619376</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1821458740304259</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2540518943197581</v>
+      </c>
+      <c r="C86">
+        <v>-27.2247144812923</v>
+      </c>
+      <c r="D86">
+        <v>13.4982855187077</v>
+      </c>
+      <c r="E86">
+        <v>29.66</v>
+      </c>
+      <c r="F86">
+        <v>41.16</v>
+      </c>
+      <c r="G86">
+        <v>0.437</v>
+      </c>
+      <c r="H86">
+        <v>37.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.5</v>
+      </c>
+      <c r="K86">
+        <v>1.731</v>
+      </c>
+      <c r="L86">
+        <v>1.769</v>
+      </c>
+      <c r="M86">
+        <v>9.829008</v>
+      </c>
+      <c r="N86">
+        <v>-8.060008</v>
+      </c>
+      <c r="O86">
+        <v>-1.77320176</v>
+      </c>
+      <c r="P86">
+        <v>-6.28680624</v>
+      </c>
+      <c r="Q86">
+        <v>-4.55580624</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3837646456209365</v>
+      </c>
+      <c r="T86">
+        <v>4.175667880014511</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03959504356899496</v>
+      </c>
+      <c r="W86">
+        <v>0.229344703595724</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.179977470768159</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2560518943197581</v>
+      </c>
+      <c r="C87">
+        <v>-27.83897839678977</v>
+      </c>
+      <c r="D87">
+        <v>13.37402160321023</v>
+      </c>
+      <c r="E87">
+        <v>30.15</v>
+      </c>
+      <c r="F87">
+        <v>41.65</v>
+      </c>
+      <c r="G87">
+        <v>0.437</v>
+      </c>
+      <c r="H87">
+        <v>37.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.5</v>
+      </c>
+      <c r="K87">
+        <v>1.731</v>
+      </c>
+      <c r="L87">
+        <v>1.769</v>
+      </c>
+      <c r="M87">
+        <v>9.946020000000001</v>
+      </c>
+      <c r="N87">
+        <v>-8.177020000000001</v>
+      </c>
+      <c r="O87">
+        <v>-1.7989444</v>
+      </c>
+      <c r="P87">
+        <v>-6.378075600000001</v>
+      </c>
+      <c r="Q87">
+        <v>-4.647075600000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4067622886623323</v>
+      </c>
+      <c r="T87">
+        <v>4.454045738682145</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03912921952700678</v>
+      </c>
+      <c r="W87">
+        <v>0.2294559423769508</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1778600887591217</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2580518943197581</v>
+      </c>
+      <c r="C88">
+        <v>-28.45097525929994</v>
+      </c>
+      <c r="D88">
+        <v>13.25202474070007</v>
+      </c>
+      <c r="E88">
+        <v>30.64</v>
+      </c>
+      <c r="F88">
+        <v>42.14</v>
+      </c>
+      <c r="G88">
+        <v>0.437</v>
+      </c>
+      <c r="H88">
+        <v>37.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.5</v>
+      </c>
+      <c r="K88">
+        <v>1.731</v>
+      </c>
+      <c r="L88">
+        <v>1.769</v>
+      </c>
+      <c r="M88">
+        <v>10.063032</v>
+      </c>
+      <c r="N88">
+        <v>-8.294032000000001</v>
+      </c>
+      <c r="O88">
+        <v>-1.82468704</v>
+      </c>
+      <c r="P88">
+        <v>-6.469344960000001</v>
+      </c>
+      <c r="Q88">
+        <v>-4.738344960000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4330453092810704</v>
+      </c>
+      <c r="T88">
+        <v>4.772191862873727</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03867422860227414</v>
+      </c>
+      <c r="W88">
+        <v>0.229564594209777</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1757919481921552</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2600518943197581</v>
+      </c>
+      <c r="C89">
+        <v>-29.06076654769947</v>
+      </c>
+      <c r="D89">
+        <v>13.13223345230054</v>
+      </c>
+      <c r="E89">
+        <v>31.13</v>
+      </c>
+      <c r="F89">
+        <v>42.63</v>
+      </c>
+      <c r="G89">
+        <v>0.437</v>
+      </c>
+      <c r="H89">
+        <v>37.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.5</v>
+      </c>
+      <c r="K89">
+        <v>1.731</v>
+      </c>
+      <c r="L89">
+        <v>1.769</v>
+      </c>
+      <c r="M89">
+        <v>10.180044</v>
+      </c>
+      <c r="N89">
+        <v>-8.411044</v>
+      </c>
+      <c r="O89">
+        <v>-1.85042968</v>
+      </c>
+      <c r="P89">
+        <v>-6.56061432</v>
+      </c>
+      <c r="Q89">
+        <v>-4.82961432</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4633718715334604</v>
+      </c>
+      <c r="T89">
+        <v>5.139283544633245</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03822969723902962</v>
+      </c>
+      <c r="W89">
+        <v>0.2296707482993197</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1737713510864982</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2620518943197581</v>
+      </c>
+      <c r="C90">
+        <v>-29.66841153783326</v>
+      </c>
+      <c r="D90">
+        <v>13.01458846216673</v>
+      </c>
+      <c r="E90">
+        <v>31.62</v>
+      </c>
+      <c r="F90">
+        <v>43.12</v>
+      </c>
+      <c r="G90">
+        <v>0.437</v>
+      </c>
+      <c r="H90">
+        <v>37.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.5</v>
+      </c>
+      <c r="K90">
+        <v>1.731</v>
+      </c>
+      <c r="L90">
+        <v>1.769</v>
+      </c>
+      <c r="M90">
+        <v>10.297056</v>
+      </c>
+      <c r="N90">
+        <v>-8.528055999999999</v>
+      </c>
+      <c r="O90">
+        <v>-1.87617232</v>
+      </c>
+      <c r="P90">
+        <v>-6.651883679999999</v>
+      </c>
+      <c r="Q90">
+        <v>-4.920883679999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4987528608279155</v>
+      </c>
+      <c r="T90">
+        <v>5.567557173352683</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03779526886131337</v>
+      </c>
+      <c r="W90">
+        <v>0.2297744897959184</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1717966766423336</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.264051894319758</v>
+      </c>
+      <c r="C91">
+        <v>-30.27396740031752</v>
+      </c>
+      <c r="D91">
+        <v>12.89903259968248</v>
+      </c>
+      <c r="E91">
+        <v>32.11</v>
+      </c>
+      <c r="F91">
+        <v>43.61</v>
+      </c>
+      <c r="G91">
+        <v>0.437</v>
+      </c>
+      <c r="H91">
+        <v>37.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.5</v>
+      </c>
+      <c r="K91">
+        <v>1.731</v>
+      </c>
+      <c r="L91">
+        <v>1.769</v>
+      </c>
+      <c r="M91">
+        <v>10.414068</v>
+      </c>
+      <c r="N91">
+        <v>-8.645068</v>
+      </c>
+      <c r="O91">
+        <v>-1.90191496</v>
+      </c>
+      <c r="P91">
+        <v>-6.74315304</v>
+      </c>
+      <c r="Q91">
+        <v>-5.01215304</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5405667572668169</v>
+      </c>
+      <c r="T91">
+        <v>6.073698734566563</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03737060291905142</v>
+      </c>
+      <c r="W91">
+        <v>0.2298759000229305</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1698663769047792</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2660518943197581</v>
+      </c>
+      <c r="C92">
+        <v>-30.87748929317826</v>
+      </c>
+      <c r="D92">
+        <v>12.78551070682175</v>
+      </c>
+      <c r="E92">
+        <v>32.6</v>
+      </c>
+      <c r="F92">
+        <v>44.1</v>
+      </c>
+      <c r="G92">
+        <v>0.437</v>
+      </c>
+      <c r="H92">
+        <v>37.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.5</v>
+      </c>
+      <c r="K92">
+        <v>1.731</v>
+      </c>
+      <c r="L92">
+        <v>1.769</v>
+      </c>
+      <c r="M92">
+        <v>10.53108</v>
+      </c>
+      <c r="N92">
+        <v>-8.762080000000001</v>
+      </c>
+      <c r="O92">
+        <v>-1.9276576</v>
+      </c>
+      <c r="P92">
+        <v>-6.834422400000001</v>
+      </c>
+      <c r="Q92">
+        <v>-5.103422400000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5907434329934986</v>
+      </c>
+      <c r="T92">
+        <v>6.681068608023219</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03695537399772862</v>
+      </c>
+      <c r="W92">
+        <v>0.2299750566893424</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1679789727169483</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2680518943197581</v>
+      </c>
+      <c r="C93">
+        <v>-31.47903044964075</v>
+      </c>
+      <c r="D93">
+        <v>12.67396955035925</v>
+      </c>
+      <c r="E93">
+        <v>33.09</v>
+      </c>
+      <c r="F93">
+        <v>44.59</v>
+      </c>
+      <c r="G93">
+        <v>0.437</v>
+      </c>
+      <c r="H93">
+        <v>37.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.5</v>
+      </c>
+      <c r="K93">
+        <v>1.731</v>
+      </c>
+      <c r="L93">
+        <v>1.769</v>
+      </c>
+      <c r="M93">
+        <v>10.648092</v>
+      </c>
+      <c r="N93">
+        <v>-8.879092000000002</v>
+      </c>
+      <c r="O93">
+        <v>-1.95340024</v>
+      </c>
+      <c r="P93">
+        <v>-6.925691760000001</v>
+      </c>
+      <c r="Q93">
+        <v>-5.194691760000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6520704811038875</v>
+      </c>
+      <c r="T93">
+        <v>7.423409564470245</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03654927098676457</v>
+      </c>
+      <c r="W93">
+        <v>0.2300720340883606</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.166133049939839</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.270051894319758</v>
+      </c>
+      <c r="C94">
+        <v>-32.07864226136356</v>
+      </c>
+      <c r="D94">
+        <v>12.56435773863645</v>
+      </c>
+      <c r="E94">
+        <v>33.58000000000001</v>
+      </c>
+      <c r="F94">
+        <v>45.08000000000001</v>
+      </c>
+      <c r="G94">
+        <v>0.437</v>
+      </c>
+      <c r="H94">
+        <v>37.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.5</v>
+      </c>
+      <c r="K94">
+        <v>1.731</v>
+      </c>
+      <c r="L94">
+        <v>1.769</v>
+      </c>
+      <c r="M94">
+        <v>10.765104</v>
+      </c>
+      <c r="N94">
+        <v>-8.996104000000003</v>
+      </c>
+      <c r="O94">
+        <v>-1.979142880000001</v>
+      </c>
+      <c r="P94">
+        <v>-7.016961120000002</v>
+      </c>
+      <c r="Q94">
+        <v>-5.285961120000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7287292912418735</v>
+      </c>
+      <c r="T94">
+        <v>8.351335760029027</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03615199630212582</v>
+      </c>
+      <c r="W94">
+        <v>0.2301669032830524</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1643272559187537</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.272051894319758</v>
+      </c>
+      <c r="C95">
+        <v>-32.67637435739028</v>
+      </c>
+      <c r="D95">
+        <v>12.45662564260972</v>
+      </c>
+      <c r="E95">
+        <v>34.07</v>
+      </c>
+      <c r="F95">
+        <v>45.57</v>
+      </c>
+      <c r="G95">
+        <v>0.437</v>
+      </c>
+      <c r="H95">
+        <v>37.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.5</v>
+      </c>
+      <c r="K95">
+        <v>1.731</v>
+      </c>
+      <c r="L95">
+        <v>1.769</v>
+      </c>
+      <c r="M95">
+        <v>10.882116</v>
+      </c>
+      <c r="N95">
+        <v>-9.113116</v>
+      </c>
+      <c r="O95">
+        <v>-2.00488552</v>
+      </c>
+      <c r="P95">
+        <v>-7.10823048</v>
+      </c>
+      <c r="Q95">
+        <v>-5.37723048</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8272906185621411</v>
+      </c>
+      <c r="T95">
+        <v>9.54438372574746</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03576326515909222</v>
+      </c>
+      <c r="W95">
+        <v>0.2302597322800088</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.162560296177692</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.274051894319758</v>
+      </c>
+      <c r="C96">
+        <v>-33.27227467907423</v>
+      </c>
+      <c r="D96">
+        <v>12.35072532092578</v>
+      </c>
+      <c r="E96">
+        <v>34.56</v>
+      </c>
+      <c r="F96">
+        <v>46.06</v>
+      </c>
+      <c r="G96">
+        <v>0.437</v>
+      </c>
+      <c r="H96">
+        <v>37.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.5</v>
+      </c>
+      <c r="K96">
+        <v>1.731</v>
+      </c>
+      <c r="L96">
+        <v>1.769</v>
+      </c>
+      <c r="M96">
+        <v>10.999128</v>
+      </c>
+      <c r="N96">
+        <v>-9.230128000000001</v>
+      </c>
+      <c r="O96">
+        <v>-2.03062816</v>
+      </c>
+      <c r="P96">
+        <v>-7.199499840000001</v>
+      </c>
+      <c r="Q96">
+        <v>-5.468499840000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9587057216558317</v>
+      </c>
+      <c r="T96">
+        <v>11.13511434670537</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0353828048914423</v>
+      </c>
+      <c r="W96">
+        <v>0.2303505861919236</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1608309313247377</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.276051894319758</v>
+      </c>
+      <c r="C97">
+        <v>-33.86638955121329</v>
+      </c>
+      <c r="D97">
+        <v>12.24661044878671</v>
+      </c>
+      <c r="E97">
+        <v>35.05</v>
+      </c>
+      <c r="F97">
+        <v>46.55</v>
+      </c>
+      <c r="G97">
+        <v>0.437</v>
+      </c>
+      <c r="H97">
+        <v>37.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.5</v>
+      </c>
+      <c r="K97">
+        <v>1.731</v>
+      </c>
+      <c r="L97">
+        <v>1.769</v>
+      </c>
+      <c r="M97">
+        <v>11.11614</v>
+      </c>
+      <c r="N97">
+        <v>-9.347140000000001</v>
+      </c>
+      <c r="O97">
+        <v>-2.0563708</v>
+      </c>
+      <c r="P97">
+        <v>-7.290769200000002</v>
+      </c>
+      <c r="Q97">
+        <v>-5.559769200000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.142686865986998</v>
+      </c>
+      <c r="T97">
+        <v>13.36213721604645</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03501035431363764</v>
+      </c>
+      <c r="W97">
+        <v>0.2304395273899033</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1591379741528984</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2780518943197581</v>
+      </c>
+      <c r="C98">
+        <v>-34.45876374961708</v>
+      </c>
+      <c r="D98">
+        <v>12.14423625038292</v>
+      </c>
+      <c r="E98">
+        <v>35.54</v>
+      </c>
+      <c r="F98">
+        <v>47.04</v>
+      </c>
+      <c r="G98">
+        <v>0.437</v>
+      </c>
+      <c r="H98">
+        <v>37.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.5</v>
+      </c>
+      <c r="K98">
+        <v>1.731</v>
+      </c>
+      <c r="L98">
+        <v>1.769</v>
+      </c>
+      <c r="M98">
+        <v>11.233152</v>
+      </c>
+      <c r="N98">
+        <v>-9.464152</v>
+      </c>
+      <c r="O98">
+        <v>-2.08211344</v>
+      </c>
+      <c r="P98">
+        <v>-7.38203856</v>
+      </c>
+      <c r="Q98">
+        <v>-5.65103856</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.418658582483745</v>
+      </c>
+      <c r="T98">
+        <v>16.70267152005803</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03464566312287059</v>
+      </c>
+      <c r="W98">
+        <v>0.2305266156462585</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.157480286922139</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.280051894319758</v>
+      </c>
+      <c r="C99">
+        <v>-35.04944056531318</v>
+      </c>
+      <c r="D99">
+        <v>12.04355943468683</v>
+      </c>
+      <c r="E99">
+        <v>36.03</v>
+      </c>
+      <c r="F99">
+        <v>47.53</v>
+      </c>
+      <c r="G99">
+        <v>0.437</v>
+      </c>
+      <c r="H99">
+        <v>37.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.5</v>
+      </c>
+      <c r="K99">
+        <v>1.731</v>
+      </c>
+      <c r="L99">
+        <v>1.769</v>
+      </c>
+      <c r="M99">
+        <v>11.350164</v>
+      </c>
+      <c r="N99">
+        <v>-9.581164000000001</v>
+      </c>
+      <c r="O99">
+        <v>-2.10785608</v>
+      </c>
+      <c r="P99">
+        <v>-7.473307920000001</v>
+      </c>
+      <c r="Q99">
+        <v>-5.742307920000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.878611443311661</v>
+      </c>
+      <c r="T99">
+        <v>22.27022869341071</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03428849133809872</v>
+      </c>
+      <c r="W99">
+        <v>0.230611908268462</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1558567788095396</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.282051894319758</v>
+      </c>
+      <c r="C100">
+        <v>-35.63846186558601</v>
+      </c>
+      <c r="D100">
+        <v>11.94453813441399</v>
+      </c>
+      <c r="E100">
+        <v>36.52</v>
+      </c>
+      <c r="F100">
+        <v>48.02</v>
+      </c>
+      <c r="G100">
+        <v>0.437</v>
+      </c>
+      <c r="H100">
+        <v>37.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.5</v>
+      </c>
+      <c r="K100">
+        <v>1.731</v>
+      </c>
+      <c r="L100">
+        <v>1.769</v>
+      </c>
+      <c r="M100">
+        <v>11.467176</v>
+      </c>
+      <c r="N100">
+        <v>-9.698176</v>
+      </c>
+      <c r="O100">
+        <v>-2.13359872</v>
+      </c>
+      <c r="P100">
+        <v>-7.56457728</v>
+      </c>
+      <c r="Q100">
+        <v>-5.83357728</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.798517164967491</v>
+      </c>
+      <c r="T100">
+        <v>33.40534304011607</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03393860877342424</v>
+      </c>
+      <c r="W100">
+        <v>0.2306954602249063</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1542664035155648</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.284051894319758</v>
+      </c>
+      <c r="C101">
+        <v>-36.22586815202914</v>
+      </c>
+      <c r="D101">
+        <v>11.84713184797087</v>
+      </c>
+      <c r="E101">
+        <v>37.01</v>
+      </c>
+      <c r="F101">
+        <v>48.51</v>
+      </c>
+      <c r="G101">
+        <v>0.437</v>
+      </c>
+      <c r="H101">
+        <v>37.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.5</v>
+      </c>
+      <c r="K101">
+        <v>1.731</v>
+      </c>
+      <c r="L101">
+        <v>1.769</v>
+      </c>
+      <c r="M101">
+        <v>11.584188</v>
+      </c>
+      <c r="N101">
+        <v>-9.815187999999999</v>
+      </c>
+      <c r="O101">
+        <v>-2.15934136</v>
+      </c>
+      <c r="P101">
+        <v>-7.655846639999999</v>
+      </c>
+      <c r="Q101">
+        <v>-5.924846639999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.558234329934981</v>
+      </c>
+      <c r="T101">
+        <v>66.81068608023213</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03359579454338966</v>
+      </c>
+      <c r="W101">
+        <v>0.2307773242630386</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1527081570154075</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/greece/greece_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09882492159389236</v>
+        <v>0.0986426067663858</v>
       </c>
       <c r="C2">
-        <v>50.13122552147592</v>
+        <v>49.81400991633681</v>
       </c>
       <c r="D2">
-        <v>48.34122552147592</v>
+        <v>48.50800991633681</v>
       </c>
       <c r="E2">
-        <v>-13.7</v>
+        <v>-13.216</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.484</v>
       </c>
       <c r="G2">
         <v>1.79</v>
@@ -1451,28 +1451,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0243452</v>
       </c>
       <c r="N2">
-        <v>2.233000000000001</v>
+        <v>2.208654800000001</v>
       </c>
       <c r="O2">
-        <v>0.4912600000000001</v>
+        <v>0.4859040560000001</v>
       </c>
       <c r="P2">
-        <v>1.741740000000001</v>
+        <v>1.722750744000001</v>
       </c>
       <c r="Q2">
-        <v>3.808740000000001</v>
+        <v>3.789750744000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09882492159389236</v>
+        <v>0.09924269370342</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6965374549757971</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>91.72239291523587</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0986426067663858</v>
+        <v>0.09846029193887923</v>
       </c>
       <c r="C3">
-        <v>49.81400991633681</v>
+        <v>49.49794915736586</v>
       </c>
       <c r="D3">
-        <v>48.50800991633681</v>
+        <v>48.67594915736586</v>
       </c>
       <c r="E3">
-        <v>-13.216</v>
+        <v>-12.732</v>
       </c>
       <c r="F3">
-        <v>0.484</v>
+        <v>0.9680000000000001</v>
       </c>
       <c r="G3">
         <v>1.79</v>
@@ -1533,28 +1533,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0243452</v>
+        <v>0.0486904</v>
       </c>
       <c r="N3">
-        <v>2.208654800000001</v>
+        <v>2.184309600000001</v>
       </c>
       <c r="O3">
-        <v>0.4859040560000001</v>
+        <v>0.4805481120000001</v>
       </c>
       <c r="P3">
-        <v>1.722750744000001</v>
+        <v>1.703761488</v>
       </c>
       <c r="Q3">
-        <v>3.789750744000001</v>
+        <v>3.770761488000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09924269370342</v>
+        <v>0.09966899177436657</v>
       </c>
       <c r="T3">
-        <v>0.6965374549757971</v>
+        <v>0.7020935479198774</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>91.72239291523587</v>
+        <v>45.86119645761794</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09846029193887923</v>
+        <v>0.09827797711137268</v>
       </c>
       <c r="C4">
-        <v>49.49794915736586</v>
+        <v>49.18305528078807</v>
       </c>
       <c r="D4">
-        <v>48.67594915736586</v>
+        <v>48.84505528078807</v>
       </c>
       <c r="E4">
-        <v>-12.732</v>
+        <v>-12.248</v>
       </c>
       <c r="F4">
-        <v>0.9680000000000001</v>
+        <v>1.452</v>
       </c>
       <c r="G4">
         <v>1.79</v>
@@ -1615,28 +1615,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M4">
-        <v>0.0486904</v>
+        <v>0.07303560000000001</v>
       </c>
       <c r="N4">
-        <v>2.184309600000001</v>
+        <v>2.159964400000001</v>
       </c>
       <c r="O4">
-        <v>0.4805481120000001</v>
+        <v>0.4751921680000001</v>
       </c>
       <c r="P4">
-        <v>1.703761488</v>
+        <v>1.684772232</v>
       </c>
       <c r="Q4">
-        <v>3.770761488000001</v>
+        <v>3.751772232</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09966899177436657</v>
+        <v>0.1001040794962605</v>
       </c>
       <c r="T4">
-        <v>0.7020935479198774</v>
+        <v>0.7077641994813614</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>45.86119645761794</v>
+        <v>30.57413097174529</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09827797711137268</v>
+        <v>0.09809566228386611</v>
       </c>
       <c r="C5">
-        <v>49.18305528078807</v>
+        <v>48.86934049067273</v>
       </c>
       <c r="D5">
-        <v>48.84505528078807</v>
+        <v>49.01534049067273</v>
       </c>
       <c r="E5">
-        <v>-12.248</v>
+        <v>-11.764</v>
       </c>
       <c r="F5">
-        <v>1.452</v>
+        <v>1.936</v>
       </c>
       <c r="G5">
         <v>1.79</v>
@@ -1697,28 +1697,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M5">
-        <v>0.07303560000000001</v>
+        <v>0.0973808</v>
       </c>
       <c r="N5">
-        <v>2.159964400000001</v>
+        <v>2.135619200000001</v>
       </c>
       <c r="O5">
-        <v>0.4751921680000001</v>
+        <v>0.4698362240000001</v>
       </c>
       <c r="P5">
-        <v>1.684772232</v>
+        <v>1.665782976</v>
       </c>
       <c r="Q5">
-        <v>3.751772232</v>
+        <v>3.732782976000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1001040794962605</v>
+        <v>0.1005482315456939</v>
       </c>
       <c r="T5">
-        <v>0.7077641994813614</v>
+        <v>0.7135529896170429</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>30.57413097174529</v>
+        <v>22.93059822880897</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09809566228386611</v>
+        <v>0.09791334745635955</v>
       </c>
       <c r="C6">
-        <v>48.86934049067273</v>
+        <v>48.5568171618694</v>
       </c>
       <c r="D6">
-        <v>49.01534049067273</v>
+        <v>49.18681716186941</v>
       </c>
       <c r="E6">
-        <v>-11.764</v>
+        <v>-11.28</v>
       </c>
       <c r="F6">
-        <v>1.936</v>
+        <v>2.42</v>
       </c>
       <c r="G6">
         <v>1.79</v>
@@ -1779,28 +1779,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M6">
-        <v>0.0973808</v>
+        <v>0.121726</v>
       </c>
       <c r="N6">
-        <v>2.135619200000001</v>
+        <v>2.111274</v>
       </c>
       <c r="O6">
-        <v>0.4698362240000001</v>
+        <v>0.4644802800000001</v>
       </c>
       <c r="P6">
-        <v>1.665782976</v>
+        <v>1.64679372</v>
       </c>
       <c r="Q6">
-        <v>3.732782976000001</v>
+        <v>3.71379372</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1005482315456939</v>
+        <v>0.101001734164589</v>
       </c>
       <c r="T6">
-        <v>0.7135529896170429</v>
+        <v>0.7194636490187389</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>22.93059822880897</v>
+        <v>18.34447858304717</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09791334745635955</v>
+        <v>0.09773103262885298</v>
       </c>
       <c r="C7">
-        <v>48.5568171618694</v>
+        <v>48.24549784300573</v>
       </c>
       <c r="D7">
-        <v>49.18681716186941</v>
+        <v>49.35949784300573</v>
       </c>
       <c r="E7">
-        <v>-11.28</v>
+        <v>-10.796</v>
       </c>
       <c r="F7">
-        <v>2.42</v>
+        <v>2.904</v>
       </c>
       <c r="G7">
         <v>1.79</v>
@@ -1861,28 +1861,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M7">
-        <v>0.121726</v>
+        <v>0.1460712</v>
       </c>
       <c r="N7">
-        <v>2.111274</v>
+        <v>2.0869288</v>
       </c>
       <c r="O7">
-        <v>0.4644802800000001</v>
+        <v>0.4591243360000001</v>
       </c>
       <c r="P7">
-        <v>1.64679372</v>
+        <v>1.627804464</v>
       </c>
       <c r="Q7">
-        <v>3.71379372</v>
+        <v>3.694804464000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.101001734164589</v>
+        <v>0.1014648857753755</v>
       </c>
       <c r="T7">
-        <v>0.7194636490187389</v>
+        <v>0.7255000671311091</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.34447858304717</v>
+        <v>15.28706548587264</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09773103262885298</v>
+        <v>0.09754871780134644</v>
       </c>
       <c r="C8">
-        <v>48.24549784300573</v>
+        <v>47.93539525954854</v>
       </c>
       <c r="D8">
-        <v>49.35949784300573</v>
+        <v>49.53339525954854</v>
       </c>
       <c r="E8">
-        <v>-10.796</v>
+        <v>-10.312</v>
       </c>
       <c r="F8">
-        <v>2.904</v>
+        <v>3.388</v>
       </c>
       <c r="G8">
         <v>1.79</v>
@@ -1943,28 +1943,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M8">
-        <v>0.1460712</v>
+        <v>0.1704164</v>
       </c>
       <c r="N8">
-        <v>2.0869288</v>
+        <v>2.0625836</v>
       </c>
       <c r="O8">
-        <v>0.4591243360000001</v>
+        <v>0.4537683920000001</v>
       </c>
       <c r="P8">
-        <v>1.627804464</v>
+        <v>1.608815208</v>
       </c>
       <c r="Q8">
-        <v>3.694804464000001</v>
+        <v>3.675815208</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1014648857753755</v>
+        <v>0.1019379976358564</v>
       </c>
       <c r="T8">
-        <v>0.7255000671311091</v>
+        <v>0.7316663006867562</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.28706548587264</v>
+        <v>13.10319898789084</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09754871780134643</v>
+        <v>0.09746000297383986</v>
       </c>
       <c r="C9">
-        <v>47.93539525954856</v>
+        <v>47.53645810049517</v>
       </c>
       <c r="D9">
-        <v>49.53339525954856</v>
+        <v>49.61845810049517</v>
       </c>
       <c r="E9">
-        <v>-10.312</v>
+        <v>-9.827999999999999</v>
       </c>
       <c r="F9">
-        <v>3.388000000000001</v>
+        <v>3.872</v>
       </c>
       <c r="G9">
         <v>1.79</v>
@@ -2025,45 +2025,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M9">
-        <v>0.1704164</v>
+        <v>0.2005696</v>
       </c>
       <c r="N9">
-        <v>2.0625836</v>
+        <v>2.0324304</v>
       </c>
       <c r="O9">
-        <v>0.4537683920000001</v>
+        <v>0.4471346880000001</v>
       </c>
       <c r="P9">
-        <v>1.608815208</v>
+        <v>1.585295712</v>
       </c>
       <c r="Q9">
-        <v>3.675815208</v>
+        <v>3.652295712</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1019379976358564</v>
+        <v>0.1024213945367825</v>
       </c>
       <c r="T9">
-        <v>0.7316663006867563</v>
+        <v>0.7379665827979608</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.10319898789084</v>
+        <v>11.13329238329239</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09746000297383986</v>
+        <v>0.09728938814633331</v>
       </c>
       <c r="C10">
-        <v>47.53645810049517</v>
+        <v>47.21687342906534</v>
       </c>
       <c r="D10">
-        <v>49.61845810049517</v>
+        <v>49.78287342906535</v>
       </c>
       <c r="E10">
-        <v>-9.827999999999999</v>
+        <v>-9.343999999999998</v>
       </c>
       <c r="F10">
-        <v>3.872</v>
+        <v>4.356000000000001</v>
       </c>
       <c r="G10">
         <v>1.79</v>
@@ -2107,28 +2107,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M10">
-        <v>0.2005696</v>
+        <v>0.2256408</v>
       </c>
       <c r="N10">
-        <v>2.0324304</v>
+        <v>2.007359200000001</v>
       </c>
       <c r="O10">
-        <v>0.4471346880000001</v>
+        <v>0.4416190240000001</v>
       </c>
       <c r="P10">
-        <v>1.585295712</v>
+        <v>1.565740176</v>
       </c>
       <c r="Q10">
-        <v>3.652295712</v>
+        <v>3.632740176</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1024213945367825</v>
+        <v>0.1029154155454212</v>
       </c>
       <c r="T10">
-        <v>0.7379665827979608</v>
+        <v>0.7444053326478733</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.13329238329239</v>
+        <v>9.896259896259899</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09728938814633331</v>
+        <v>0.09725137331882673</v>
       </c>
       <c r="C11">
-        <v>47.21687342906534</v>
+        <v>46.76965548606626</v>
       </c>
       <c r="D11">
-        <v>49.78287342906535</v>
+        <v>49.81965548606625</v>
       </c>
       <c r="E11">
-        <v>-9.343999999999998</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="F11">
-        <v>4.356000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="G11">
         <v>1.79</v>
@@ -2189,45 +2189,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M11">
-        <v>0.2256408</v>
+        <v>0.25894</v>
       </c>
       <c r="N11">
-        <v>2.007359200000001</v>
+        <v>1.974060000000001</v>
       </c>
       <c r="O11">
-        <v>0.4416190240000001</v>
+        <v>0.4342932000000002</v>
       </c>
       <c r="P11">
-        <v>1.565740176</v>
+        <v>1.5397668</v>
       </c>
       <c r="Q11">
-        <v>3.632740176</v>
+        <v>3.606766800000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1029154155454212</v>
+        <v>0.1034204147986964</v>
       </c>
       <c r="T11">
-        <v>0.7444053326478733</v>
+        <v>0.7509871658277837</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.896259896259899</v>
+        <v>8.623619371282924</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09725137331882673</v>
+        <v>0.09709401849132018</v>
       </c>
       <c r="C12">
-        <v>46.76965548606625</v>
+        <v>46.438487405382</v>
       </c>
       <c r="D12">
-        <v>49.81965548606625</v>
+        <v>49.972487405382</v>
       </c>
       <c r="E12">
-        <v>-8.859999999999999</v>
+        <v>-8.375999999999998</v>
       </c>
       <c r="F12">
-        <v>4.840000000000001</v>
+        <v>5.324000000000001</v>
       </c>
       <c r="G12">
         <v>1.79</v>
@@ -2271,28 +2271,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M12">
-        <v>0.2589400000000001</v>
+        <v>0.284834</v>
       </c>
       <c r="N12">
-        <v>1.974060000000001</v>
+        <v>1.948166000000001</v>
       </c>
       <c r="O12">
-        <v>0.4342932000000002</v>
+        <v>0.4285965200000001</v>
       </c>
       <c r="P12">
-        <v>1.5397668</v>
+        <v>1.51956948</v>
       </c>
       <c r="Q12">
-        <v>3.606766800000001</v>
+        <v>3.586569480000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1034204147986964</v>
+        <v>0.103936762349798</v>
       </c>
       <c r="T12">
-        <v>0.7509871658277837</v>
+        <v>0.7577169053712878</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.623619371282924</v>
+        <v>7.839653973893567</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09709401849132018</v>
+        <v>0.09701154366381361</v>
       </c>
       <c r="C13">
-        <v>46.438487405382</v>
+        <v>46.03496676577561</v>
       </c>
       <c r="D13">
-        <v>49.972487405382</v>
+        <v>50.05296676577561</v>
       </c>
       <c r="E13">
-        <v>-8.375999999999998</v>
+        <v>-7.891999999999999</v>
       </c>
       <c r="F13">
-        <v>5.324000000000001</v>
+        <v>5.808000000000001</v>
       </c>
       <c r="G13">
         <v>1.79</v>
@@ -2353,45 +2353,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M13">
-        <v>0.284834</v>
+        <v>0.3153744000000001</v>
       </c>
       <c r="N13">
-        <v>1.948166000000001</v>
+        <v>1.9176256</v>
       </c>
       <c r="O13">
-        <v>0.4285965200000001</v>
+        <v>0.4218776320000001</v>
       </c>
       <c r="P13">
-        <v>1.51956948</v>
+        <v>1.495747968</v>
       </c>
       <c r="Q13">
-        <v>3.586569480000001</v>
+        <v>3.562747968</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.103936762349798</v>
+        <v>0.1044648450725155</v>
       </c>
       <c r="T13">
-        <v>0.7577169053712878</v>
+        <v>0.7645995935407804</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.839653973893567</v>
+        <v>7.080473240694236</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09701154366381361</v>
+        <v>0.09686042883630704</v>
       </c>
       <c r="C14">
-        <v>46.03496676577561</v>
+        <v>45.69909997991783</v>
       </c>
       <c r="D14">
-        <v>50.05296676577561</v>
+        <v>50.20109997991783</v>
       </c>
       <c r="E14">
-        <v>-7.891999999999999</v>
+        <v>-7.407999999999999</v>
       </c>
       <c r="F14">
-        <v>5.808000000000001</v>
+        <v>6.292000000000001</v>
       </c>
       <c r="G14">
         <v>1.79</v>
@@ -2435,28 +2435,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M14">
-        <v>0.3153744000000001</v>
+        <v>0.3416556000000001</v>
       </c>
       <c r="N14">
-        <v>1.9176256</v>
+        <v>1.8913444</v>
       </c>
       <c r="O14">
-        <v>0.4218776320000001</v>
+        <v>0.4160957680000001</v>
       </c>
       <c r="P14">
-        <v>1.495747968</v>
+        <v>1.475248632</v>
       </c>
       <c r="Q14">
-        <v>3.562747968</v>
+        <v>3.542248632000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1044648450725155</v>
+        <v>0.1050050676279391</v>
       </c>
       <c r="T14">
-        <v>0.7645995935407804</v>
+        <v>0.7716405044268131</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.080473240694236</v>
+        <v>6.535821452948525</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09686042883630704</v>
+        <v>0.09681851400880048</v>
       </c>
       <c r="C15">
-        <v>45.69909997991783</v>
+        <v>45.25634325183935</v>
       </c>
       <c r="D15">
-        <v>50.20109997991783</v>
+        <v>50.24234325183936</v>
       </c>
       <c r="E15">
-        <v>-7.407999999999999</v>
+        <v>-6.923999999999998</v>
       </c>
       <c r="F15">
-        <v>6.292000000000001</v>
+        <v>6.776000000000002</v>
       </c>
       <c r="G15">
         <v>1.79</v>
@@ -2517,45 +2517,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M15">
-        <v>0.3416556000000001</v>
+        <v>0.3747128000000001</v>
       </c>
       <c r="N15">
-        <v>1.8913444</v>
+        <v>1.8582872</v>
       </c>
       <c r="O15">
-        <v>0.4160957680000001</v>
+        <v>0.4088231840000001</v>
       </c>
       <c r="P15">
-        <v>1.475248632</v>
+        <v>1.449464016</v>
       </c>
       <c r="Q15">
-        <v>3.542248632000001</v>
+        <v>3.516464016</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1050050676279391</v>
+        <v>0.1055578534986052</v>
       </c>
       <c r="T15">
-        <v>0.7716405044268131</v>
+        <v>0.7788451574264745</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.535821452948525</v>
+        <v>5.959230642774946</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09681851400880048</v>
+        <v>0.09667519918129391</v>
       </c>
       <c r="C16">
-        <v>45.25634325183935</v>
+        <v>44.91387533176309</v>
       </c>
       <c r="D16">
-        <v>50.24234325183936</v>
+        <v>50.3838753317631</v>
       </c>
       <c r="E16">
-        <v>-6.923999999999998</v>
+        <v>-6.439999999999998</v>
       </c>
       <c r="F16">
-        <v>6.776000000000002</v>
+        <v>7.260000000000002</v>
       </c>
       <c r="G16">
         <v>1.79</v>
@@ -2599,28 +2599,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M16">
-        <v>0.3747128000000001</v>
+        <v>0.4014780000000001</v>
       </c>
       <c r="N16">
-        <v>1.8582872</v>
+        <v>1.831522000000001</v>
       </c>
       <c r="O16">
-        <v>0.4088231840000001</v>
+        <v>0.4029348400000001</v>
       </c>
       <c r="P16">
-        <v>1.449464016</v>
+        <v>1.42858716</v>
       </c>
       <c r="Q16">
-        <v>3.516464016</v>
+        <v>3.49558716</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1055578534986052</v>
+        <v>0.1061236460956399</v>
       </c>
       <c r="T16">
-        <v>0.7788451574264745</v>
+        <v>0.7862193316731868</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.959230642774946</v>
+        <v>5.561948599923284</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09667519918129391</v>
+        <v>0.09653188435378733</v>
       </c>
       <c r="C17">
-        <v>44.9138753317631</v>
+        <v>44.57220705261797</v>
       </c>
       <c r="D17">
-        <v>50.3838753317631</v>
+        <v>50.52620705261797</v>
       </c>
       <c r="E17">
-        <v>-6.439999999999999</v>
+        <v>-5.955999999999999</v>
       </c>
       <c r="F17">
-        <v>7.260000000000001</v>
+        <v>7.744000000000001</v>
       </c>
       <c r="G17">
         <v>1.79</v>
@@ -2681,28 +2681,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M17">
-        <v>0.4014780000000001</v>
+        <v>0.4282432</v>
       </c>
       <c r="N17">
-        <v>1.831522000000001</v>
+        <v>1.8047568</v>
       </c>
       <c r="O17">
-        <v>0.4029348400000001</v>
+        <v>0.3970464960000001</v>
       </c>
       <c r="P17">
-        <v>1.42858716</v>
+        <v>1.407710304</v>
       </c>
       <c r="Q17">
-        <v>3.49558716</v>
+        <v>3.474710304</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1061236460956399</v>
+        <v>0.1067029099449849</v>
       </c>
       <c r="T17">
-        <v>0.7862193316731868</v>
+        <v>0.7937690814972017</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.561948599923284</v>
+        <v>5.214326812428079</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09653188435378733</v>
+        <v>0.09638856952628079</v>
       </c>
       <c r="C18">
-        <v>44.57220705261797</v>
+        <v>44.23134521042937</v>
       </c>
       <c r="D18">
-        <v>50.52620705261797</v>
+        <v>50.66934521042938</v>
       </c>
       <c r="E18">
-        <v>-5.955999999999999</v>
+        <v>-5.471999999999998</v>
       </c>
       <c r="F18">
-        <v>7.744000000000001</v>
+        <v>8.228000000000002</v>
       </c>
       <c r="G18">
         <v>1.79</v>
@@ -2763,28 +2763,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M18">
-        <v>0.4282432</v>
+        <v>0.4550084000000001</v>
       </c>
       <c r="N18">
-        <v>1.8047568</v>
+        <v>1.7779916</v>
       </c>
       <c r="O18">
-        <v>0.3970464960000001</v>
+        <v>0.3911581520000001</v>
       </c>
       <c r="P18">
-        <v>1.407710304</v>
+        <v>1.386833448</v>
       </c>
       <c r="Q18">
-        <v>3.474710304</v>
+        <v>3.453833448000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1067029099449849</v>
+        <v>0.1072961319593745</v>
       </c>
       <c r="T18">
-        <v>0.7937690814972017</v>
+        <v>0.8015007530037231</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.214326812428079</v>
+        <v>4.907601705814661</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09638856952628079</v>
+        <v>0.09624525469877422</v>
       </c>
       <c r="C19">
-        <v>44.23134521042937</v>
+        <v>43.89129667845278</v>
       </c>
       <c r="D19">
-        <v>50.66934521042938</v>
+        <v>50.81329667845279</v>
       </c>
       <c r="E19">
-        <v>-5.471999999999998</v>
+        <v>-4.987999999999998</v>
       </c>
       <c r="F19">
-        <v>8.228000000000002</v>
+        <v>8.712000000000002</v>
       </c>
       <c r="G19">
         <v>1.79</v>
@@ -2845,28 +2845,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M19">
-        <v>0.4550084000000001</v>
+        <v>0.4817736000000001</v>
       </c>
       <c r="N19">
-        <v>1.7779916</v>
+        <v>1.7512264</v>
       </c>
       <c r="O19">
-        <v>0.3911581520000001</v>
+        <v>0.3852698080000001</v>
       </c>
       <c r="P19">
-        <v>1.386833448</v>
+        <v>1.365956592</v>
       </c>
       <c r="Q19">
-        <v>3.453833448000001</v>
+        <v>3.432956592</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1072961319593745</v>
+        <v>0.1079038228033832</v>
       </c>
       <c r="T19">
-        <v>0.8015007530037231</v>
+        <v>0.8094210018640621</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.907601705814661</v>
+        <v>4.634957166602737</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09624525469877424</v>
+        <v>0.09647243987126766</v>
       </c>
       <c r="C20">
-        <v>43.89129667845278</v>
+        <v>43.17947998756159</v>
       </c>
       <c r="D20">
-        <v>50.81329667845278</v>
+        <v>50.5854799875616</v>
       </c>
       <c r="E20">
-        <v>-4.987999999999998</v>
+        <v>-4.503999999999998</v>
       </c>
       <c r="F20">
-        <v>8.712000000000002</v>
+        <v>9.196000000000002</v>
       </c>
       <c r="G20">
         <v>1.79</v>
@@ -2927,45 +2927,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M20">
-        <v>0.4817736000000001</v>
+        <v>0.5315288000000001</v>
       </c>
       <c r="N20">
-        <v>1.7512264</v>
+        <v>1.7014712</v>
       </c>
       <c r="O20">
-        <v>0.3852698080000001</v>
+        <v>0.3743236640000001</v>
       </c>
       <c r="P20">
-        <v>1.365956592</v>
+        <v>1.327147536</v>
       </c>
       <c r="Q20">
-        <v>3.432956592</v>
+        <v>3.394147536</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1079038228033832</v>
+        <v>0.1085265183595897</v>
       </c>
       <c r="T20">
-        <v>0.809421001864062</v>
+        <v>0.8175368124246561</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.634957166602737</v>
+        <v>4.201089385937319</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09647243987126766</v>
+        <v>0.09689462504376112</v>
       </c>
       <c r="C21">
-        <v>43.17947998756159</v>
+        <v>42.27750178386754</v>
       </c>
       <c r="D21">
-        <v>50.5854799875616</v>
+        <v>50.16750178386754</v>
       </c>
       <c r="E21">
-        <v>-4.503999999999998</v>
+        <v>-4.019999999999998</v>
       </c>
       <c r="F21">
-        <v>9.196000000000002</v>
+        <v>9.680000000000001</v>
       </c>
       <c r="G21">
         <v>1.79</v>
@@ -3009,45 +3009,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M21">
-        <v>0.5315288000000001</v>
+        <v>0.5933840000000001</v>
       </c>
       <c r="N21">
-        <v>1.7014712</v>
+        <v>1.639616</v>
       </c>
       <c r="O21">
-        <v>0.3743236640000001</v>
+        <v>0.3607155200000001</v>
       </c>
       <c r="P21">
-        <v>1.327147536</v>
+        <v>1.27890048</v>
       </c>
       <c r="Q21">
-        <v>3.394147536</v>
+        <v>3.345900480000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1085265183595897</v>
+        <v>0.1091647813047014</v>
       </c>
       <c r="T21">
-        <v>0.8175368124246561</v>
+        <v>0.8258555182492653</v>
       </c>
       <c r="U21">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.201089385937319</v>
+        <v>3.763161797419546</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09689462504376112</v>
+        <v>0.09679811021625453</v>
       </c>
       <c r="C22">
-        <v>42.27750178386754</v>
+        <v>41.88844467019361</v>
       </c>
       <c r="D22">
-        <v>50.16750178386754</v>
+        <v>50.26244467019361</v>
       </c>
       <c r="E22">
-        <v>-4.019999999999998</v>
+        <v>-3.535999999999998</v>
       </c>
       <c r="F22">
-        <v>9.680000000000001</v>
+        <v>10.164</v>
       </c>
       <c r="G22">
         <v>1.79</v>
@@ -3091,28 +3091,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M22">
-        <v>0.5933840000000001</v>
+        <v>0.6230532000000001</v>
       </c>
       <c r="N22">
-        <v>1.639616</v>
+        <v>1.6099468</v>
       </c>
       <c r="O22">
-        <v>0.3607155200000001</v>
+        <v>0.3541882960000001</v>
       </c>
       <c r="P22">
-        <v>1.27890048</v>
+        <v>1.255758504</v>
       </c>
       <c r="Q22">
-        <v>3.345900480000001</v>
+        <v>3.322758504</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1091647813047014</v>
+        <v>0.1098192028053855</v>
       </c>
       <c r="T22">
-        <v>0.8258555182492653</v>
+        <v>0.8343848242213329</v>
       </c>
       <c r="U22">
         <v>0.0613</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.763161797419546</v>
+        <v>3.583963616590044</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09679811021625453</v>
+        <v>0.09718207538874798</v>
       </c>
       <c r="C23">
-        <v>41.88844467019361</v>
+        <v>41.02884621311065</v>
       </c>
       <c r="D23">
-        <v>50.26244467019361</v>
+        <v>49.88684621311066</v>
       </c>
       <c r="E23">
-        <v>-3.535999999999998</v>
+        <v>-3.051999999999998</v>
       </c>
       <c r="F23">
-        <v>10.164</v>
+        <v>10.648</v>
       </c>
       <c r="G23">
         <v>1.79</v>
@@ -3173,45 +3173,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M23">
-        <v>0.6230532000000001</v>
+        <v>0.6825368000000002</v>
       </c>
       <c r="N23">
-        <v>1.6099468</v>
+        <v>1.5504632</v>
       </c>
       <c r="O23">
-        <v>0.3541882960000001</v>
+        <v>0.3411019040000001</v>
       </c>
       <c r="P23">
-        <v>1.255758504</v>
+        <v>1.209361296</v>
       </c>
       <c r="Q23">
-        <v>3.322758504</v>
+        <v>3.276361296</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1098192028053855</v>
+        <v>0.1104904043445487</v>
       </c>
       <c r="T23">
-        <v>0.8343848242213326</v>
+        <v>0.8431328303465302</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.583963616590044</v>
+        <v>3.271618468044507</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09718207538874798</v>
+        <v>0.09710740056124141</v>
       </c>
       <c r="C24">
-        <v>41.02884621311065</v>
+        <v>40.61745350942778</v>
       </c>
       <c r="D24">
-        <v>49.88684621311066</v>
+        <v>49.95945350942777</v>
       </c>
       <c r="E24">
-        <v>-3.051999999999998</v>
+        <v>-2.567999999999998</v>
       </c>
       <c r="F24">
-        <v>10.648</v>
+        <v>11.132</v>
       </c>
       <c r="G24">
         <v>1.79</v>
@@ -3255,28 +3255,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M24">
-        <v>0.6825368000000002</v>
+        <v>0.7135612000000001</v>
       </c>
       <c r="N24">
-        <v>1.5504632</v>
+        <v>1.519438800000001</v>
       </c>
       <c r="O24">
-        <v>0.3411019040000001</v>
+        <v>0.3342765360000001</v>
       </c>
       <c r="P24">
-        <v>1.209361296</v>
+        <v>1.185162264</v>
       </c>
       <c r="Q24">
-        <v>3.276361296</v>
+        <v>3.252162264000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1104904043445487</v>
+        <v>0.1111790396899239</v>
       </c>
       <c r="T24">
-        <v>0.8431328303465302</v>
+        <v>0.8521080574100445</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.271618468044507</v>
+        <v>3.129374186825181</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09710740056124141</v>
+        <v>0.09849288573373485</v>
       </c>
       <c r="C25">
-        <v>40.61745350942778</v>
+        <v>38.81984008516103</v>
       </c>
       <c r="D25">
-        <v>49.95945350942777</v>
+        <v>48.64584008516103</v>
       </c>
       <c r="E25">
-        <v>-2.567999999999998</v>
+        <v>-2.083999999999998</v>
       </c>
       <c r="F25">
-        <v>11.132</v>
+        <v>11.616</v>
       </c>
       <c r="G25">
         <v>1.79</v>
@@ -3337,45 +3337,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M25">
-        <v>0.7135612000000001</v>
+        <v>0.8351904000000002</v>
       </c>
       <c r="N25">
-        <v>1.519438800000001</v>
+        <v>1.3978096</v>
       </c>
       <c r="O25">
-        <v>0.3342765360000001</v>
+        <v>0.3075181120000001</v>
       </c>
       <c r="P25">
-        <v>1.185162264</v>
+        <v>1.090291488</v>
       </c>
       <c r="Q25">
-        <v>3.252162264000001</v>
+        <v>3.157291488</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1111790396899239</v>
+        <v>0.1118857970180722</v>
       </c>
       <c r="T25">
-        <v>0.8521080574100445</v>
+        <v>0.8613194746594407</v>
       </c>
       <c r="U25">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.129374186825181</v>
+        <v>2.673641842626544</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09849288573373485</v>
+        <v>0.09847905090622829</v>
       </c>
       <c r="C26">
-        <v>38.81984008516103</v>
+        <v>38.34861569130641</v>
       </c>
       <c r="D26">
-        <v>48.64584008516103</v>
+        <v>48.65861569130641</v>
       </c>
       <c r="E26">
-        <v>-2.083999999999998</v>
+        <v>-1.599999999999998</v>
       </c>
       <c r="F26">
-        <v>11.616</v>
+        <v>12.1</v>
       </c>
       <c r="G26">
         <v>1.79</v>
@@ -3419,28 +3419,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M26">
-        <v>0.8351904000000002</v>
+        <v>0.8699900000000002</v>
       </c>
       <c r="N26">
-        <v>1.3978096</v>
+        <v>1.36301</v>
       </c>
       <c r="O26">
-        <v>0.3075181120000001</v>
+        <v>0.2998622000000001</v>
       </c>
       <c r="P26">
-        <v>1.090291488</v>
+        <v>1.0631478</v>
       </c>
       <c r="Q26">
-        <v>3.157291488</v>
+        <v>3.1301478</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1118857970180722</v>
+        <v>0.1126114012083044</v>
       </c>
       <c r="T26">
-        <v>0.8613194746594407</v>
+        <v>0.8707765297021541</v>
       </c>
       <c r="U26">
         <v>0.07190000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.673641842626544</v>
+        <v>2.566696168921482</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09847905090622829</v>
+        <v>0.09925613607872172</v>
       </c>
       <c r="C27">
-        <v>38.34861569130641</v>
+        <v>37.15727147338375</v>
       </c>
       <c r="D27">
-        <v>48.65861569130641</v>
+        <v>47.95127147338376</v>
       </c>
       <c r="E27">
-        <v>-1.599999999999998</v>
+        <v>-1.115999999999998</v>
       </c>
       <c r="F27">
-        <v>12.1</v>
+        <v>12.584</v>
       </c>
       <c r="G27">
         <v>1.79</v>
@@ -3501,45 +3501,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M27">
-        <v>0.8699900000000002</v>
+        <v>0.9538672000000001</v>
       </c>
       <c r="N27">
-        <v>1.36301</v>
+        <v>1.2791328</v>
       </c>
       <c r="O27">
-        <v>0.2998622000000001</v>
+        <v>0.2814092160000001</v>
       </c>
       <c r="P27">
-        <v>1.0631478</v>
+        <v>0.9977235840000003</v>
       </c>
       <c r="Q27">
-        <v>3.1301478</v>
+        <v>3.064723584</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1126114012083044</v>
+        <v>0.1133566163225969</v>
       </c>
       <c r="T27">
-        <v>0.8707765297021541</v>
+        <v>0.8804891808271031</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.566696168921482</v>
+        <v>2.340996734136576</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09925613607872172</v>
+        <v>0.09927272125121517</v>
       </c>
       <c r="C28">
-        <v>37.15727147338375</v>
+        <v>36.65839884131907</v>
       </c>
       <c r="D28">
-        <v>47.95127147338376</v>
+        <v>47.93639884131908</v>
       </c>
       <c r="E28">
-        <v>-1.115999999999998</v>
+        <v>-0.6319999999999961</v>
       </c>
       <c r="F28">
-        <v>12.584</v>
+        <v>13.068</v>
       </c>
       <c r="G28">
         <v>1.79</v>
@@ -3583,28 +3583,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M28">
-        <v>0.9538672000000001</v>
+        <v>0.9905544000000003</v>
       </c>
       <c r="N28">
-        <v>1.2791328</v>
+        <v>1.2424456</v>
       </c>
       <c r="O28">
-        <v>0.2814092160000001</v>
+        <v>0.2733380320000001</v>
       </c>
       <c r="P28">
-        <v>0.9977235840000003</v>
+        <v>0.9691075680000003</v>
       </c>
       <c r="Q28">
-        <v>3.064723584</v>
+        <v>3.036107568</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1133566163225969</v>
+        <v>0.1141222482893358</v>
       </c>
       <c r="T28">
-        <v>0.8804891808271031</v>
+        <v>0.8904679319828726</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.340996734136576</v>
+        <v>2.254293151390777</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09927272125121517</v>
+        <v>0.0992893064237086</v>
       </c>
       <c r="C29">
-        <v>36.65839884131907</v>
+        <v>36.15953543222568</v>
       </c>
       <c r="D29">
-        <v>47.93639884131908</v>
+        <v>47.92153543222569</v>
       </c>
       <c r="E29">
-        <v>-0.6319999999999961</v>
+        <v>-0.1479999999999961</v>
       </c>
       <c r="F29">
-        <v>13.068</v>
+        <v>13.552</v>
       </c>
       <c r="G29">
         <v>1.79</v>
@@ -3665,28 +3665,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M29">
-        <v>0.9905544000000003</v>
+        <v>1.0272416</v>
       </c>
       <c r="N29">
-        <v>1.2424456</v>
+        <v>1.2057584</v>
       </c>
       <c r="O29">
-        <v>0.2733380320000001</v>
+        <v>0.2652668480000001</v>
       </c>
       <c r="P29">
-        <v>0.9691075680000003</v>
+        <v>0.9404915520000001</v>
       </c>
       <c r="Q29">
-        <v>3.036107568</v>
+        <v>3.007491552</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1141222482893358</v>
+        <v>0.1149091478107064</v>
       </c>
       <c r="T29">
-        <v>0.8904679319828726</v>
+        <v>0.9007238706707468</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.254293151390777</v>
+        <v>2.173782681698249</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0992893064237086</v>
+        <v>0.09930589159620204</v>
       </c>
       <c r="C30">
-        <v>36.15953543222568</v>
+        <v>35.66068123752705</v>
       </c>
       <c r="D30">
-        <v>47.92153543222569</v>
+        <v>47.90668123752705</v>
       </c>
       <c r="E30">
-        <v>-0.1479999999999961</v>
+        <v>0.3360000000000039</v>
       </c>
       <c r="F30">
-        <v>13.552</v>
+        <v>14.036</v>
       </c>
       <c r="G30">
         <v>1.79</v>
@@ -3747,28 +3747,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M30">
-        <v>1.0272416</v>
+        <v>1.0639288</v>
       </c>
       <c r="N30">
-        <v>1.2057584</v>
+        <v>1.1690712</v>
       </c>
       <c r="O30">
-        <v>0.2652668480000001</v>
+        <v>0.257195664</v>
       </c>
       <c r="P30">
-        <v>0.9404915520000001</v>
+        <v>0.9118755360000003</v>
       </c>
       <c r="Q30">
-        <v>3.007491552</v>
+        <v>2.978875536</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1149091478107064</v>
+        <v>0.1157182135157775</v>
       </c>
       <c r="T30">
-        <v>0.9007238706707468</v>
+        <v>0.9112687090399695</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.173782681698249</v>
+        <v>2.098824658191413</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09930589159620204</v>
+        <v>0.09932247676869546</v>
       </c>
       <c r="C31">
-        <v>35.66068123752705</v>
+        <v>35.16183624865732</v>
       </c>
       <c r="D31">
-        <v>47.90668123752705</v>
+        <v>47.89183624865733</v>
       </c>
       <c r="E31">
-        <v>0.3360000000000021</v>
+        <v>0.8200000000000021</v>
       </c>
       <c r="F31">
-        <v>14.036</v>
+        <v>14.52</v>
       </c>
       <c r="G31">
         <v>1.79</v>
@@ -3829,28 +3829,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M31">
-        <v>1.0639288</v>
+        <v>1.100616</v>
       </c>
       <c r="N31">
-        <v>1.1690712</v>
+        <v>1.132384</v>
       </c>
       <c r="O31">
-        <v>0.257195664</v>
+        <v>0.2491244800000001</v>
       </c>
       <c r="P31">
-        <v>0.9118755360000003</v>
+        <v>0.8832595200000002</v>
       </c>
       <c r="Q31">
-        <v>2.978875536</v>
+        <v>2.95025952</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1157182135157775</v>
+        <v>0.1165503953838507</v>
       </c>
       <c r="T31">
-        <v>0.9112687090399695</v>
+        <v>0.9221148285054558</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.098824658191413</v>
+        <v>2.028863836251699</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09932247676869546</v>
+        <v>0.1027726219411889</v>
       </c>
       <c r="C32">
-        <v>35.16183624865732</v>
+        <v>31.77760483916176</v>
       </c>
       <c r="D32">
-        <v>47.89183624865733</v>
+        <v>44.99160483916177</v>
       </c>
       <c r="E32">
-        <v>0.8200000000000021</v>
+        <v>1.304000000000002</v>
       </c>
       <c r="F32">
-        <v>14.52</v>
+        <v>15.004</v>
       </c>
       <c r="G32">
         <v>1.79</v>
@@ -3911,45 +3911,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M32">
-        <v>1.100616</v>
+        <v>1.35036</v>
       </c>
       <c r="N32">
-        <v>1.132384</v>
+        <v>0.8826400000000005</v>
       </c>
       <c r="O32">
-        <v>0.2491244800000001</v>
+        <v>0.1941808000000001</v>
       </c>
       <c r="P32">
-        <v>0.8832595200000002</v>
+        <v>0.6884592000000004</v>
       </c>
       <c r="Q32">
-        <v>2.95025952</v>
+        <v>2.755459200000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1165503953838507</v>
+        <v>0.1174066984654912</v>
       </c>
       <c r="T32">
-        <v>0.9221148285054558</v>
+        <v>0.933275328245304</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.028863836251699</v>
+        <v>1.653633105246009</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1027726219411889</v>
+        <v>0.1028999671136823</v>
       </c>
       <c r="C33">
-        <v>31.77760483916176</v>
+        <v>31.19326391133615</v>
       </c>
       <c r="D33">
-        <v>44.99160483916177</v>
+        <v>44.89126391133615</v>
       </c>
       <c r="E33">
-        <v>1.304000000000002</v>
+        <v>1.788000000000002</v>
       </c>
       <c r="F33">
-        <v>15.004</v>
+        <v>15.488</v>
       </c>
       <c r="G33">
         <v>1.79</v>
@@ -3993,28 +3993,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M33">
-        <v>1.35036</v>
+        <v>1.39392</v>
       </c>
       <c r="N33">
-        <v>0.8826400000000005</v>
+        <v>0.8390800000000005</v>
       </c>
       <c r="O33">
-        <v>0.1941808000000001</v>
+        <v>0.1845976000000001</v>
       </c>
       <c r="P33">
-        <v>0.6884592000000004</v>
+        <v>0.6544824000000004</v>
       </c>
       <c r="Q33">
-        <v>2.755459200000001</v>
+        <v>2.721482400000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1174066984654912</v>
+        <v>0.1182881869318858</v>
       </c>
       <c r="T33">
-        <v>0.933275328245304</v>
+        <v>0.9447640779775006</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.653633105246009</v>
+        <v>1.601957070707071</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1028999671136823</v>
+        <v>0.1030273122861758</v>
       </c>
       <c r="C34">
-        <v>31.19326391133615</v>
+        <v>30.60936955114587</v>
       </c>
       <c r="D34">
-        <v>44.89126391133615</v>
+        <v>44.79136955114587</v>
       </c>
       <c r="E34">
-        <v>1.788000000000002</v>
+        <v>2.272000000000004</v>
       </c>
       <c r="F34">
-        <v>15.488</v>
+        <v>15.972</v>
       </c>
       <c r="G34">
         <v>1.79</v>
@@ -4075,28 +4075,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M34">
-        <v>1.39392</v>
+        <v>1.43748</v>
       </c>
       <c r="N34">
-        <v>0.8390800000000005</v>
+        <v>0.7955200000000002</v>
       </c>
       <c r="O34">
-        <v>0.1845976000000001</v>
+        <v>0.1750144</v>
       </c>
       <c r="P34">
-        <v>0.6544824000000004</v>
+        <v>0.6205056000000002</v>
       </c>
       <c r="Q34">
-        <v>2.721482400000001</v>
+        <v>2.687505600000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1182881869318858</v>
+        <v>0.1191959884868295</v>
       </c>
       <c r="T34">
-        <v>0.9447640779775006</v>
+        <v>0.9565957754628971</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.601957070707071</v>
+        <v>1.553412917049281</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1030273122861758</v>
+        <v>0.1031546574586692</v>
       </c>
       <c r="C35">
-        <v>30.60936955114587</v>
+        <v>30.02591878403392</v>
       </c>
       <c r="D35">
-        <v>44.79136955114587</v>
+        <v>44.69191878403392</v>
       </c>
       <c r="E35">
-        <v>2.272000000000004</v>
+        <v>2.756000000000004</v>
       </c>
       <c r="F35">
-        <v>15.972</v>
+        <v>16.456</v>
       </c>
       <c r="G35">
         <v>1.79</v>
@@ -4157,28 +4157,28 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M35">
-        <v>1.43748</v>
+        <v>1.48104</v>
       </c>
       <c r="N35">
-        <v>0.7955200000000002</v>
+        <v>0.7519600000000004</v>
       </c>
       <c r="O35">
-        <v>0.1750144</v>
+        <v>0.1654312000000001</v>
       </c>
       <c r="P35">
-        <v>0.6205056000000002</v>
+        <v>0.5865288000000003</v>
       </c>
       <c r="Q35">
-        <v>2.687505600000001</v>
+        <v>2.653528800000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1191959884868295</v>
+        <v>0.1201312991798018</v>
       </c>
       <c r="T35">
-        <v>0.9565957754628971</v>
+        <v>0.96878600923573</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.553412917049281</v>
+        <v>1.507724301841949</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1031546574586692</v>
+        <v>0.120358688936004</v>
       </c>
       <c r="C36">
-        <v>30.02591878403392</v>
+        <v>19.22948989726842</v>
       </c>
       <c r="D36">
-        <v>44.69191878403392</v>
+        <v>34.37948989726842</v>
       </c>
       <c r="E36">
-        <v>2.756000000000004</v>
+        <v>3.240000000000006</v>
       </c>
       <c r="F36">
-        <v>16.456</v>
+        <v>16.94</v>
       </c>
       <c r="G36">
         <v>1.79</v>
@@ -4239,45 +4239,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M36">
-        <v>1.48104</v>
+        <v>2.486792000000001</v>
       </c>
       <c r="N36">
-        <v>0.7519600000000004</v>
+        <v>-0.2537920000000002</v>
       </c>
       <c r="O36">
-        <v>0.1654312000000001</v>
+        <v>-0.05583424000000006</v>
       </c>
       <c r="P36">
-        <v>0.5865288000000003</v>
+        <v>-0.1979577600000002</v>
       </c>
       <c r="Q36">
-        <v>2.653528800000001</v>
+        <v>1.86904224</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1201312991798018</v>
+        <v>0.1217364445169293</v>
       </c>
       <c r="T36">
-        <v>0.96878600923573</v>
+        <v>0.9897064339095609</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.22</v>
+        <v>0.1975476839237057</v>
       </c>
       <c r="W36">
-        <v>0.0702</v>
+        <v>0.1178</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.507724301841949</v>
+        <v>0.897944017835026</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.120358688936004</v>
+        <v>0.121368688936004</v>
       </c>
       <c r="C37">
-        <v>19.22948989726842</v>
+        <v>18.28599688124366</v>
       </c>
       <c r="D37">
-        <v>34.37948989726842</v>
+        <v>33.91999688124366</v>
       </c>
       <c r="E37">
-        <v>3.240000000000006</v>
+        <v>3.724000000000004</v>
       </c>
       <c r="F37">
-        <v>16.94</v>
+        <v>17.424</v>
       </c>
       <c r="G37">
         <v>1.79</v>
@@ -4321,37 +4321,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M37">
-        <v>2.486792000000001</v>
+        <v>2.557843200000001</v>
       </c>
       <c r="N37">
-        <v>-0.2537920000000002</v>
+        <v>-0.3248432000000001</v>
       </c>
       <c r="O37">
-        <v>-0.05583424000000006</v>
+        <v>-0.07146550400000003</v>
       </c>
       <c r="P37">
-        <v>-0.1979577600000002</v>
+        <v>-0.2533776960000001</v>
       </c>
       <c r="Q37">
-        <v>1.86904224</v>
+        <v>1.813622304</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1217364445169293</v>
+        <v>0.1229229514625063</v>
       </c>
       <c r="T37">
-        <v>0.9897064339095609</v>
+        <v>1.005170596939398</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1975476839237057</v>
+        <v>0.1920602482591584</v>
       </c>
       <c r="W37">
-        <v>0.1178</v>
+        <v>0.1186055555555556</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.897944017835026</v>
+        <v>0.8730011284507198</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.121368688936004</v>
+        <v>0.122378688936004</v>
       </c>
       <c r="C38">
-        <v>18.28599688124366</v>
+        <v>17.35462441605708</v>
       </c>
       <c r="D38">
-        <v>33.91999688124366</v>
+        <v>33.47262441605708</v>
       </c>
       <c r="E38">
-        <v>3.724000000000004</v>
+        <v>4.208000000000002</v>
       </c>
       <c r="F38">
-        <v>17.424</v>
+        <v>17.908</v>
       </c>
       <c r="G38">
         <v>1.79</v>
@@ -4403,37 +4403,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M38">
-        <v>2.557843200000001</v>
+        <v>2.628894400000001</v>
       </c>
       <c r="N38">
-        <v>-0.3248432000000001</v>
+        <v>-0.3958944</v>
       </c>
       <c r="O38">
-        <v>-0.07146550400000003</v>
+        <v>-0.08709676799999999</v>
       </c>
       <c r="P38">
-        <v>-0.2533776960000001</v>
+        <v>-0.308797632</v>
       </c>
       <c r="Q38">
-        <v>1.813622304</v>
+        <v>1.758202368</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1229229514625063</v>
+        <v>0.1241471252952445</v>
       </c>
       <c r="T38">
-        <v>1.005170596939398</v>
+        <v>1.021125685779706</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1920602482591584</v>
+        <v>0.1868694307386405</v>
       </c>
       <c r="W38">
-        <v>0.1186055555555556</v>
+        <v>0.1193675675675676</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8730011284507198</v>
+        <v>0.849406503357457</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.122378688936004</v>
+        <v>0.123388688936004</v>
       </c>
       <c r="C39">
-        <v>17.35462441605708</v>
+        <v>16.43489916893888</v>
       </c>
       <c r="D39">
-        <v>33.47262441605708</v>
+        <v>33.03689916893888</v>
       </c>
       <c r="E39">
-        <v>4.208000000000002</v>
+        <v>4.692000000000004</v>
       </c>
       <c r="F39">
-        <v>17.908</v>
+        <v>18.392</v>
       </c>
       <c r="G39">
         <v>1.79</v>
@@ -4485,37 +4485,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M39">
-        <v>2.628894400000001</v>
+        <v>2.699945600000001</v>
       </c>
       <c r="N39">
-        <v>-0.3958944</v>
+        <v>-0.4669456000000003</v>
       </c>
       <c r="O39">
-        <v>-0.08709676799999999</v>
+        <v>-0.1027280320000001</v>
       </c>
       <c r="P39">
-        <v>-0.308797632</v>
+        <v>-0.3642175680000002</v>
       </c>
       <c r="Q39">
-        <v>1.758202368</v>
+        <v>1.702782432</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1241471252952445</v>
+        <v>0.1254107886064581</v>
       </c>
       <c r="T39">
-        <v>1.021125685779706</v>
+        <v>1.037595454905185</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1868694307386405</v>
+        <v>0.1819518141402553</v>
       </c>
       <c r="W39">
-        <v>0.1193675675675676</v>
+        <v>0.1200894736842105</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.849406503357457</v>
+        <v>0.8270537006375239</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.123388688936004</v>
+        <v>0.124398688936004</v>
       </c>
       <c r="C40">
-        <v>16.43489916893888</v>
+        <v>15.52637213658855</v>
       </c>
       <c r="D40">
-        <v>33.03689916893888</v>
+        <v>32.61237213658855</v>
       </c>
       <c r="E40">
-        <v>4.692000000000004</v>
+        <v>5.176000000000002</v>
       </c>
       <c r="F40">
-        <v>18.392</v>
+        <v>18.876</v>
       </c>
       <c r="G40">
         <v>1.79</v>
@@ -4567,37 +4567,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M40">
-        <v>2.699945600000001</v>
+        <v>2.7709968</v>
       </c>
       <c r="N40">
-        <v>-0.4669456000000003</v>
+        <v>-0.5379967999999997</v>
       </c>
       <c r="O40">
-        <v>-0.1027280320000001</v>
+        <v>-0.1183592959999999</v>
       </c>
       <c r="P40">
-        <v>-0.3642175680000002</v>
+        <v>-0.4196375039999998</v>
       </c>
       <c r="Q40">
-        <v>1.702782432</v>
+        <v>1.647362496</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1254107886064581</v>
+        <v>0.1267158835016459</v>
       </c>
       <c r="T40">
-        <v>1.037595454905185</v>
+        <v>1.054605216461007</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1819518141402553</v>
+        <v>0.1772863830084539</v>
       </c>
       <c r="W40">
-        <v>0.1200894736842105</v>
+        <v>0.120774358974359</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8270537006375239</v>
+        <v>0.8058471954929722</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.124398688936004</v>
+        <v>0.1479946279973883</v>
       </c>
       <c r="C41">
-        <v>15.52637213658855</v>
+        <v>7.512430879776144</v>
       </c>
       <c r="D41">
-        <v>32.61237213658855</v>
+        <v>25.08243087977615</v>
       </c>
       <c r="E41">
-        <v>5.176000000000002</v>
+        <v>5.660000000000004</v>
       </c>
       <c r="F41">
-        <v>18.876</v>
+        <v>19.36</v>
       </c>
       <c r="G41">
         <v>1.79</v>
@@ -4649,45 +4649,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M41">
-        <v>2.7709968</v>
+        <v>3.887488000000001</v>
       </c>
       <c r="N41">
-        <v>-0.5379967999999997</v>
+        <v>-1.654488</v>
       </c>
       <c r="O41">
-        <v>-0.1183592959999999</v>
+        <v>-0.36398736</v>
       </c>
       <c r="P41">
-        <v>-0.4196375039999998</v>
+        <v>-1.29050064</v>
       </c>
       <c r="Q41">
-        <v>1.647362496</v>
+        <v>0.7764993600000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1267158835016459</v>
+        <v>0.1297077133289806</v>
       </c>
       <c r="T41">
-        <v>1.054605216461007</v>
+        <v>1.093598788626682</v>
       </c>
       <c r="U41">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1772863830084539</v>
+        <v>0.1263695219123506</v>
       </c>
       <c r="W41">
-        <v>0.120774358974359</v>
+        <v>0.175425</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8058471954929722</v>
+        <v>0.5744069177834119</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1479946279973883</v>
+        <v>0.1495446279973884</v>
       </c>
       <c r="C42">
-        <v>7.512430879776144</v>
+        <v>6.653686002724459</v>
       </c>
       <c r="D42">
-        <v>25.08243087977615</v>
+        <v>24.70768600272446</v>
       </c>
       <c r="E42">
-        <v>5.660000000000004</v>
+        <v>6.144000000000005</v>
       </c>
       <c r="F42">
-        <v>19.36</v>
+        <v>19.844</v>
       </c>
       <c r="G42">
         <v>1.79</v>
@@ -4731,37 +4731,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M42">
-        <v>3.887488000000001</v>
+        <v>3.984675200000001</v>
       </c>
       <c r="N42">
-        <v>-1.654488</v>
+        <v>-1.751675200000001</v>
       </c>
       <c r="O42">
-        <v>-0.36398736</v>
+        <v>-0.3853685440000001</v>
       </c>
       <c r="P42">
-        <v>-1.29050064</v>
+        <v>-1.366306656000001</v>
       </c>
       <c r="Q42">
-        <v>0.7764993600000001</v>
+        <v>0.7006933439999996</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1297077133289806</v>
+        <v>0.1311298779616752</v>
       </c>
       <c r="T42">
-        <v>1.093598788626682</v>
+        <v>1.112134361315269</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1263695219123506</v>
+        <v>0.1232873384510737</v>
       </c>
       <c r="W42">
-        <v>0.175425</v>
+        <v>0.1760439024390244</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5744069177834119</v>
+        <v>0.5603969929594261</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1495446279973884</v>
+        <v>0.1510946279973883</v>
       </c>
       <c r="C43">
-        <v>6.653686002724459</v>
+        <v>5.805974063828849</v>
       </c>
       <c r="D43">
-        <v>24.70768600272446</v>
+        <v>24.34397406382885</v>
       </c>
       <c r="E43">
-        <v>6.144000000000005</v>
+        <v>6.628000000000004</v>
       </c>
       <c r="F43">
-        <v>19.844</v>
+        <v>20.328</v>
       </c>
       <c r="G43">
         <v>1.79</v>
@@ -4813,37 +4813,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M43">
-        <v>3.984675200000001</v>
+        <v>4.0818624</v>
       </c>
       <c r="N43">
-        <v>-1.751675200000001</v>
+        <v>-1.8488624</v>
       </c>
       <c r="O43">
-        <v>-0.3853685440000001</v>
+        <v>-0.406749728</v>
       </c>
       <c r="P43">
-        <v>-1.366306656000001</v>
+        <v>-1.442112672</v>
       </c>
       <c r="Q43">
-        <v>0.7006933439999996</v>
+        <v>0.6248873280000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1311298779616752</v>
+        <v>0.1326010827541178</v>
       </c>
       <c r="T43">
-        <v>1.112134361315269</v>
+        <v>1.131309091682774</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1232873384510737</v>
+        <v>0.1203519256308101</v>
       </c>
       <c r="W43">
-        <v>0.1760439024390244</v>
+        <v>0.1766333333333333</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5603969929594261</v>
+        <v>0.5470542074127732</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1510946279973883</v>
+        <v>0.1526446279973884</v>
       </c>
       <c r="C44">
-        <v>5.805974063828849</v>
+        <v>4.968814897044552</v>
       </c>
       <c r="D44">
-        <v>24.34397406382885</v>
+        <v>23.99081489704455</v>
       </c>
       <c r="E44">
-        <v>6.628000000000004</v>
+        <v>7.112000000000002</v>
       </c>
       <c r="F44">
-        <v>20.328</v>
+        <v>20.812</v>
       </c>
       <c r="G44">
         <v>1.79</v>
@@ -4895,37 +4895,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M44">
-        <v>4.0818624</v>
+        <v>4.179049600000001</v>
       </c>
       <c r="N44">
-        <v>-1.8488624</v>
+        <v>-1.9460496</v>
       </c>
       <c r="O44">
-        <v>-0.406749728</v>
+        <v>-0.4281309120000001</v>
       </c>
       <c r="P44">
-        <v>-1.442112672</v>
+        <v>-1.517918688</v>
       </c>
       <c r="Q44">
-        <v>0.6248873280000002</v>
+        <v>0.549081312</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1326010827541178</v>
+        <v>0.134123908767348</v>
       </c>
       <c r="T44">
-        <v>1.131309091682774</v>
+        <v>1.151156619607033</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1203519256308101</v>
+        <v>0.1175530436393959</v>
       </c>
       <c r="W44">
-        <v>0.1766333333333333</v>
+        <v>0.1771953488372093</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5470542074127732</v>
+        <v>0.5343320165427087</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1526446279973884</v>
+        <v>0.1541946279973884</v>
       </c>
       <c r="C45">
-        <v>4.968814897044552</v>
+        <v>4.14175580105951</v>
       </c>
       <c r="D45">
-        <v>23.99081489704455</v>
+        <v>23.64775580105951</v>
       </c>
       <c r="E45">
-        <v>7.112000000000002</v>
+        <v>7.596000000000004</v>
       </c>
       <c r="F45">
-        <v>20.812</v>
+        <v>21.296</v>
       </c>
       <c r="G45">
         <v>1.79</v>
@@ -4977,37 +4977,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M45">
-        <v>4.179049600000001</v>
+        <v>4.2762368</v>
       </c>
       <c r="N45">
-        <v>-1.9460496</v>
+        <v>-2.0432368</v>
       </c>
       <c r="O45">
-        <v>-0.4281309120000001</v>
+        <v>-0.449512096</v>
       </c>
       <c r="P45">
-        <v>-1.517918688</v>
+        <v>-1.593724704</v>
       </c>
       <c r="Q45">
-        <v>0.549081312</v>
+        <v>0.4732752960000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.134123908767348</v>
+        <v>0.1357011214239078</v>
       </c>
       <c r="T45">
-        <v>1.151156619607033</v>
+        <v>1.171712987814302</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1175530436393959</v>
+        <v>0.1148813835566824</v>
       </c>
       <c r="W45">
-        <v>0.1771953488372093</v>
+        <v>0.1777318181818182</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5343320165427087</v>
+        <v>0.522188107075829</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1541946279973884</v>
+        <v>0.1557446279973884</v>
       </c>
       <c r="C46">
-        <v>4.14175580105951</v>
+        <v>3.324369603304465</v>
       </c>
       <c r="D46">
-        <v>23.64775580105951</v>
+        <v>23.31436960330447</v>
       </c>
       <c r="E46">
-        <v>7.596000000000004</v>
+        <v>8.080000000000005</v>
       </c>
       <c r="F46">
-        <v>21.296</v>
+        <v>21.78</v>
       </c>
       <c r="G46">
         <v>1.79</v>
@@ -5059,37 +5059,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M46">
-        <v>4.2762368</v>
+        <v>4.373424000000001</v>
       </c>
       <c r="N46">
-        <v>-2.0432368</v>
+        <v>-2.140424</v>
       </c>
       <c r="O46">
-        <v>-0.449512096</v>
+        <v>-0.4708932800000001</v>
       </c>
       <c r="P46">
-        <v>-1.593724704</v>
+        <v>-1.66953072</v>
       </c>
       <c r="Q46">
-        <v>0.4732752960000002</v>
+        <v>0.3974692799999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1357011214239078</v>
+        <v>0.1373356872679788</v>
       </c>
       <c r="T46">
-        <v>1.171712987814302</v>
+        <v>1.193016860320016</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1148813835566824</v>
+        <v>0.1123284639220894</v>
       </c>
       <c r="W46">
-        <v>0.1777318181818182</v>
+        <v>0.1782444444444445</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.522188107075829</v>
+        <v>0.5105839269185883</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1557446279973884</v>
+        <v>0.1737924663174801</v>
       </c>
       <c r="C47">
-        <v>3.324369603304465</v>
+        <v>-0.4471205532770028</v>
       </c>
       <c r="D47">
-        <v>23.31436960330447</v>
+        <v>20.026879446723</v>
       </c>
       <c r="E47">
-        <v>8.080000000000005</v>
+        <v>8.564000000000004</v>
       </c>
       <c r="F47">
-        <v>21.78</v>
+        <v>22.264</v>
       </c>
       <c r="G47">
         <v>1.79</v>
@@ -5141,45 +5141,45 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M47">
-        <v>4.373424000000001</v>
+        <v>5.249851200000001</v>
       </c>
       <c r="N47">
-        <v>-2.140424</v>
+        <v>-3.016851200000001</v>
       </c>
       <c r="O47">
-        <v>-0.4708932800000001</v>
+        <v>-0.6637072640000001</v>
       </c>
       <c r="P47">
-        <v>-1.66953072</v>
+        <v>-2.353143936</v>
       </c>
       <c r="Q47">
-        <v>0.3974692799999999</v>
+        <v>-0.2861439360000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1373356872679788</v>
+        <v>0.1397675302175558</v>
       </c>
       <c r="T47">
-        <v>1.193016860320016</v>
+        <v>1.224711926223679</v>
       </c>
       <c r="U47">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1123284639220894</v>
+        <v>0.09357598554412362</v>
       </c>
       <c r="W47">
-        <v>0.1782444444444445</v>
+        <v>0.2137347826086957</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.5105839269185883</v>
+        <v>0.4253453888369255</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1737924663174801</v>
+        <v>0.1756924663174801</v>
       </c>
       <c r="C48">
-        <v>-0.4471205532770028</v>
+        <v>-1.224063416150745</v>
       </c>
       <c r="D48">
-        <v>20.026879446723</v>
+        <v>19.73393658384926</v>
       </c>
       <c r="E48">
-        <v>8.564000000000004</v>
+        <v>9.048000000000005</v>
       </c>
       <c r="F48">
-        <v>22.264</v>
+        <v>22.748</v>
       </c>
       <c r="G48">
         <v>1.79</v>
@@ -5223,37 +5223,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M48">
-        <v>5.249851200000001</v>
+        <v>5.363978400000001</v>
       </c>
       <c r="N48">
-        <v>-3.016851200000001</v>
+        <v>-3.130978400000001</v>
       </c>
       <c r="O48">
-        <v>-0.6637072640000001</v>
+        <v>-0.6888152480000002</v>
       </c>
       <c r="P48">
-        <v>-2.353143936</v>
+        <v>-2.442163152000001</v>
       </c>
       <c r="Q48">
-        <v>-0.2861439360000002</v>
+        <v>-0.3751631520000007</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1397675302175558</v>
+        <v>0.1415405024858115</v>
       </c>
       <c r="T48">
-        <v>1.224711926223679</v>
+        <v>1.247819698416579</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09357598554412362</v>
+        <v>0.09158500712829119</v>
       </c>
       <c r="W48">
-        <v>0.2137347826086957</v>
+        <v>0.2142042553191489</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4253453888369255</v>
+        <v>0.4162954869467781</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1756924663174801</v>
+        <v>0.1775924663174802</v>
       </c>
       <c r="C49">
-        <v>-1.224063416150745</v>
+        <v>-1.992559795625066</v>
       </c>
       <c r="D49">
-        <v>19.73393658384926</v>
+        <v>19.44944020437494</v>
       </c>
       <c r="E49">
-        <v>9.048000000000005</v>
+        <v>9.532000000000004</v>
       </c>
       <c r="F49">
-        <v>22.748</v>
+        <v>23.232</v>
       </c>
       <c r="G49">
         <v>1.79</v>
@@ -5305,37 +5305,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M49">
-        <v>5.363978400000001</v>
+        <v>5.478105600000001</v>
       </c>
       <c r="N49">
-        <v>-3.130978400000001</v>
+        <v>-3.2451056</v>
       </c>
       <c r="O49">
-        <v>-0.6888152480000002</v>
+        <v>-0.7139232320000001</v>
       </c>
       <c r="P49">
-        <v>-2.442163152000001</v>
+        <v>-2.531182368000001</v>
       </c>
       <c r="Q49">
-        <v>-0.3751631520000007</v>
+        <v>-0.4641823680000003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1415405024858115</v>
+        <v>0.1433816659951541</v>
       </c>
       <c r="T49">
-        <v>1.247819698416579</v>
+        <v>1.271816231078436</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.09158500712829119</v>
+        <v>0.0896769861464518</v>
       </c>
       <c r="W49">
-        <v>0.2142042553191489</v>
+        <v>0.2146541666666667</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4162954869467781</v>
+        <v>0.4076226643020536</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1775924663174801</v>
+        <v>0.1794924663174801</v>
       </c>
       <c r="C50">
-        <v>-1.992559795625059</v>
+        <v>-2.752969808890558</v>
       </c>
       <c r="D50">
-        <v>19.44944020437494</v>
+        <v>19.17303019110944</v>
       </c>
       <c r="E50">
-        <v>9.532000000000004</v>
+        <v>10.016</v>
       </c>
       <c r="F50">
-        <v>23.232</v>
+        <v>23.716</v>
       </c>
       <c r="G50">
         <v>1.79</v>
@@ -5387,37 +5387,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M50">
-        <v>5.478105600000001</v>
+        <v>5.592232800000001</v>
       </c>
       <c r="N50">
-        <v>-3.2451056</v>
+        <v>-3.3592328</v>
       </c>
       <c r="O50">
-        <v>-0.7139232320000001</v>
+        <v>-0.739031216</v>
       </c>
       <c r="P50">
-        <v>-2.531182368000001</v>
+        <v>-2.620201584</v>
       </c>
       <c r="Q50">
-        <v>-0.4641823680000003</v>
+        <v>-0.553201584</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1433816659951541</v>
+        <v>0.1452950319950591</v>
       </c>
       <c r="T50">
-        <v>1.271816231078436</v>
+        <v>1.296753804236837</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0896769861464518</v>
+        <v>0.08784684357203443</v>
       </c>
       <c r="W50">
-        <v>0.2146541666666667</v>
+        <v>0.2150857142857143</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4076226643020536</v>
+        <v>0.3993038344183383</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1794924663174801</v>
+        <v>0.1813924663174801</v>
       </c>
       <c r="C51">
-        <v>-2.752969808890558</v>
+        <v>-3.505633388457088</v>
       </c>
       <c r="D51">
-        <v>19.17303019110944</v>
+        <v>18.90436661154292</v>
       </c>
       <c r="E51">
-        <v>10.016</v>
+        <v>10.5</v>
       </c>
       <c r="F51">
-        <v>23.716</v>
+        <v>24.2</v>
       </c>
       <c r="G51">
         <v>1.79</v>
@@ -5469,37 +5469,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M51">
-        <v>5.592232800000001</v>
+        <v>5.706360000000001</v>
       </c>
       <c r="N51">
-        <v>-3.3592328</v>
+        <v>-3.47336</v>
       </c>
       <c r="O51">
-        <v>-0.739031216</v>
+        <v>-0.7641392000000001</v>
       </c>
       <c r="P51">
-        <v>-2.620201584</v>
+        <v>-2.7092208</v>
       </c>
       <c r="Q51">
-        <v>-0.553201584</v>
+        <v>-0.6422208</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1452950319950591</v>
+        <v>0.1472849326349602</v>
       </c>
       <c r="T51">
-        <v>1.296753804236837</v>
+        <v>1.322688880321574</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08784684357203443</v>
+        <v>0.08608990670059373</v>
       </c>
       <c r="W51">
-        <v>0.2150857142857143</v>
+        <v>0.2155</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3993038344183383</v>
+        <v>0.3913177577299715</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1813924663174801</v>
+        <v>0.1832924663174801</v>
       </c>
       <c r="C52">
-        <v>-3.505633388457088</v>
+        <v>-4.250871676808057</v>
       </c>
       <c r="D52">
-        <v>18.90436661154292</v>
+        <v>18.64312832319195</v>
       </c>
       <c r="E52">
-        <v>10.5</v>
+        <v>10.98400000000001</v>
       </c>
       <c r="F52">
-        <v>24.2</v>
+        <v>24.684</v>
       </c>
       <c r="G52">
         <v>1.79</v>
@@ -5551,37 +5551,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M52">
-        <v>5.706360000000001</v>
+        <v>5.820487200000001</v>
       </c>
       <c r="N52">
-        <v>-3.47336</v>
+        <v>-3.587487200000001</v>
       </c>
       <c r="O52">
-        <v>-0.7641392000000001</v>
+        <v>-0.7892471840000002</v>
       </c>
       <c r="P52">
-        <v>-2.7092208</v>
+        <v>-2.798240016000001</v>
       </c>
       <c r="Q52">
-        <v>-0.6422208</v>
+        <v>-0.7312400160000005</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1472849326349602</v>
+        <v>0.1493560537091431</v>
       </c>
       <c r="T52">
-        <v>1.322688880321574</v>
+        <v>1.349682530940381</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08608990670059373</v>
+        <v>0.08440186931430757</v>
       </c>
       <c r="W52">
-        <v>0.2155</v>
+        <v>0.2158980392156863</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3913177577299715</v>
+        <v>0.3836448605195799</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1832924663174801</v>
+        <v>0.1851924663174801</v>
       </c>
       <c r="C53">
-        <v>-4.250871676808057</v>
+        <v>-4.988988306995136</v>
       </c>
       <c r="D53">
-        <v>18.64312832319195</v>
+        <v>18.38901169300487</v>
       </c>
       <c r="E53">
-        <v>10.98400000000001</v>
+        <v>11.468</v>
       </c>
       <c r="F53">
-        <v>24.684</v>
+        <v>25.168</v>
       </c>
       <c r="G53">
         <v>1.79</v>
@@ -5633,37 +5633,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M53">
-        <v>5.820487200000001</v>
+        <v>5.934614400000001</v>
       </c>
       <c r="N53">
-        <v>-3.587487200000001</v>
+        <v>-3.7016144</v>
       </c>
       <c r="O53">
-        <v>-0.7892471840000002</v>
+        <v>-0.8143551680000001</v>
       </c>
       <c r="P53">
-        <v>-2.798240016000001</v>
+        <v>-2.887259232</v>
       </c>
       <c r="Q53">
-        <v>-0.7312400160000005</v>
+        <v>-0.8202592320000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1493560537091431</v>
+        <v>0.1515134714947503</v>
       </c>
       <c r="T53">
-        <v>1.349682530940381</v>
+        <v>1.377800917001639</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08440186931430757</v>
+        <v>0.08277875644287859</v>
       </c>
       <c r="W53">
-        <v>0.2158980392156863</v>
+        <v>0.2162807692307692</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3836448605195799</v>
+        <v>0.3762670747403573</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1851924663174801</v>
+        <v>0.1870924663174801</v>
       </c>
       <c r="C54">
-        <v>-4.988988306995136</v>
+        <v>-5.720270579909833</v>
       </c>
       <c r="D54">
-        <v>18.38901169300487</v>
+        <v>18.14172942009017</v>
       </c>
       <c r="E54">
-        <v>11.468</v>
+        <v>11.95200000000001</v>
       </c>
       <c r="F54">
-        <v>25.168</v>
+        <v>25.652</v>
       </c>
       <c r="G54">
         <v>1.79</v>
@@ -5715,37 +5715,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M54">
-        <v>5.934614400000001</v>
+        <v>6.048741600000001</v>
       </c>
       <c r="N54">
-        <v>-3.7016144</v>
+        <v>-3.815741600000001</v>
       </c>
       <c r="O54">
-        <v>-0.8143551680000001</v>
+        <v>-0.8394631520000002</v>
       </c>
       <c r="P54">
-        <v>-2.887259232</v>
+        <v>-2.976278448</v>
       </c>
       <c r="Q54">
-        <v>-0.8202592320000002</v>
+        <v>-0.9092784480000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1515134714947503</v>
+        <v>0.1537626942925109</v>
       </c>
       <c r="T54">
-        <v>1.377800917001639</v>
+        <v>1.407115830129334</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08277875644287859</v>
+        <v>0.08121689311376766</v>
       </c>
       <c r="W54">
-        <v>0.2162807692307692</v>
+        <v>0.2166490566037736</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3762670747403573</v>
+        <v>0.3691676959716712</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1870924663174801</v>
+        <v>0.1889924663174801</v>
       </c>
       <c r="C55">
-        <v>-5.720270579909833</v>
+        <v>-6.444990547828727</v>
       </c>
       <c r="D55">
-        <v>18.14172942009017</v>
+        <v>17.90100945217128</v>
       </c>
       <c r="E55">
-        <v>11.95200000000001</v>
+        <v>12.43600000000001</v>
       </c>
       <c r="F55">
-        <v>25.652</v>
+        <v>26.13600000000001</v>
       </c>
       <c r="G55">
         <v>1.79</v>
@@ -5797,37 +5797,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M55">
-        <v>6.048741600000001</v>
+        <v>6.162868800000002</v>
       </c>
       <c r="N55">
-        <v>-3.815741600000001</v>
+        <v>-3.929868800000001</v>
       </c>
       <c r="O55">
-        <v>-0.8394631520000002</v>
+        <v>-0.8645711360000002</v>
       </c>
       <c r="P55">
-        <v>-2.976278448</v>
+        <v>-3.065297664000001</v>
       </c>
       <c r="Q55">
-        <v>-0.9092784480000002</v>
+        <v>-0.9982976640000008</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1537626942925109</v>
+        <v>0.1561097093858264</v>
       </c>
       <c r="T55">
-        <v>1.407115830129334</v>
+        <v>1.437705304697363</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.08121689311376766</v>
+        <v>0.07971287657462381</v>
       </c>
       <c r="W55">
-        <v>0.2166490566037736</v>
+        <v>0.2170037037037037</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3691676959716712</v>
+        <v>0.362331257157381</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1889924663174801</v>
+        <v>0.1908924663174801</v>
       </c>
       <c r="C56">
-        <v>-6.444990547828727</v>
+        <v>-7.163406012824019</v>
       </c>
       <c r="D56">
-        <v>17.90100945217128</v>
+        <v>17.66659398717599</v>
       </c>
       <c r="E56">
-        <v>12.43600000000001</v>
+        <v>12.92000000000001</v>
       </c>
       <c r="F56">
-        <v>26.13600000000001</v>
+        <v>26.62</v>
       </c>
       <c r="G56">
         <v>1.79</v>
@@ -5879,37 +5879,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M56">
-        <v>6.162868800000002</v>
+        <v>6.276996000000001</v>
       </c>
       <c r="N56">
-        <v>-3.929868800000001</v>
+        <v>-4.043996000000001</v>
       </c>
       <c r="O56">
-        <v>-0.8645711360000002</v>
+        <v>-0.8896791200000002</v>
       </c>
       <c r="P56">
-        <v>-3.065297664000001</v>
+        <v>-3.154316880000001</v>
       </c>
       <c r="Q56">
-        <v>-0.9982976640000008</v>
+        <v>-1.08731688</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1561097093858264</v>
+        <v>0.1585610362610669</v>
       </c>
       <c r="T56">
-        <v>1.437705304697363</v>
+        <v>1.469654311468415</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07971287657462381</v>
+        <v>0.07826355154599431</v>
       </c>
       <c r="W56">
-        <v>0.2170037037037037</v>
+        <v>0.2173454545454546</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.362331257157381</v>
+        <v>0.3557434161181559</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1908924663174801</v>
+        <v>0.1927924663174801</v>
       </c>
       <c r="C57">
-        <v>-7.163406012824019</v>
+        <v>-7.875761447742274</v>
       </c>
       <c r="D57">
-        <v>17.66659398717599</v>
+        <v>17.43823855225773</v>
       </c>
       <c r="E57">
-        <v>12.92000000000001</v>
+        <v>13.40400000000001</v>
       </c>
       <c r="F57">
-        <v>26.62</v>
+        <v>27.10400000000001</v>
       </c>
       <c r="G57">
         <v>1.79</v>
@@ -5961,37 +5961,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M57">
-        <v>6.276996000000001</v>
+        <v>6.391123200000002</v>
       </c>
       <c r="N57">
-        <v>-4.043996000000001</v>
+        <v>-4.158123200000001</v>
       </c>
       <c r="O57">
-        <v>-0.8896791200000002</v>
+        <v>-0.9147871040000003</v>
       </c>
       <c r="P57">
-        <v>-3.154316880000001</v>
+        <v>-3.243336096000001</v>
       </c>
       <c r="Q57">
-        <v>-1.08731688</v>
+        <v>-1.176336096000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1585610362610669</v>
+        <v>0.1611237870851821</v>
       </c>
       <c r="T57">
-        <v>1.469654311468415</v>
+        <v>1.50305554581997</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07826355154599431</v>
+        <v>0.07686598812553011</v>
       </c>
       <c r="W57">
-        <v>0.2173454545454546</v>
+        <v>0.217675</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3557434161181559</v>
+        <v>0.349390855116046</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1927924663174801</v>
+        <v>0.1946924663174802</v>
       </c>
       <c r="C58">
-        <v>-7.875761447742274</v>
+        <v>-8.582288846668163</v>
       </c>
       <c r="D58">
-        <v>17.43823855225773</v>
+        <v>17.21571115333184</v>
       </c>
       <c r="E58">
-        <v>13.40400000000001</v>
+        <v>13.88800000000001</v>
       </c>
       <c r="F58">
-        <v>27.10400000000001</v>
+        <v>27.588</v>
       </c>
       <c r="G58">
         <v>1.79</v>
@@ -6043,37 +6043,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M58">
-        <v>6.391123200000002</v>
+        <v>6.505250400000001</v>
       </c>
       <c r="N58">
-        <v>-4.158123200000001</v>
+        <v>-4.272250400000001</v>
       </c>
       <c r="O58">
-        <v>-0.9147871040000003</v>
+        <v>-0.9398950880000002</v>
       </c>
       <c r="P58">
-        <v>-3.243336096000001</v>
+        <v>-3.332355312000001</v>
       </c>
       <c r="Q58">
-        <v>-1.176336096000001</v>
+        <v>-1.265355312000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1611237870851821</v>
+        <v>0.1638057356220468</v>
       </c>
       <c r="T58">
-        <v>1.50305554581997</v>
+        <v>1.538010325955319</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07686598812553011</v>
+        <v>0.07551746201806467</v>
       </c>
       <c r="W58">
-        <v>0.217675</v>
+        <v>0.2179929824561404</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.349390855116046</v>
+        <v>0.343261190991203</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1946924663174802</v>
+        <v>0.1965924663174801</v>
       </c>
       <c r="C59">
-        <v>-8.582288846668163</v>
+        <v>-9.283208511092667</v>
       </c>
       <c r="D59">
-        <v>17.21571115333184</v>
+        <v>16.99879148890734</v>
       </c>
       <c r="E59">
-        <v>13.88800000000001</v>
+        <v>14.37200000000001</v>
       </c>
       <c r="F59">
-        <v>27.588</v>
+        <v>28.07200000000001</v>
       </c>
       <c r="G59">
         <v>1.79</v>
@@ -6125,37 +6125,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M59">
-        <v>6.505250400000001</v>
+        <v>6.619377600000002</v>
       </c>
       <c r="N59">
-        <v>-4.272250400000001</v>
+        <v>-4.386377600000001</v>
       </c>
       <c r="O59">
-        <v>-0.9398950880000002</v>
+        <v>-0.9650030720000002</v>
       </c>
       <c r="P59">
-        <v>-3.332355312000001</v>
+        <v>-3.421374528000001</v>
       </c>
       <c r="Q59">
-        <v>-1.265355312000001</v>
+        <v>-1.354374528000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1638057356220468</v>
+        <v>0.1666153959940003</v>
       </c>
       <c r="T59">
-        <v>1.538010325955319</v>
+        <v>1.574629619430445</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07551746201806467</v>
+        <v>0.07421543681085666</v>
       </c>
       <c r="W59">
-        <v>0.2179929824561404</v>
+        <v>0.2183</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.343261190991203</v>
+        <v>0.3373428945948029</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1965924663174801</v>
+        <v>0.1984924663174801</v>
       </c>
       <c r="C60">
-        <v>-9.283208511092656</v>
+        <v>-9.978729777385979</v>
       </c>
       <c r="D60">
-        <v>16.99879148890735</v>
+        <v>16.78727022261402</v>
       </c>
       <c r="E60">
-        <v>14.372</v>
+        <v>14.856</v>
       </c>
       <c r="F60">
-        <v>28.072</v>
+        <v>28.556</v>
       </c>
       <c r="G60">
         <v>1.79</v>
@@ -6207,37 +6207,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M60">
-        <v>6.619377600000001</v>
+        <v>6.7335048</v>
       </c>
       <c r="N60">
-        <v>-4.3863776</v>
+        <v>-4.5005048</v>
       </c>
       <c r="O60">
-        <v>-0.9650030720000001</v>
+        <v>-0.9901110559999999</v>
       </c>
       <c r="P60">
-        <v>-3.421374528</v>
+        <v>-3.510393744</v>
       </c>
       <c r="Q60">
-        <v>-1.354374528</v>
+        <v>-1.443393744</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1666153959940003</v>
+        <v>0.1695621129694637</v>
       </c>
       <c r="T60">
-        <v>1.574629619430445</v>
+        <v>1.613035219904358</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07421543681085667</v>
+        <v>0.07295754805135063</v>
       </c>
       <c r="W60">
-        <v>0.2183</v>
+        <v>0.2185966101694915</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.337342894594803</v>
+        <v>0.3316252184152301</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1984924663174801</v>
+        <v>0.2003924663174801</v>
       </c>
       <c r="C61">
-        <v>-9.978729777385979</v>
+        <v>-10.66905169062504</v>
       </c>
       <c r="D61">
-        <v>16.78727022261402</v>
+        <v>16.58094830937496</v>
       </c>
       <c r="E61">
-        <v>14.856</v>
+        <v>15.34</v>
       </c>
       <c r="F61">
-        <v>28.556</v>
+        <v>29.04</v>
       </c>
       <c r="G61">
         <v>1.79</v>
@@ -6289,37 +6289,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M61">
-        <v>6.7335048</v>
+        <v>6.847632000000001</v>
       </c>
       <c r="N61">
-        <v>-4.5005048</v>
+        <v>-4.614632</v>
       </c>
       <c r="O61">
-        <v>-0.9901110559999999</v>
+        <v>-1.01521904</v>
       </c>
       <c r="P61">
-        <v>-3.510393744</v>
+        <v>-3.59941296</v>
       </c>
       <c r="Q61">
-        <v>-1.443393744</v>
+        <v>-1.53241296</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1695621129694637</v>
+        <v>0.1726561657937003</v>
       </c>
       <c r="T61">
-        <v>1.613035219904358</v>
+        <v>1.653361100401967</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07295754805135063</v>
+        <v>0.07174158891716145</v>
       </c>
       <c r="W61">
-        <v>0.2185966101694915</v>
+        <v>0.2188833333333333</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3316252184152301</v>
+        <v>0.3260981314416429</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2003924663174801</v>
+        <v>0.2022924663174801</v>
       </c>
       <c r="C62">
-        <v>-10.66905169062504</v>
+        <v>-11.3543636293346</v>
       </c>
       <c r="D62">
-        <v>16.58094830937496</v>
+        <v>16.37963637066541</v>
       </c>
       <c r="E62">
-        <v>15.34</v>
+        <v>15.82400000000001</v>
       </c>
       <c r="F62">
-        <v>29.04</v>
+        <v>29.524</v>
       </c>
       <c r="G62">
         <v>1.79</v>
@@ -6371,37 +6371,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M62">
-        <v>6.847632000000001</v>
+        <v>6.961759200000001</v>
       </c>
       <c r="N62">
-        <v>-4.614632</v>
+        <v>-4.728759200000001</v>
       </c>
       <c r="O62">
-        <v>-1.01521904</v>
+        <v>-1.040327024</v>
       </c>
       <c r="P62">
-        <v>-3.59941296</v>
+        <v>-3.688432176000001</v>
       </c>
       <c r="Q62">
-        <v>-1.53241296</v>
+        <v>-1.621432176</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1726561657937003</v>
+        <v>0.1759088879935388</v>
       </c>
       <c r="T62">
-        <v>1.653361100401967</v>
+        <v>1.695754974771248</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07174158891716145</v>
+        <v>0.07056549729556863</v>
       </c>
       <c r="W62">
-        <v>0.2188833333333333</v>
+        <v>0.2191606557377049</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3260981314416429</v>
+        <v>0.3207522604344029</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2022924663174801</v>
+        <v>0.2041924663174801</v>
       </c>
       <c r="C63">
-        <v>-11.3543636293346</v>
+        <v>-12.03484588526389</v>
       </c>
       <c r="D63">
-        <v>16.37963637066541</v>
+        <v>16.18315411473611</v>
       </c>
       <c r="E63">
-        <v>15.82400000000001</v>
+        <v>16.308</v>
       </c>
       <c r="F63">
-        <v>29.524</v>
+        <v>30.008</v>
       </c>
       <c r="G63">
         <v>1.79</v>
@@ -6453,37 +6453,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M63">
-        <v>6.961759200000001</v>
+        <v>7.075886400000001</v>
       </c>
       <c r="N63">
-        <v>-4.728759200000001</v>
+        <v>-4.8428864</v>
       </c>
       <c r="O63">
-        <v>-1.040327024</v>
+        <v>-1.065435008</v>
       </c>
       <c r="P63">
-        <v>-3.688432176000001</v>
+        <v>-3.777451392</v>
       </c>
       <c r="Q63">
-        <v>-1.621432176</v>
+        <v>-1.710451392</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1759088879935388</v>
+        <v>0.1793328060986319</v>
       </c>
       <c r="T63">
-        <v>1.695754974771248</v>
+        <v>1.740380105686281</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07056549729556863</v>
+        <v>0.06942734411338204</v>
       </c>
       <c r="W63">
-        <v>0.2191606557377049</v>
+        <v>0.2194290322580645</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3207522604344029</v>
+        <v>0.3155788368790093</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2041924663174801</v>
+        <v>0.2060924663174801</v>
       </c>
       <c r="C64">
-        <v>-12.03484588526389</v>
+        <v>-12.71067020192952</v>
       </c>
       <c r="D64">
-        <v>16.18315411473611</v>
+        <v>15.99132979807048</v>
       </c>
       <c r="E64">
-        <v>16.308</v>
+        <v>16.79200000000001</v>
       </c>
       <c r="F64">
-        <v>30.008</v>
+        <v>30.492</v>
       </c>
       <c r="G64">
         <v>1.79</v>
@@ -6535,37 +6535,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M64">
-        <v>7.075886400000001</v>
+        <v>7.190013600000001</v>
       </c>
       <c r="N64">
-        <v>-4.8428864</v>
+        <v>-4.957013600000001</v>
       </c>
       <c r="O64">
-        <v>-1.065435008</v>
+        <v>-1.090542992</v>
       </c>
       <c r="P64">
-        <v>-3.777451392</v>
+        <v>-3.866470608</v>
       </c>
       <c r="Q64">
-        <v>-1.710451392</v>
+        <v>-1.799470608</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1793328060986319</v>
+        <v>0.1829418008580544</v>
       </c>
       <c r="T64">
-        <v>1.740380105686281</v>
+        <v>1.787417405839965</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06942734411338204</v>
+        <v>0.06832532277824899</v>
       </c>
       <c r="W64">
-        <v>0.2194290322580645</v>
+        <v>0.2196888888888889</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3155788368790093</v>
+        <v>0.3105696489920409</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2060924663174801</v>
+        <v>0.2079924663174801</v>
       </c>
       <c r="C65">
-        <v>-12.71067020192952</v>
+        <v>-13.38200027530581</v>
       </c>
       <c r="D65">
-        <v>15.99132979807048</v>
+        <v>15.80399972469419</v>
       </c>
       <c r="E65">
-        <v>16.79200000000001</v>
+        <v>17.276</v>
       </c>
       <c r="F65">
-        <v>30.492</v>
+        <v>30.976</v>
       </c>
       <c r="G65">
         <v>1.79</v>
@@ -6617,37 +6617,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M65">
-        <v>7.190013600000001</v>
+        <v>7.304140800000001</v>
       </c>
       <c r="N65">
-        <v>-4.957013600000001</v>
+        <v>-5.0711408</v>
       </c>
       <c r="O65">
-        <v>-1.090542992</v>
+        <v>-1.115650976</v>
       </c>
       <c r="P65">
-        <v>-3.866470608</v>
+        <v>-3.955489824</v>
       </c>
       <c r="Q65">
-        <v>-1.799470608</v>
+        <v>-1.888489824</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1829418008580544</v>
+        <v>0.1867512953263337</v>
       </c>
       <c r="T65">
-        <v>1.787417405839965</v>
+        <v>1.837067889335519</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06832532277824899</v>
+        <v>0.06725773960983886</v>
       </c>
       <c r="W65">
-        <v>0.2196888888888889</v>
+        <v>0.219940625</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3105696489920409</v>
+        <v>0.3057169982265403</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2079924663174801</v>
+        <v>0.2098924663174802</v>
       </c>
       <c r="C66">
-        <v>-13.38200027530581</v>
+        <v>-14.04899221973075</v>
       </c>
       <c r="D66">
-        <v>15.80399972469419</v>
+        <v>15.62100778026926</v>
       </c>
       <c r="E66">
-        <v>17.276</v>
+        <v>17.76000000000001</v>
       </c>
       <c r="F66">
-        <v>30.976</v>
+        <v>31.46</v>
       </c>
       <c r="G66">
         <v>1.79</v>
@@ -6699,37 +6699,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M66">
-        <v>7.304140800000001</v>
+        <v>7.418268000000001</v>
       </c>
       <c r="N66">
-        <v>-5.0711408</v>
+        <v>-5.185268000000001</v>
       </c>
       <c r="O66">
-        <v>-1.115650976</v>
+        <v>-1.14075896</v>
       </c>
       <c r="P66">
-        <v>-3.955489824</v>
+        <v>-4.04450904</v>
       </c>
       <c r="Q66">
-        <v>-1.888489824</v>
+        <v>-1.97750904</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1867512953263337</v>
+        <v>0.1907784751928004</v>
       </c>
       <c r="T66">
-        <v>1.837067889335519</v>
+        <v>1.889555543316534</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06725773960983886</v>
+        <v>0.06622300515430288</v>
       </c>
       <c r="W66">
-        <v>0.219940625</v>
+        <v>0.2201846153846154</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3057169982265403</v>
+        <v>0.3010136597922858</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2098924663174802</v>
+        <v>0.2117924663174802</v>
       </c>
       <c r="C67">
-        <v>-14.04899221973075</v>
+        <v>-14.71179500181452</v>
       </c>
       <c r="D67">
-        <v>15.62100778026926</v>
+        <v>15.44220499818549</v>
       </c>
       <c r="E67">
-        <v>17.76000000000001</v>
+        <v>18.24400000000001</v>
       </c>
       <c r="F67">
-        <v>31.46</v>
+        <v>31.94400000000001</v>
       </c>
       <c r="G67">
         <v>1.79</v>
@@ -6781,37 +6781,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M67">
-        <v>7.418268000000001</v>
+        <v>7.532395200000002</v>
       </c>
       <c r="N67">
-        <v>-5.185268000000001</v>
+        <v>-5.299395200000001</v>
       </c>
       <c r="O67">
-        <v>-1.14075896</v>
+        <v>-1.165866944</v>
       </c>
       <c r="P67">
-        <v>-4.04450904</v>
+        <v>-4.133528256000001</v>
       </c>
       <c r="Q67">
-        <v>-1.97750904</v>
+        <v>-2.066528256000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1907784751928004</v>
+        <v>0.1950425479925886</v>
       </c>
       <c r="T67">
-        <v>1.889555543316534</v>
+        <v>1.945130706355256</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06622300515430288</v>
+        <v>0.06521962628832857</v>
       </c>
       <c r="W67">
-        <v>0.2201846153846154</v>
+        <v>0.2204212121212121</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3010136597922858</v>
+        <v>0.29645284676513</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2117924663174802</v>
+        <v>0.2136924663174801</v>
       </c>
       <c r="C68">
-        <v>-14.71179500181452</v>
+        <v>-15.37055084488534</v>
       </c>
       <c r="D68">
-        <v>15.44220499818549</v>
+        <v>15.26744915511466</v>
       </c>
       <c r="E68">
-        <v>18.24400000000001</v>
+        <v>18.72800000000001</v>
       </c>
       <c r="F68">
-        <v>31.94400000000001</v>
+        <v>32.428</v>
       </c>
       <c r="G68">
         <v>1.79</v>
@@ -6863,37 +6863,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M68">
-        <v>7.532395200000002</v>
+        <v>7.646522400000001</v>
       </c>
       <c r="N68">
-        <v>-5.299395200000001</v>
+        <v>-5.413522400000001</v>
       </c>
       <c r="O68">
-        <v>-1.165866944</v>
+        <v>-1.190974928</v>
       </c>
       <c r="P68">
-        <v>-4.133528256000001</v>
+        <v>-4.222547472</v>
       </c>
       <c r="Q68">
-        <v>-2.066528256000001</v>
+        <v>-2.155547472</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1950425479925886</v>
+        <v>0.1995650494469095</v>
       </c>
       <c r="T68">
-        <v>1.945130706355256</v>
+        <v>2.004074061093294</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06521962628832857</v>
+        <v>0.06424619903029383</v>
       </c>
       <c r="W68">
-        <v>0.2204212121212121</v>
+        <v>0.2206507462686567</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.29645284676513</v>
+        <v>0.2920281774104265</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2136924663174801</v>
+        <v>0.2155924663174801</v>
       </c>
       <c r="C69">
-        <v>-15.37055084488534</v>
+        <v>-16.02539560628058</v>
       </c>
       <c r="D69">
-        <v>15.26744915511466</v>
+        <v>15.09660439371943</v>
       </c>
       <c r="E69">
-        <v>18.72800000000001</v>
+        <v>19.21200000000001</v>
       </c>
       <c r="F69">
-        <v>32.428</v>
+        <v>32.91200000000001</v>
       </c>
       <c r="G69">
         <v>1.79</v>
@@ -6945,37 +6945,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M69">
-        <v>7.646522400000001</v>
+        <v>7.760649600000002</v>
       </c>
       <c r="N69">
-        <v>-5.413522400000001</v>
+        <v>-5.527649600000001</v>
       </c>
       <c r="O69">
-        <v>-1.190974928</v>
+        <v>-1.216082912</v>
       </c>
       <c r="P69">
-        <v>-4.222547472</v>
+        <v>-4.311566688000001</v>
       </c>
       <c r="Q69">
-        <v>-2.155547472</v>
+        <v>-2.244566688000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1995650494469095</v>
+        <v>0.2043702072421254</v>
       </c>
       <c r="T69">
-        <v>2.004074061093294</v>
+        <v>2.066701375502459</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06424619903029383</v>
+        <v>0.06330140198573068</v>
       </c>
       <c r="W69">
-        <v>0.2206507462686567</v>
+        <v>0.2208735294117647</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2920281774104265</v>
+        <v>0.2877336453896849</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2155924663174801</v>
+        <v>0.2174924663174801</v>
       </c>
       <c r="C70">
-        <v>-16.02539560628058</v>
+        <v>-16.67645912958641</v>
       </c>
       <c r="D70">
-        <v>15.09660439371943</v>
+        <v>14.92954087041359</v>
       </c>
       <c r="E70">
-        <v>19.21200000000001</v>
+        <v>19.69600000000001</v>
       </c>
       <c r="F70">
-        <v>32.91200000000001</v>
+        <v>33.39600000000001</v>
       </c>
       <c r="G70">
         <v>1.79</v>
@@ -7027,37 +7027,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M70">
-        <v>7.760649600000002</v>
+        <v>7.874776800000002</v>
       </c>
       <c r="N70">
-        <v>-5.527649600000001</v>
+        <v>-5.641776800000001</v>
       </c>
       <c r="O70">
-        <v>-1.216082912</v>
+        <v>-1.241190896</v>
       </c>
       <c r="P70">
-        <v>-4.311566688000001</v>
+        <v>-4.400585904000001</v>
       </c>
       <c r="Q70">
-        <v>-2.244566688000001</v>
+        <v>-2.333585904000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2043702072421254</v>
+        <v>0.2094853752176778</v>
       </c>
       <c r="T70">
-        <v>2.066701375502459</v>
+        <v>2.13336916180899</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06330140198573068</v>
+        <v>0.06238399036274907</v>
       </c>
       <c r="W70">
-        <v>0.2208735294117647</v>
+        <v>0.2210898550724638</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2877336453896849</v>
+        <v>0.2835635925579504</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2174924663174801</v>
+        <v>0.2193924663174801</v>
       </c>
       <c r="C71">
-        <v>-16.67645912958641</v>
+        <v>-17.32386557374573</v>
       </c>
       <c r="D71">
-        <v>14.92954087041359</v>
+        <v>14.76613442625427</v>
       </c>
       <c r="E71">
-        <v>19.69600000000001</v>
+        <v>20.18000000000001</v>
       </c>
       <c r="F71">
-        <v>33.39600000000001</v>
+        <v>33.88000000000001</v>
       </c>
       <c r="G71">
         <v>1.79</v>
@@ -7109,37 +7109,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M71">
-        <v>7.874776800000002</v>
+        <v>7.988904000000002</v>
       </c>
       <c r="N71">
-        <v>-5.641776800000001</v>
+        <v>-5.755904000000002</v>
       </c>
       <c r="O71">
-        <v>-1.241190896</v>
+        <v>-1.26629888</v>
       </c>
       <c r="P71">
-        <v>-4.400585904000001</v>
+        <v>-4.489605120000002</v>
       </c>
       <c r="Q71">
-        <v>-2.333585904000001</v>
+        <v>-2.422605120000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2094853752176778</v>
+        <v>0.2149415543916004</v>
       </c>
       <c r="T71">
-        <v>2.13336916180899</v>
+        <v>2.204481467202623</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06238399036274907</v>
+        <v>0.06149279050042408</v>
       </c>
       <c r="W71">
-        <v>0.2210898550724638</v>
+        <v>0.2213</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2835635925579504</v>
+        <v>0.2795126840928367</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2193924663174801</v>
+        <v>0.2212924663174801</v>
       </c>
       <c r="C72">
-        <v>-17.32386557374573</v>
+        <v>-17.96773372078703</v>
       </c>
       <c r="D72">
-        <v>14.76613442625427</v>
+        <v>14.60626627921297</v>
       </c>
       <c r="E72">
-        <v>20.18000000000001</v>
+        <v>20.66400000000001</v>
       </c>
       <c r="F72">
-        <v>33.88000000000001</v>
+        <v>34.364</v>
       </c>
       <c r="G72">
         <v>1.79</v>
@@ -7191,37 +7191,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M72">
-        <v>7.988904000000002</v>
+        <v>8.103031200000002</v>
       </c>
       <c r="N72">
-        <v>-5.755904000000002</v>
+        <v>-5.870031200000001</v>
       </c>
       <c r="O72">
-        <v>-1.26629888</v>
+        <v>-1.291406864</v>
       </c>
       <c r="P72">
-        <v>-4.489605120000002</v>
+        <v>-4.578624336000001</v>
       </c>
       <c r="Q72">
-        <v>-2.422605120000002</v>
+        <v>-2.511624336000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2149415543916004</v>
+        <v>0.2207740217844143</v>
       </c>
       <c r="T72">
-        <v>2.204481467202623</v>
+        <v>2.280498069519956</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06149279050042408</v>
+        <v>0.06062669485957305</v>
       </c>
       <c r="W72">
-        <v>0.2213</v>
+        <v>0.2215042253521127</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2795126840928367</v>
+        <v>0.275575885725332</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2212924663174801</v>
+        <v>0.2231924663174801</v>
       </c>
       <c r="C73">
-        <v>-17.96773372078703</v>
+        <v>-18.60817726377739</v>
       </c>
       <c r="D73">
-        <v>14.60626627921297</v>
+        <v>14.44982273622261</v>
       </c>
       <c r="E73">
-        <v>20.66400000000001</v>
+        <v>21.14800000000001</v>
       </c>
       <c r="F73">
-        <v>34.364</v>
+        <v>34.84800000000001</v>
       </c>
       <c r="G73">
         <v>1.79</v>
@@ -7273,37 +7273,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M73">
-        <v>8.103031200000002</v>
+        <v>8.217158400000002</v>
       </c>
       <c r="N73">
-        <v>-5.870031200000001</v>
+        <v>-5.984158400000002</v>
       </c>
       <c r="O73">
-        <v>-1.291406864</v>
+        <v>-1.316514848</v>
       </c>
       <c r="P73">
-        <v>-4.578624336000001</v>
+        <v>-4.667643552000001</v>
       </c>
       <c r="Q73">
-        <v>-2.511624336000001</v>
+        <v>-2.600643552000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2207740217844142</v>
+        <v>0.2270230939910004</v>
       </c>
       <c r="T73">
-        <v>2.280498069519955</v>
+        <v>2.361944429145668</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06062669485957305</v>
+        <v>0.05978465743096786</v>
       </c>
       <c r="W73">
-        <v>0.2215042253521127</v>
+        <v>0.2217027777777778</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.275575885725332</v>
+        <v>0.2717484428680357</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2231924663174801</v>
+        <v>0.2250924663174801</v>
       </c>
       <c r="C74">
-        <v>-18.60817726377739</v>
+        <v>-19.24530507646645</v>
       </c>
       <c r="D74">
-        <v>14.44982273622261</v>
+        <v>14.29669492353355</v>
       </c>
       <c r="E74">
-        <v>21.14800000000001</v>
+        <v>21.632</v>
       </c>
       <c r="F74">
-        <v>34.84800000000001</v>
+        <v>35.332</v>
       </c>
       <c r="G74">
         <v>1.79</v>
@@ -7355,37 +7355,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M74">
-        <v>8.217158400000002</v>
+        <v>8.331285600000001</v>
       </c>
       <c r="N74">
-        <v>-5.984158400000002</v>
+        <v>-6.098285600000001</v>
       </c>
       <c r="O74">
-        <v>-1.316514848</v>
+        <v>-1.341622832</v>
       </c>
       <c r="P74">
-        <v>-4.667643552000001</v>
+        <v>-4.756662768</v>
       </c>
       <c r="Q74">
-        <v>-2.600643552000001</v>
+        <v>-2.689662768</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2270230939910004</v>
+        <v>0.2337350604351116</v>
       </c>
       <c r="T74">
-        <v>2.361944429145668</v>
+        <v>2.449423852447359</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05978465743096786</v>
+        <v>0.05896568952095461</v>
       </c>
       <c r="W74">
-        <v>0.2217027777777778</v>
+        <v>0.2218958904109589</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2717484428680357</v>
+        <v>0.2680258614588846</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2250924663174801</v>
+        <v>0.2269924663174801</v>
       </c>
       <c r="C75">
-        <v>-19.24530507646645</v>
+        <v>-19.87922146596533</v>
       </c>
       <c r="D75">
-        <v>14.29669492353355</v>
+        <v>14.14677853403467</v>
       </c>
       <c r="E75">
-        <v>21.632</v>
+        <v>22.116</v>
       </c>
       <c r="F75">
-        <v>35.332</v>
+        <v>35.816</v>
       </c>
       <c r="G75">
         <v>1.79</v>
@@ -7437,37 +7437,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M75">
-        <v>8.331285600000001</v>
+        <v>8.445412800000001</v>
       </c>
       <c r="N75">
-        <v>-6.098285600000001</v>
+        <v>-6.212412800000001</v>
       </c>
       <c r="O75">
-        <v>-1.341622832</v>
+        <v>-1.366730816</v>
       </c>
       <c r="P75">
-        <v>-4.756662768</v>
+        <v>-4.845681984</v>
       </c>
       <c r="Q75">
-        <v>-2.689662768</v>
+        <v>-2.778681984</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2337350604351116</v>
+        <v>0.2409633319903081</v>
       </c>
       <c r="T75">
-        <v>2.449423852447359</v>
+        <v>2.543632462156872</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05896568952095461</v>
+        <v>0.05816885587877955</v>
       </c>
       <c r="W75">
-        <v>0.2218958904109589</v>
+        <v>0.2220837837837838</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2680258614588846</v>
+        <v>0.2644038903580889</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2269924663174801</v>
+        <v>0.2288924663174801</v>
       </c>
       <c r="C76">
-        <v>-19.87922146596533</v>
+        <v>-20.51002640969282</v>
       </c>
       <c r="D76">
-        <v>14.14677853403467</v>
+        <v>13.99997359030719</v>
       </c>
       <c r="E76">
-        <v>22.116</v>
+        <v>22.6</v>
       </c>
       <c r="F76">
-        <v>35.816</v>
+        <v>36.3</v>
       </c>
       <c r="G76">
         <v>1.79</v>
@@ -7519,37 +7519,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M76">
-        <v>8.445412800000001</v>
+        <v>8.559540000000002</v>
       </c>
       <c r="N76">
-        <v>-6.212412800000001</v>
+        <v>-6.326540000000001</v>
       </c>
       <c r="O76">
-        <v>-1.366730816</v>
+        <v>-1.3918388</v>
       </c>
       <c r="P76">
-        <v>-4.845681984</v>
+        <v>-4.934701200000001</v>
       </c>
       <c r="Q76">
-        <v>-2.778681984</v>
+        <v>-2.867701200000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2409633319903081</v>
+        <v>0.2487698652699205</v>
       </c>
       <c r="T76">
-        <v>2.543632462156872</v>
+        <v>2.645377760643147</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05816885587877955</v>
+        <v>0.05739327113372916</v>
       </c>
       <c r="W76">
-        <v>0.2220837837837838</v>
+        <v>0.2222666666666667</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2644038903580889</v>
+        <v>0.2608785051533143</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2288924663174801</v>
+        <v>0.2307924663174801</v>
       </c>
       <c r="C77">
-        <v>-20.51002640969282</v>
+        <v>-21.13781577772003</v>
       </c>
       <c r="D77">
-        <v>13.99997359030719</v>
+        <v>13.85618422227998</v>
       </c>
       <c r="E77">
-        <v>22.6</v>
+        <v>23.08400000000001</v>
       </c>
       <c r="F77">
-        <v>36.3</v>
+        <v>36.78400000000001</v>
       </c>
       <c r="G77">
         <v>1.79</v>
@@ -7601,37 +7601,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M77">
-        <v>8.559540000000002</v>
+        <v>8.673667200000002</v>
       </c>
       <c r="N77">
-        <v>-6.326540000000001</v>
+        <v>-6.440667200000002</v>
       </c>
       <c r="O77">
-        <v>-1.3918388</v>
+        <v>-1.416946784000001</v>
       </c>
       <c r="P77">
-        <v>-4.934701200000001</v>
+        <v>-5.023720416000002</v>
       </c>
       <c r="Q77">
-        <v>-2.867701200000001</v>
+        <v>-2.956720416000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2487698652699205</v>
+        <v>0.2572269429895005</v>
       </c>
       <c r="T77">
-        <v>2.645377760643147</v>
+        <v>2.755601834003279</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05739327113372916</v>
+        <v>0.0566380965135485</v>
       </c>
       <c r="W77">
-        <v>0.2222666666666667</v>
+        <v>0.2224447368421053</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2608785051533143</v>
+        <v>0.2574458932434023</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2307924663174801</v>
+        <v>0.2326924663174801</v>
       </c>
       <c r="C78">
-        <v>-21.13781577772003</v>
+        <v>-21.76268154155242</v>
       </c>
       <c r="D78">
-        <v>13.85618422227998</v>
+        <v>13.71531845844759</v>
       </c>
       <c r="E78">
-        <v>23.08400000000001</v>
+        <v>23.56800000000001</v>
       </c>
       <c r="F78">
-        <v>36.78400000000001</v>
+        <v>37.26800000000001</v>
       </c>
       <c r="G78">
         <v>1.79</v>
@@ -7683,37 +7683,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M78">
-        <v>8.673667200000002</v>
+        <v>8.787794400000003</v>
       </c>
       <c r="N78">
-        <v>-6.440667200000002</v>
+        <v>-6.554794400000002</v>
       </c>
       <c r="O78">
-        <v>-1.416946784000001</v>
+        <v>-1.442054768</v>
       </c>
       <c r="P78">
-        <v>-5.023720416000002</v>
+        <v>-5.112739632000002</v>
       </c>
       <c r="Q78">
-        <v>-2.956720416000001</v>
+        <v>-3.045739632000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2572269429895005</v>
+        <v>0.2664194187716527</v>
       </c>
       <c r="T78">
-        <v>2.755601834003279</v>
+        <v>2.875410609394726</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0566380965135485</v>
+        <v>0.05590253681856735</v>
       </c>
       <c r="W78">
-        <v>0.2224447368421053</v>
+        <v>0.2226181818181818</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2574458932434023</v>
+        <v>0.2541024400843971</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2326924663174801</v>
+        <v>0.2345924663174801</v>
       </c>
       <c r="C79">
-        <v>-21.76268154155242</v>
+        <v>-22.38471197030496</v>
       </c>
       <c r="D79">
-        <v>13.71531845844759</v>
+        <v>13.57728802969504</v>
       </c>
       <c r="E79">
-        <v>23.56800000000001</v>
+        <v>24.052</v>
       </c>
       <c r="F79">
-        <v>37.26800000000001</v>
+        <v>37.752</v>
       </c>
       <c r="G79">
         <v>1.79</v>
@@ -7765,37 +7765,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M79">
-        <v>8.787794400000003</v>
+        <v>8.901921600000001</v>
       </c>
       <c r="N79">
-        <v>-6.554794400000002</v>
+        <v>-6.668921600000001</v>
       </c>
       <c r="O79">
-        <v>-1.442054768</v>
+        <v>-1.467162752</v>
       </c>
       <c r="P79">
-        <v>-5.112739632000002</v>
+        <v>-5.201758848000001</v>
       </c>
       <c r="Q79">
-        <v>-3.045739632000002</v>
+        <v>-3.134758848000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2664194187716527</v>
+        <v>0.2764475741703642</v>
       </c>
       <c r="T79">
-        <v>2.875410609394726</v>
+        <v>3.006111091639941</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05590253681856735</v>
+        <v>0.05518583762858573</v>
       </c>
       <c r="W79">
-        <v>0.2226181818181818</v>
+        <v>0.2227871794871795</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2541024400843971</v>
+        <v>0.2508447164935714</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2345924663174801</v>
+        <v>0.2364924663174801</v>
       </c>
       <c r="C80">
-        <v>-22.38471197030496</v>
+        <v>-23.00399181514933</v>
       </c>
       <c r="D80">
-        <v>13.57728802969504</v>
+        <v>13.44200818485068</v>
       </c>
       <c r="E80">
-        <v>24.052</v>
+        <v>24.536</v>
       </c>
       <c r="F80">
-        <v>37.752</v>
+        <v>38.236</v>
       </c>
       <c r="G80">
         <v>1.79</v>
@@ -7847,37 +7847,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M80">
-        <v>8.901921600000001</v>
+        <v>9.016048800000002</v>
       </c>
       <c r="N80">
-        <v>-6.668921600000001</v>
+        <v>-6.783048800000001</v>
       </c>
       <c r="O80">
-        <v>-1.467162752</v>
+        <v>-1.492270736</v>
       </c>
       <c r="P80">
-        <v>-5.201758848000001</v>
+        <v>-5.290778064000001</v>
       </c>
       <c r="Q80">
-        <v>-3.134758848000001</v>
+        <v>-3.223778064000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2764475741703642</v>
+        <v>0.2874307919880006</v>
       </c>
       <c r="T80">
-        <v>3.006111091639941</v>
+        <v>3.149259238860891</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05518583762858573</v>
+        <v>0.05448728272189476</v>
       </c>
       <c r="W80">
-        <v>0.2227871794871795</v>
+        <v>0.2229518987341772</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2508447164935714</v>
+        <v>0.2476694669177034</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2364924663174801</v>
+        <v>0.2383924663174802</v>
       </c>
       <c r="C81">
-        <v>-23.00399181514933</v>
+        <v>-23.62060248284345</v>
       </c>
       <c r="D81">
-        <v>13.44200818485068</v>
+        <v>13.30939751715655</v>
       </c>
       <c r="E81">
-        <v>24.536</v>
+        <v>25.02000000000001</v>
       </c>
       <c r="F81">
-        <v>38.236</v>
+        <v>38.72000000000001</v>
       </c>
       <c r="G81">
         <v>1.79</v>
@@ -7929,37 +7929,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M81">
-        <v>9.016048800000002</v>
+        <v>9.130176000000002</v>
       </c>
       <c r="N81">
-        <v>-6.783048800000001</v>
+        <v>-6.897176000000002</v>
       </c>
       <c r="O81">
-        <v>-1.492270736</v>
+        <v>-1.51737872</v>
       </c>
       <c r="P81">
-        <v>-5.290778064000001</v>
+        <v>-5.379797280000002</v>
       </c>
       <c r="Q81">
-        <v>-3.223778064000001</v>
+        <v>-3.312797280000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2874307919880006</v>
+        <v>0.2995123315874006</v>
       </c>
       <c r="T81">
-        <v>3.149259238860891</v>
+        <v>3.306722200803935</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05448728272189476</v>
+        <v>0.05380619168787108</v>
       </c>
       <c r="W81">
-        <v>0.2229518987341772</v>
+        <v>0.2231125</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2476694669177034</v>
+        <v>0.2445735985812322</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2383924663174802</v>
+        <v>0.2402924663174801</v>
       </c>
       <c r="C82">
-        <v>-23.62060248284345</v>
+        <v>-24.23462219908951</v>
       </c>
       <c r="D82">
-        <v>13.30939751715655</v>
+        <v>13.17937780091049</v>
       </c>
       <c r="E82">
-        <v>25.02000000000001</v>
+        <v>25.50400000000001</v>
       </c>
       <c r="F82">
-        <v>38.72000000000001</v>
+        <v>39.20400000000001</v>
       </c>
       <c r="G82">
         <v>1.79</v>
@@ -8011,37 +8011,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M82">
-        <v>9.130176000000002</v>
+        <v>9.244303200000003</v>
       </c>
       <c r="N82">
-        <v>-6.897176000000002</v>
+        <v>-7.011303200000002</v>
       </c>
       <c r="O82">
-        <v>-1.51737872</v>
+        <v>-1.542486704000001</v>
       </c>
       <c r="P82">
-        <v>-5.379797280000002</v>
+        <v>-5.468816496000001</v>
       </c>
       <c r="Q82">
-        <v>-3.312797280000002</v>
+        <v>-3.401816496000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2995123315874006</v>
+        <v>0.3128656121972638</v>
       </c>
       <c r="T82">
-        <v>3.306722200803935</v>
+        <v>3.480760211372564</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05380619168787108</v>
+        <v>0.05314191771641587</v>
       </c>
       <c r="W82">
-        <v>0.2231125</v>
+        <v>0.2232691358024692</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2445735985812322</v>
+        <v>0.241554171438254</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2402924663174801</v>
+        <v>0.2421924663174801</v>
       </c>
       <c r="C83">
-        <v>-24.23462219908951</v>
+        <v>-24.84612616240983</v>
       </c>
       <c r="D83">
-        <v>13.17937780091049</v>
+        <v>13.05187383759018</v>
       </c>
       <c r="E83">
-        <v>25.50400000000001</v>
+        <v>25.98800000000001</v>
       </c>
       <c r="F83">
-        <v>39.20400000000001</v>
+        <v>39.68800000000001</v>
       </c>
       <c r="G83">
         <v>1.79</v>
@@ -8093,37 +8093,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M83">
-        <v>9.244303200000003</v>
+        <v>9.358430400000003</v>
       </c>
       <c r="N83">
-        <v>-7.011303200000002</v>
+        <v>-7.125430400000003</v>
       </c>
       <c r="O83">
-        <v>-1.542486704000001</v>
+        <v>-1.567594688000001</v>
       </c>
       <c r="P83">
-        <v>-5.468816496000001</v>
+        <v>-5.557835712000002</v>
       </c>
       <c r="Q83">
-        <v>-3.401816496000001</v>
+        <v>-3.490835712000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3128656121972638</v>
+        <v>0.3277025906526674</v>
       </c>
       <c r="T83">
-        <v>3.480760211372564</v>
+        <v>3.674135778671039</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05314191771641587</v>
+        <v>0.05249384554914251</v>
       </c>
       <c r="W83">
-        <v>0.2232691358024692</v>
+        <v>0.2234219512195122</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.241554171438254</v>
+        <v>0.2386083888597387</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2421924663174801</v>
+        <v>0.2440924663174801</v>
       </c>
       <c r="C84">
-        <v>-24.84612616240983</v>
+        <v>-25.45518668917597</v>
       </c>
       <c r="D84">
-        <v>13.05187383759018</v>
+        <v>12.92681331082404</v>
       </c>
       <c r="E84">
-        <v>25.98800000000001</v>
+        <v>26.47200000000001</v>
       </c>
       <c r="F84">
-        <v>39.68800000000001</v>
+        <v>40.17200000000001</v>
       </c>
       <c r="G84">
         <v>1.79</v>
@@ -8175,37 +8175,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M84">
-        <v>9.358430400000003</v>
+        <v>9.472557600000004</v>
       </c>
       <c r="N84">
-        <v>-7.125430400000003</v>
+        <v>-7.239557600000003</v>
       </c>
       <c r="O84">
-        <v>-1.567594688000001</v>
+        <v>-1.592702672000001</v>
       </c>
       <c r="P84">
-        <v>-5.557835712000002</v>
+        <v>-5.646854928000002</v>
       </c>
       <c r="Q84">
-        <v>-3.490835712000002</v>
+        <v>-3.579854928000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3277025906526674</v>
+        <v>0.3442850959851773</v>
       </c>
       <c r="T84">
-        <v>3.674135778671039</v>
+        <v>3.890261412710513</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05249384554914251</v>
+        <v>0.05186138957867091</v>
       </c>
       <c r="W84">
-        <v>0.2234219512195122</v>
+        <v>0.2235710843373494</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2386083888597387</v>
+        <v>0.2357335889939587</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2440924663174801</v>
+        <v>0.2459924663174801</v>
       </c>
       <c r="C85">
-        <v>-25.45518668917597</v>
+        <v>-26.06187335037937</v>
       </c>
       <c r="D85">
-        <v>12.92681331082404</v>
+        <v>12.80412664962063</v>
       </c>
       <c r="E85">
-        <v>26.47200000000001</v>
+        <v>26.95600000000001</v>
       </c>
       <c r="F85">
-        <v>40.17200000000001</v>
+        <v>40.65600000000001</v>
       </c>
       <c r="G85">
         <v>1.79</v>
@@ -8257,37 +8257,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M85">
-        <v>9.472557600000004</v>
+        <v>9.586684800000002</v>
       </c>
       <c r="N85">
-        <v>-7.239557600000003</v>
+        <v>-7.353684800000002</v>
       </c>
       <c r="O85">
-        <v>-1.592702672000001</v>
+        <v>-1.617810656</v>
       </c>
       <c r="P85">
-        <v>-5.646854928000002</v>
+        <v>-5.735874144000001</v>
       </c>
       <c r="Q85">
-        <v>-3.579854928000002</v>
+        <v>-3.668874144000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3442850959851773</v>
+        <v>0.3629404144842509</v>
       </c>
       <c r="T85">
-        <v>3.890261412710513</v>
+        <v>4.13340275100492</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05186138957867091</v>
+        <v>0.05124399208368675</v>
       </c>
       <c r="W85">
-        <v>0.2235710843373494</v>
+        <v>0.2237166666666667</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2357335889939587</v>
+        <v>0.2329272367440306</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2459924663174801</v>
+        <v>0.2478924663174801</v>
       </c>
       <c r="C86">
-        <v>-26.06187335037937</v>
+        <v>-26.66625310068664</v>
       </c>
       <c r="D86">
-        <v>12.80412664962064</v>
+        <v>12.68374689931336</v>
       </c>
       <c r="E86">
-        <v>26.95600000000001</v>
+        <v>27.44</v>
       </c>
       <c r="F86">
-        <v>40.65600000000001</v>
+        <v>41.14</v>
       </c>
       <c r="G86">
         <v>1.79</v>
@@ -8339,37 +8339,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M86">
-        <v>9.586684800000002</v>
+        <v>9.700812000000001</v>
       </c>
       <c r="N86">
-        <v>-7.353684800000002</v>
+        <v>-7.467812</v>
       </c>
       <c r="O86">
-        <v>-1.617810656</v>
+        <v>-1.64291864</v>
       </c>
       <c r="P86">
-        <v>-5.735874144000001</v>
+        <v>-5.824893360000001</v>
       </c>
       <c r="Q86">
-        <v>-3.668874144000001</v>
+        <v>-3.757893360000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3629404144842507</v>
+        <v>0.3840831087832007</v>
       </c>
       <c r="T86">
-        <v>4.133402751004918</v>
+        <v>4.408962934405245</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05124399208368675</v>
+        <v>0.05064112158858455</v>
       </c>
       <c r="W86">
-        <v>0.2237166666666667</v>
+        <v>0.2238588235294118</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2329272367440306</v>
+        <v>0.2301869163117479</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2478924663174801</v>
+        <v>0.2497924663174801</v>
       </c>
       <c r="C87">
-        <v>-26.66625310068664</v>
+        <v>-27.26839040028274</v>
       </c>
       <c r="D87">
-        <v>12.68374689931336</v>
+        <v>12.56560959971726</v>
       </c>
       <c r="E87">
-        <v>27.44</v>
+        <v>27.924</v>
       </c>
       <c r="F87">
-        <v>41.14</v>
+        <v>41.624</v>
       </c>
       <c r="G87">
         <v>1.79</v>
@@ -8421,37 +8421,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M87">
-        <v>9.700812000000001</v>
+        <v>9.814939200000001</v>
       </c>
       <c r="N87">
-        <v>-7.467812</v>
+        <v>-7.581939200000001</v>
       </c>
       <c r="O87">
-        <v>-1.64291864</v>
+        <v>-1.668026624</v>
       </c>
       <c r="P87">
-        <v>-5.824893360000001</v>
+        <v>-5.913912576</v>
       </c>
       <c r="Q87">
-        <v>-3.757893360000001</v>
+        <v>-3.846912576</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3840831087832007</v>
+        <v>0.4082461879820008</v>
       </c>
       <c r="T87">
-        <v>4.408962934405245</v>
+        <v>4.723888858291335</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05064112158858455</v>
+        <v>0.0500522713375545</v>
       </c>
       <c r="W87">
-        <v>0.2238588235294118</v>
+        <v>0.2239976744186047</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2301869163117479</v>
+        <v>0.2275103242616113</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2497924663174801</v>
+        <v>0.2516924663174801</v>
       </c>
       <c r="C88">
-        <v>-27.26839040028274</v>
+        <v>-27.86834732996781</v>
       </c>
       <c r="D88">
-        <v>12.56560959971726</v>
+        <v>12.44965267003219</v>
       </c>
       <c r="E88">
-        <v>27.924</v>
+        <v>28.408</v>
       </c>
       <c r="F88">
-        <v>41.624</v>
+        <v>42.108</v>
       </c>
       <c r="G88">
         <v>1.79</v>
@@ -8503,37 +8503,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M88">
-        <v>9.814939200000001</v>
+        <v>9.929066400000002</v>
       </c>
       <c r="N88">
-        <v>-7.581939200000001</v>
+        <v>-7.696066400000001</v>
       </c>
       <c r="O88">
-        <v>-1.668026624</v>
+        <v>-1.693134608</v>
       </c>
       <c r="P88">
-        <v>-5.913912576</v>
+        <v>-6.002931792000001</v>
       </c>
       <c r="Q88">
-        <v>-3.846912576</v>
+        <v>-3.935931792000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4082461879820008</v>
+        <v>0.4361266639806162</v>
       </c>
       <c r="T88">
-        <v>4.723888858291335</v>
+        <v>5.087264924313745</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0500522713375545</v>
+        <v>0.04947695787390444</v>
       </c>
       <c r="W88">
-        <v>0.2239976744186047</v>
+        <v>0.2241333333333333</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2275103242616113</v>
+        <v>0.224895263063202</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2516924663174801</v>
+        <v>0.2535924663174801</v>
       </c>
       <c r="C89">
-        <v>-27.86834732996781</v>
+        <v>-28.46618369993957</v>
       </c>
       <c r="D89">
-        <v>12.44965267003219</v>
+        <v>12.33581630006043</v>
       </c>
       <c r="E89">
-        <v>28.408</v>
+        <v>28.89200000000001</v>
       </c>
       <c r="F89">
-        <v>42.108</v>
+        <v>42.59200000000001</v>
       </c>
       <c r="G89">
         <v>1.79</v>
@@ -8585,37 +8585,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M89">
-        <v>9.929066400000002</v>
+        <v>10.0431936</v>
       </c>
       <c r="N89">
-        <v>-7.696066400000001</v>
+        <v>-7.810193600000002</v>
       </c>
       <c r="O89">
-        <v>-1.693134608</v>
+        <v>-1.718242592</v>
       </c>
       <c r="P89">
-        <v>-6.002931792000001</v>
+        <v>-6.091951008000001</v>
       </c>
       <c r="Q89">
-        <v>-3.935931792000001</v>
+        <v>-4.024951008000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4361266639806162</v>
+        <v>0.468653885979001</v>
       </c>
       <c r="T89">
-        <v>5.087264924313745</v>
+        <v>5.511203668006559</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04947695787390444</v>
+        <v>0.04891471971624644</v>
       </c>
       <c r="W89">
-        <v>0.2241333333333333</v>
+        <v>0.2242659090909091</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.224895263063202</v>
+        <v>0.2223396350738475</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2535924663174801</v>
+        <v>0.2554924663174801</v>
       </c>
       <c r="C90">
-        <v>-28.46618369993957</v>
+        <v>-29.06195715266167</v>
       </c>
       <c r="D90">
-        <v>12.33581630006043</v>
+        <v>12.22404284733834</v>
       </c>
       <c r="E90">
-        <v>28.89200000000001</v>
+        <v>29.37600000000001</v>
       </c>
       <c r="F90">
-        <v>42.59200000000001</v>
+        <v>43.07600000000001</v>
       </c>
       <c r="G90">
         <v>1.79</v>
@@ -8667,37 +8667,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M90">
-        <v>10.0431936</v>
+        <v>10.1573208</v>
       </c>
       <c r="N90">
-        <v>-7.810193600000002</v>
+        <v>-7.924320800000002</v>
       </c>
       <c r="O90">
-        <v>-1.718242592</v>
+        <v>-1.743350576000001</v>
       </c>
       <c r="P90">
-        <v>-6.091951008000001</v>
+        <v>-6.180970224000001</v>
       </c>
       <c r="Q90">
-        <v>-4.024951008000001</v>
+        <v>-4.113970224000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.468653885979001</v>
+        <v>0.5070951483407284</v>
       </c>
       <c r="T90">
-        <v>5.511203668006559</v>
+        <v>6.012222183279882</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04891471971624644</v>
+        <v>0.04836511612392906</v>
       </c>
       <c r="W90">
-        <v>0.2242659090909091</v>
+        <v>0.2243955056179776</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2223396350738475</v>
+        <v>0.2198414369269502</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2554924663174801</v>
+        <v>0.2573924663174801</v>
       </c>
       <c r="C91">
-        <v>-29.06195715266167</v>
+        <v>-29.65572326018978</v>
       </c>
       <c r="D91">
-        <v>12.22404284733834</v>
+        <v>12.11427673981023</v>
       </c>
       <c r="E91">
-        <v>29.37600000000001</v>
+        <v>29.86000000000001</v>
       </c>
       <c r="F91">
-        <v>43.07600000000001</v>
+        <v>43.56000000000001</v>
       </c>
       <c r="G91">
         <v>1.79</v>
@@ -8749,37 +8749,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M91">
-        <v>10.1573208</v>
+        <v>10.271448</v>
       </c>
       <c r="N91">
-        <v>-7.924320800000002</v>
+        <v>-8.038448000000002</v>
       </c>
       <c r="O91">
-        <v>-1.743350576000001</v>
+        <v>-1.76845856</v>
       </c>
       <c r="P91">
-        <v>-6.180970224000001</v>
+        <v>-6.269989440000002</v>
       </c>
       <c r="Q91">
-        <v>-4.113970224000001</v>
+        <v>-4.202989440000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5070951483407284</v>
+        <v>0.5532246631748012</v>
       </c>
       <c r="T91">
-        <v>6.012222183279882</v>
+        <v>6.613444401607871</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04836511612392906</v>
+        <v>0.04782772594477429</v>
       </c>
       <c r="W91">
-        <v>0.2243955056179776</v>
+        <v>0.2245222222222222</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2198414369269502</v>
+        <v>0.2173987542944286</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2573924663174801</v>
+        <v>0.2592924663174802</v>
       </c>
       <c r="C92">
-        <v>-29.65572326018978</v>
+        <v>-30.24753561630079</v>
       </c>
       <c r="D92">
-        <v>12.11427673981023</v>
+        <v>12.00646438369921</v>
       </c>
       <c r="E92">
-        <v>29.86000000000001</v>
+        <v>30.344</v>
       </c>
       <c r="F92">
-        <v>43.56000000000001</v>
+        <v>44.044</v>
       </c>
       <c r="G92">
         <v>1.79</v>
@@ -8831,37 +8831,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M92">
-        <v>10.271448</v>
+        <v>10.3855752</v>
       </c>
       <c r="N92">
-        <v>-8.038448000000002</v>
+        <v>-8.152575200000001</v>
       </c>
       <c r="O92">
-        <v>-1.76845856</v>
+        <v>-1.793566544</v>
       </c>
       <c r="P92">
-        <v>-6.269989440000002</v>
+        <v>-6.359008656000001</v>
       </c>
       <c r="Q92">
-        <v>-4.202989440000001</v>
+        <v>-4.292008656000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5532246631748012</v>
+        <v>0.6096051813053347</v>
       </c>
       <c r="T92">
-        <v>6.613444401607871</v>
+        <v>7.348271557342079</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04782772594477429</v>
+        <v>0.04730214653878777</v>
       </c>
       <c r="W92">
-        <v>0.2245222222222222</v>
+        <v>0.2246461538461539</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2173987542944286</v>
+        <v>0.2150097569944899</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2592924663174802</v>
+        <v>0.2611924663174802</v>
       </c>
       <c r="C93">
-        <v>-30.24753561630079</v>
+        <v>-30.83744592374583</v>
       </c>
       <c r="D93">
-        <v>12.00646438369921</v>
+        <v>11.90055407625418</v>
       </c>
       <c r="E93">
-        <v>30.344</v>
+        <v>30.82800000000001</v>
       </c>
       <c r="F93">
-        <v>44.044</v>
+        <v>44.52800000000001</v>
       </c>
       <c r="G93">
         <v>1.79</v>
@@ -8913,37 +8913,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M93">
-        <v>10.3855752</v>
+        <v>10.4997024</v>
       </c>
       <c r="N93">
-        <v>-8.152575200000001</v>
+        <v>-8.266702400000002</v>
       </c>
       <c r="O93">
-        <v>-1.793566544</v>
+        <v>-1.818674528</v>
       </c>
       <c r="P93">
-        <v>-6.359008656000001</v>
+        <v>-6.448027872000001</v>
       </c>
       <c r="Q93">
-        <v>-4.292008656000001</v>
+        <v>-4.381027872000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6096051813053347</v>
+        <v>0.6800808289685017</v>
       </c>
       <c r="T93">
-        <v>7.348271557342079</v>
+        <v>8.266805502009841</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04730214653878777</v>
+        <v>0.04678799277206181</v>
       </c>
       <c r="W93">
-        <v>0.2246461538461539</v>
+        <v>0.2247673913043478</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2150097569944899</v>
+        <v>0.2126726944184628</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2611924663174802</v>
+        <v>0.2630924663174801</v>
       </c>
       <c r="C94">
-        <v>-30.83744592374583</v>
+        <v>-31.42550407692564</v>
       </c>
       <c r="D94">
-        <v>11.90055407625418</v>
+        <v>11.79649592307437</v>
       </c>
       <c r="E94">
-        <v>30.82800000000001</v>
+        <v>31.31200000000001</v>
       </c>
       <c r="F94">
-        <v>44.52800000000001</v>
+        <v>45.01200000000001</v>
       </c>
       <c r="G94">
         <v>1.79</v>
@@ -8995,37 +8995,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M94">
-        <v>10.4997024</v>
+        <v>10.6138296</v>
       </c>
       <c r="N94">
-        <v>-8.266702400000002</v>
+        <v>-8.380829600000002</v>
       </c>
       <c r="O94">
-        <v>-1.818674528</v>
+        <v>-1.843782512</v>
       </c>
       <c r="P94">
-        <v>-6.448027872000001</v>
+        <v>-6.537047088000001</v>
       </c>
       <c r="Q94">
-        <v>-4.381027872000001</v>
+        <v>-4.470047088000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6800808289685017</v>
+        <v>0.7706923759640021</v>
       </c>
       <c r="T94">
-        <v>8.266805502009841</v>
+        <v>9.447777716582676</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04678799277206181</v>
+        <v>0.04628489607558803</v>
       </c>
       <c r="W94">
-        <v>0.2247673913043478</v>
+        <v>0.2248860215053763</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2126726944184628</v>
+        <v>0.2103858912526728</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2630924663174801</v>
+        <v>0.2649924663174802</v>
       </c>
       <c r="C95">
-        <v>-31.42550407692564</v>
+        <v>-32.01175824026618</v>
       </c>
       <c r="D95">
-        <v>11.79649592307437</v>
+        <v>11.69424175973384</v>
       </c>
       <c r="E95">
-        <v>31.31200000000001</v>
+        <v>31.79600000000001</v>
       </c>
       <c r="F95">
-        <v>45.01200000000001</v>
+        <v>45.49600000000001</v>
       </c>
       <c r="G95">
         <v>1.79</v>
@@ -9077,37 +9077,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M95">
-        <v>10.6138296</v>
+        <v>10.7279568</v>
       </c>
       <c r="N95">
-        <v>-8.380829600000002</v>
+        <v>-8.494956800000002</v>
       </c>
       <c r="O95">
-        <v>-1.843782512</v>
+        <v>-1.868890496000001</v>
       </c>
       <c r="P95">
-        <v>-6.537047088000001</v>
+        <v>-6.626066304000002</v>
       </c>
       <c r="Q95">
-        <v>-4.470047088000001</v>
+        <v>-4.559066304000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7706923759640021</v>
+        <v>0.8915077719580027</v>
       </c>
       <c r="T95">
-        <v>9.447777716582676</v>
+        <v>11.02240733601313</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04628489607558803</v>
+        <v>0.0457925035641456</v>
       </c>
       <c r="W95">
-        <v>0.2248860215053763</v>
+        <v>0.2250021276595745</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2103858912526728</v>
+        <v>0.208147743473389</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2649924663174802</v>
+        <v>0.2668924663174801</v>
       </c>
       <c r="C96">
-        <v>-32.01175824026618</v>
+        <v>-32.59625492255289</v>
       </c>
       <c r="D96">
-        <v>11.69424175973384</v>
+        <v>11.59374507744712</v>
       </c>
       <c r="E96">
-        <v>31.79600000000001</v>
+        <v>32.28000000000002</v>
       </c>
       <c r="F96">
-        <v>45.49600000000001</v>
+        <v>45.98000000000001</v>
       </c>
       <c r="G96">
         <v>1.79</v>
@@ -9159,37 +9159,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M96">
-        <v>10.7279568</v>
+        <v>10.842084</v>
       </c>
       <c r="N96">
-        <v>-8.494956800000002</v>
+        <v>-8.609084000000003</v>
       </c>
       <c r="O96">
-        <v>-1.868890496000001</v>
+        <v>-1.893998480000001</v>
       </c>
       <c r="P96">
-        <v>-6.626066304000002</v>
+        <v>-6.715085520000002</v>
       </c>
       <c r="Q96">
-        <v>-4.559066304000002</v>
+        <v>-4.648085520000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8915077719580027</v>
+        <v>1.060649326349604</v>
       </c>
       <c r="T96">
-        <v>11.02240733601313</v>
+        <v>13.22688880321576</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0457925035641456</v>
+        <v>0.0453104772108388</v>
       </c>
       <c r="W96">
-        <v>0.2250021276595745</v>
+        <v>0.2251157894736842</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.208147743473389</v>
+        <v>0.2059567145947218</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2668924663174801</v>
+        <v>0.2687924663174802</v>
       </c>
       <c r="C97">
-        <v>-32.59625492255289</v>
+        <v>-33.17903904746492</v>
       </c>
       <c r="D97">
-        <v>11.59374507744712</v>
+        <v>11.49496095253509</v>
       </c>
       <c r="E97">
-        <v>32.28000000000002</v>
+        <v>32.76400000000001</v>
       </c>
       <c r="F97">
-        <v>45.98000000000001</v>
+        <v>46.46400000000001</v>
       </c>
       <c r="G97">
         <v>1.79</v>
@@ -9241,37 +9241,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M97">
-        <v>10.842084</v>
+        <v>10.9562112</v>
       </c>
       <c r="N97">
-        <v>-8.609084000000003</v>
+        <v>-8.723211200000001</v>
       </c>
       <c r="O97">
-        <v>-1.893998480000001</v>
+        <v>-1.919106464</v>
       </c>
       <c r="P97">
-        <v>-6.715085520000002</v>
+        <v>-6.804104736000001</v>
       </c>
       <c r="Q97">
-        <v>-4.648085520000002</v>
+        <v>-4.737104736000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.060649326349604</v>
+        <v>1.314361657937005</v>
       </c>
       <c r="T97">
-        <v>13.22688880321576</v>
+        <v>16.5336110040197</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0453104772108388</v>
+        <v>0.0448384930732259</v>
       </c>
       <c r="W97">
-        <v>0.2251157894736842</v>
+        <v>0.2252270833333334</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2059567145947218</v>
+        <v>0.2038113321510269</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2687924663174802</v>
+        <v>0.2706924663174801</v>
       </c>
       <c r="C98">
-        <v>-33.17903904746492</v>
+        <v>-33.7601540205338</v>
       </c>
       <c r="D98">
-        <v>11.49496095253509</v>
+        <v>11.3978459794662</v>
       </c>
       <c r="E98">
-        <v>32.76400000000001</v>
+        <v>33.248</v>
       </c>
       <c r="F98">
-        <v>46.46400000000001</v>
+        <v>46.94800000000001</v>
       </c>
       <c r="G98">
         <v>1.79</v>
@@ -9323,37 +9323,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M98">
-        <v>10.9562112</v>
+        <v>11.0703384</v>
       </c>
       <c r="N98">
-        <v>-8.723211200000001</v>
+        <v>-8.837338400000002</v>
       </c>
       <c r="O98">
-        <v>-1.919106464</v>
+        <v>-1.944214448000001</v>
       </c>
       <c r="P98">
-        <v>-6.804104736000001</v>
+        <v>-6.893123952000002</v>
       </c>
       <c r="Q98">
-        <v>-4.737104736000001</v>
+        <v>-4.826123952000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.314361657937002</v>
+        <v>1.737215543916003</v>
       </c>
       <c r="T98">
-        <v>16.53361100401966</v>
+        <v>22.04481467202621</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0448384930732259</v>
+        <v>0.04437624056731635</v>
       </c>
       <c r="W98">
-        <v>0.2252270833333334</v>
+        <v>0.2253360824742268</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2038113321510269</v>
+        <v>0.2017101843968925</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2706924663174801</v>
+        <v>0.2725924663174801</v>
       </c>
       <c r="C99">
-        <v>-33.7601540205338</v>
+        <v>-34.33964179273639</v>
       </c>
       <c r="D99">
-        <v>11.3978459794662</v>
+        <v>11.30235820726362</v>
       </c>
       <c r="E99">
-        <v>33.248</v>
+        <v>33.732</v>
       </c>
       <c r="F99">
-        <v>46.94800000000001</v>
+        <v>47.432</v>
       </c>
       <c r="G99">
         <v>1.79</v>
@@ -9405,37 +9405,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M99">
-        <v>11.0703384</v>
+        <v>11.1844656</v>
       </c>
       <c r="N99">
-        <v>-8.837338400000002</v>
+        <v>-8.951465600000001</v>
       </c>
       <c r="O99">
-        <v>-1.944214448000001</v>
+        <v>-1.969322432</v>
       </c>
       <c r="P99">
-        <v>-6.893123952000002</v>
+        <v>-6.982143168</v>
       </c>
       <c r="Q99">
-        <v>-4.826123952000001</v>
+        <v>-4.915143168</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.737215543916003</v>
+        <v>2.582923315874004</v>
       </c>
       <c r="T99">
-        <v>22.04481467202621</v>
+        <v>33.06722200803932</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04437624056731635</v>
+        <v>0.04392342178601721</v>
       </c>
       <c r="W99">
-        <v>0.2253360824742268</v>
+        <v>0.2254428571428572</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2017101843968925</v>
+        <v>0.1996519172091692</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2725924663174801</v>
+        <v>0.2744924663174801</v>
       </c>
       <c r="C100">
-        <v>-34.33964179273639</v>
+        <v>-34.9175429209178</v>
       </c>
       <c r="D100">
-        <v>11.30235820726362</v>
+        <v>11.20845707908221</v>
       </c>
       <c r="E100">
-        <v>33.732</v>
+        <v>34.21600000000001</v>
       </c>
       <c r="F100">
-        <v>47.432</v>
+        <v>47.916</v>
       </c>
       <c r="G100">
         <v>1.79</v>
@@ -9487,37 +9487,37 @@
         <v>2.233000000000001</v>
       </c>
       <c r="M100">
-        <v>11.1844656</v>
+        <v>11.2985928</v>
       </c>
       <c r="N100">
-        <v>-8.951465600000001</v>
+        <v>-9.065592800000001</v>
       </c>
       <c r="O100">
-        <v>-1.969322432</v>
+        <v>-1.994430416</v>
       </c>
       <c r="P100">
-        <v>-6.982143168</v>
+        <v>-7.071162384000001</v>
       </c>
       <c r="Q100">
-        <v>-4.915143168</v>
+        <v>-5.004162384000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.582923315874004</v>
+        <v>5.120046631748007</v>
       </c>
       <c r="T100">
-        <v>33.06722200803932</v>
+        <v>66.13444401607863</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04392342178601721</v>
+        <v>0.04347975085888572</v>
       </c>
       <c r="W100">
-        <v>0.2254428571428572</v>
+        <v>0.2255474747474747</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1996519172091692</v>
+        <v>0.1976352311767533</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2744924663174801</v>
-      </c>
-      <c r="C101">
-        <v>-34.9175429209178</v>
-      </c>
-      <c r="D101">
-        <v>11.20845707908221</v>
-      </c>
-      <c r="E101">
-        <v>34.21600000000001</v>
-      </c>
-      <c r="F101">
-        <v>47.916</v>
-      </c>
-      <c r="G101">
-        <v>1.79</v>
-      </c>
-      <c r="H101">
-        <v>34.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.300000000000001</v>
-      </c>
-      <c r="K101">
-        <v>2.067</v>
-      </c>
-      <c r="L101">
-        <v>2.233000000000001</v>
-      </c>
-      <c r="M101">
-        <v>11.2985928</v>
-      </c>
-      <c r="N101">
-        <v>-9.065592800000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.994430416</v>
-      </c>
-      <c r="P101">
-        <v>-7.071162384000001</v>
-      </c>
-      <c r="Q101">
-        <v>-5.004162384000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.120046631748007</v>
-      </c>
-      <c r="T101">
-        <v>66.13444401607863</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04347975085888572</v>
-      </c>
-      <c r="W101">
-        <v>0.2255474747474747</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1976352311767533</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
